--- a/Docs/밸런스시트.xlsx
+++ b/Docs/밸런스시트.xlsx
@@ -7689,8 +7689,8 @@
       <c r="C8" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="D8" s="17" t="n">
-        <v>4</v>
+      <c r="D8" s="17">
+        <v>2</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>0.2</v>
@@ -7730,11 +7730,13 @@
         <v>0</v>
       </c>
       <c r="O8" s="17"/>
-      <c r="P8" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q8" s="24" t="s">
-        <v>102</v>
+      <c r="P8" s="17">
+        <v>2.5</v>
+      </c>
+      <c r="Q8" s="24" t="inlineStr">
+        <is>
+          <t>침묵 2코스트·경직 2.5초. 판정·손패: 10 결정 로그 A14~A16. 구현 확인 필요.</t>
+        </is>
       </c>
       <c r="R8" s="22" t="str">
         <f aca="false">IF(AND(LEFT($C8,1)="딜",ISNUMBER(M8)),M8,"")</f>
@@ -8679,9 +8681,9 @@
         <f aca="false">IFERROR(INDEX(스킬!$C:$C,MATCH($B8,스킬!$B:$B,0)),"")</f>
         <v>차단</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="23">
         <f aca="false">IFERROR(INDEX(스킬!$D:$D,MATCH($B8,스킬!$B:$B,0)),"")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" s="22" t="n">
         <f aca="false">IFERROR(INDEX(스킬!$F:$F,MATCH($B8,스킬!$B:$B,0)),"")</f>
@@ -8887,13 +8889,13 @@
         <f aca="false">IF($A12&lt;=4,"손패","대기열")</f>
         <v>대기열</v>
       </c>
-      <c r="H12" s="23" t="n">
+      <c r="H12" s="23">
         <f aca="false">IF($A12&lt;=4,0,SUM($D$5:INDEX($D$5:$D$12,$A12-4)))</f>
-        <v>14</v>
-      </c>
-      <c r="I12" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" s="22">
         <f aca="false">IFERROR(H12/범례!$C$23,"")</f>
-        <v>17.5</v>
+        <v>15.0</v>
       </c>
       <c r="J12" s="22" t="n">
         <f aca="false">IF($A12&lt;=4,0,SUM($E$5:INDEX($E$5:$E$12,$A12-4)))</f>
@@ -8917,9 +8919,9 @@
       <c r="A16" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="B16" s="23" t="n">
+      <c r="B16" s="23">
         <f aca="false">SUM(D5:D12)</f>
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" s="25"/>
     </row>
@@ -8927,9 +8929,9 @@
       <c r="A17" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B17" s="22">
         <f aca="false">IFERROR(B16/범례!$C$23,"")</f>
-        <v>46.25</v>
+        <v>43.75</v>
       </c>
       <c r="D17" s="25" t="s">
         <v>151</v>
@@ -8961,9 +8963,9 @@
       <c r="A20" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="22">
         <f aca="false">IFERROR(B19/B17,"")</f>
-        <v>16.3459459459459</v>
+        <v>17.28</v>
       </c>
       <c r="D20" s="25" t="s">
         <v>156</v>
@@ -8973,9 +8975,9 @@
       <c r="A21" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="B21" s="19" t="n">
+      <c r="B21" s="19">
         <f aca="false">IFERROR(범례!$C$27/B17,"")</f>
-        <v>0.972972972972973</v>
+        <v>1.0285714285714285</v>
       </c>
       <c r="D21" s="25" t="s">
         <v>158</v>
@@ -9145,12 +9147,14 @@
       <c r="G5" s="17" t="n">
         <v>2.5</v>
       </c>
-      <c r="H5" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I5" s="22" t="n">
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="I5" s="22">
         <f aca="false">IFERROR(C5/덱시뮬!$B$20,"")</f>
-        <v>18.3531746031746</v>
+        <v>17.36111111111111</v>
       </c>
       <c r="J5" s="20" t="s">
         <v>182</v>
@@ -9182,9 +9186,9 @@
       <c r="H6" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="I6" s="22" t="n">
+      <c r="I6" s="22">
         <f aca="false">IFERROR(C6/덱시뮬!$B$20,"")</f>
-        <v>18.3531746031746</v>
+        <v>17.36111111111111</v>
       </c>
       <c r="J6" s="20" t="s">
         <v>186</v>
@@ -9216,9 +9220,9 @@
       <c r="H7" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="I7" s="22" t="n">
+      <c r="I7" s="22">
         <f aca="false">IFERROR(C7/덱시뮬!$B$20,"")</f>
-        <v>18.3531746031746</v>
+        <v>17.36111111111111</v>
       </c>
       <c r="J7" s="20" t="s">
         <v>190</v>

--- a/Docs/밸런스시트.xlsx
+++ b/Docs/밸런스시트.xlsx
@@ -6496,8 +6496,10 @@
         <x:f aca="0">COUNTIF(C5:C18,"딜/단일")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C29" s="25" t="s">
-        <x:v>118</x:v>
+      <x:c r="C29" s="25" t="inlineStr">
+        <x:is>
+          <x:t>목표 6</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="30" ht="29.850000381469727" hidden="0">
@@ -6520,8 +6522,10 @@
         <x:f aca="0">COUNTIF(C5:C18,"차단")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C31" s="25" t="s">
-        <x:v>121</x:v>
+      <x:c r="C31" s="25" t="inlineStr">
+        <x:is>
+          <x:t>목표 2</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="32" ht="29.850000381469727" hidden="0">
@@ -6532,8 +6536,10 @@
         <x:f aca="0">COUNTIF(C5:C18,"방어")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C32" s="25" t="s">
-        <x:v>121</x:v>
+      <x:c r="C32" s="25" t="inlineStr">
+        <x:is>
+          <x:t>목표 2</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0">

--- a/Docs/밸런스시트.xlsx
+++ b/Docs/밸런스시트.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범례" sheetId="1" r:id="R4c729fbfa5454cda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직업" sheetId="2" r:id="R623dcf9085d1448a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="스킬" sheetId="3" r:id="Rb402684eb8164c64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="덱시뮬" sheetId="4" r:id="R3cd2c215fdc44952"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="적" sheetId="5" r:id="R99ac07ec9c814d27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HP예산" sheetId="6" r:id="R30e7dee9b89d498d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인카운터" sheetId="7" r:id="R7684ec5e80244a16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범례" sheetId="1" r:id="R5d69d4cccbff4223"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직업" sheetId="2" r:id="Rf18344cfc67c4f76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="스킬" sheetId="3" r:id="Rc906251a3d3e47f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="덱시뮬" sheetId="4" r:id="R8a8a9ba6881045d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="적" sheetId="5" r:id="R129acdc605d54390"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HP예산" sheetId="6" r:id="Re96747d556624d08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인카운터" sheetId="7" r:id="R105d4fd406f24aff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -242,28 +242,31 @@
     <x:t xml:space="preserve">스킬</x:t>
   </x:si>
   <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">스킬 풀 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">14</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">종</x:t>
+    <x:t xml:space="preserve">덱시뮬</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">덱 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">8</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">장 시뮬레이션</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -278,124 +281,11 @@
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t xml:space="preserve">코스트당 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">/ </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">시간당 기대 피해가 자동 계산됨</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">덱시뮬</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">덱 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">8</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">장 시뮬레이션</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
       <x:t xml:space="preserve">코스트 병목과 행동 잠금 병목을 모두 계산 ★</x:t>
     </x:r>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">적</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">적 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">4</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">종 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">+ </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">보스</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">담당 색상별 스펙</x:t>
-    </x:r>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">인카운터</x:t>
@@ -509,86 +399,86 @@
     <x:t xml:space="preserve">크리티컬 발생 시 피해 배수</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">방어 상수</x:t>
+  </x:si>
+  <x:si>
     <x:r>
       <x:rPr>
         <x:sz val="1000"/>
         <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">[</x:t>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">방어감소율 </x:t>
     </x:r>
     <x:r>
       <x:rPr>
         <x:sz val="1000"/>
         <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">근거를 적으세요</x:t>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">= </x:t>
     </x:r>
     <x:r>
       <x:rPr>
         <x:sz val="1000"/>
         <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">]</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">방어 상수</x:t>
-  </x:si>
-  <x:si>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">방어력 </x:t>
+    </x:r>
     <x:r>
       <x:rPr>
         <x:sz val="1000"/>
         <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">방어감소율 </x:t>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">/ (</x:t>
     </x:r>
     <x:r>
       <x:rPr>
         <x:sz val="1000"/>
         <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">= </x:t>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">방어력 </x:t>
     </x:r>
     <x:r>
       <x:rPr>
         <x:sz val="1000"/>
         <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">방어력 </x:t>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">+ </x:t>
     </x:r>
     <x:r>
       <x:rPr>
         <x:sz val="1000"/>
         <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">/ (</x:t>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">상수</x:t>
     </x:r>
     <x:r>
       <x:rPr>
         <x:sz val="1000"/>
         <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">방어력 </x:t>
-    </x:r>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
     <x:r>
       <x:rPr>
         <x:sz val="1000"/>
         <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
       </x:rPr>
-      <x:t xml:space="preserve">+ </x:t>
+      <x:t xml:space="preserve">[</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -597,7 +487,7 @@
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t xml:space="preserve">상수</x:t>
+      <x:t xml:space="preserve">근거를 적으세요</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -605,7 +495,7 @@
         <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
       </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
+      <x:t xml:space="preserve">]</x:t>
     </x:r>
   </x:si>
   <x:si>
@@ -901,6 +791,1058 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">잡몹전 평균 적 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">직업 스펙</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">HP</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">방어력</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">기대 크리 배율</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">설계 메모</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">5</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">행이 실제 데이터입니다</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">. </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">스킬 시트가 이 행을 참조하므로 행을 옮기지 마세요</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">.</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="13"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">스킬 풀 밸런스 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="13"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(14</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="13"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">종</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="13"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">스킬명</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">분류</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">코스트</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">잠금</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">초</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">타수</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">총 피해량</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">기대 피해 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(1</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">체</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">기대 피해 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">잡몹</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">코스트당 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">보스</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">코스트당 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">잡몹</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">시간당 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">잡몹</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">방어도 부여</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">경직</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">초</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">검증</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">코스트</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">검증</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">시간</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">코스트당 최대</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">차단</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">·</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">방어 카드는 제외됨</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">코스트당 최소</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">코스트당 비율</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">목표 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">1.30 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">이하</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">시간당 최대</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">잠금 시간 대비 효율</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">시간당 최소</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">시간당 비율</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">딜</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">/</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">단일 장수</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">딜</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">/</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">광역 장수</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">목표 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">4</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">차단 카드 장수</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">방어 카드 장수</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">단일 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">/ </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">광역 설계</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">L</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">열</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">보스 기준</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">과 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">M</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">열</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">잡몹 기준</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">의 격차가 크면 그 카드는 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">'</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">상황용</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">'</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">입니다</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">. </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">격차가 없으면 범용입니다</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">.</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">보스전은 적 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">1</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">체이므로 광역기는 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">L</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">열 값만 나옵니다</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">. </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">덱 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">8</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">장에 상황용을 몇 장 넣을지가 결정이 됩니다</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">.</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="13"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">덱 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="13"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">8</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="13"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">장 구성 시뮬레이션</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">B</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">열에 스킬명만 입력하면 나머지는 자동 계산됩니다</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">. </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">스킬 시트의 스킬명과 정확히 일치해야 합니다</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">.</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">슬롯</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">위치</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">대응카드 코스트기준</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">대응카드 잠금기준</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">검증</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">덱 총 코스트</x:t>
+  </x:si>
+  <x:si>
     <x:r>
       <x:rPr>
         <x:sz val="1000"/>
@@ -908,7 +1850,7 @@
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t xml:space="preserve">최대 </x:t>
+      <x:t xml:space="preserve">덱 </x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -916,7 +1858,7 @@
         <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
       </x:rPr>
-      <x:t xml:space="preserve">HP</x:t>
+      <x:t xml:space="preserve">1</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -925,7 +1867,7 @@
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t xml:space="preserve">의 </x:t>
+      <x:t xml:space="preserve">사이클 총 잠금 시간</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -933,7 +1875,7 @@
         <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
       </x:rPr>
-      <x:t xml:space="preserve">50%</x:t>
+      <x:t xml:space="preserve">(</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -942,124 +1884,124 @@
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t xml:space="preserve">씩 회복</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
+      <x:t xml:space="preserve">초</x:t>
+    </x:r>
     <x:r>
       <x:rPr>
         <x:sz val="1000"/>
         <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">확정값 </x:t>
-    </x:r>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">1</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">사이클 시간보다 크면 코스트가 아니라 잠금이 병목입니다</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">목표 전투 시간 대비 사이클 수</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">목표 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">1.0~1.5</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">회</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
     <x:r>
       <x:rPr>
         <x:sz val="1000"/>
         <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(10_</x:t>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">대응 카드 장수 </x:t>
     </x:r>
     <x:r>
       <x:rPr>
         <x:sz val="1000"/>
         <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">결정사항</x:t>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
     </x:r>
     <x:r>
       <x:rPr>
         <x:sz val="1000"/>
         <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">_</x:t>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">차단</x:t>
     </x:r>
     <x:r>
       <x:rPr>
         <x:sz val="1000"/>
         <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">로그 </x:t>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">+</x:t>
     </x:r>
     <x:r>
       <x:rPr>
         <x:sz val="1000"/>
         <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">A8)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">잡몹전 평균 적 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">광역기 실효 피해 계산용</x:t>
-  </x:si>
-  <x:si>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">방어</x:t>
+    </x:r>
     <x:r>
       <x:rPr>
         <x:sz val="1000"/>
         <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">인카운터 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1~4</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">의 적 수 평균 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(2,2,2,3)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">직업 스펙</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">HP</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">방어력</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">기대 크리 배율</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">설계 메모</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">마법사</x:t>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
   </x:si>
   <x:si>
     <x:r>
@@ -1067,25 +2009,50 @@
         <x:i/>
         <x:sz val="900"/>
         <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">5</x:t>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">권장 </x:t>
     </x:r>
     <x:r>
       <x:rPr>
         <x:i/>
         <x:sz val="900"/>
         <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">행이 실제 데이터입니다</x:t>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">2~3</x:t>
     </x:r>
     <x:r>
       <x:rPr>
         <x:i/>
         <x:sz val="900"/>
         <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">장</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">이 시트의 목적</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">앞쪽에 캐스팅 긴 카드를 몰아두면 코스트가 넘쳐도 못 끌어옵니다</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
         <x:rFont val="Arial"/>
       </x:rPr>
       <x:t xml:space="preserve">. </x:t>
@@ -1098,7 +2065,7 @@
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t xml:space="preserve">스킬 시트가 이 행을 참조하므로 행을 옮기지 마세요</x:t>
+      <x:t xml:space="preserve">덱 순서 자체가 설계 결정입니다</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -1111,87 +2078,42 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="1000"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">공격력 스탯은 없습니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="1000"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="1000"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">최종피해 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="1000"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">= (</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="1000"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">스킬 피해량 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="1000"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">x </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="1000"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">타수</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="1000"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">) x (1 - </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="1000"/>
-        <x:color rgb="FFC00000"/>
+    <x:t xml:space="preserve">적 스펙</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">F</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">열</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1199,23 +2121,203 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:b/>
-        <x:sz val="1000"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">) x </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="1000"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">크리배율</x:t>
-    </x:r>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">), I</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">열</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">예상 처치 시간</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">은 자동 계산</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">.</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">담당 색상</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">피해량</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">방어감소율</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">캐스팅</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">초</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">차단 가능</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">교육 의도</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:color rgb="FF0000FF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">잡몹 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:color rgb="FF0000FF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">A</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">초록</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:color rgb="FF0000FF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">잡몹 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:color rgb="FF0000FF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">B</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">주황</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">가능</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">차단 카드의 존재와 사용 타이밍</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:color rgb="FF0000FF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">잡몹 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="10"/>
+        <x:color rgb="FF0000FF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">C</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">빨강</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">불가</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">방어도 카드의 존재</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -1225,7 +2327,7 @@
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t xml:space="preserve">스킬 풀 밸런스 </x:t>
+      <x:t xml:space="preserve">런 전체 </x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -1233,7 +2335,7 @@
         <x:sz val="13"/>
         <x:rFont val="Arial"/>
       </x:rPr>
-      <x:t xml:space="preserve">(14</x:t>
+      <x:t xml:space="preserve">HP </x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -1242,12 +2344,56 @@
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t xml:space="preserve">종</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="13"/>
+      <x:t xml:space="preserve">예산</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">전투</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">구성</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">완벽 대응 시 피해</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">평범 대응 시 피해</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">누적 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">HP (</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">완벽</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="10"/>
+        <x:color rgb="FFFFFFFF"/>
         <x:rFont val="Arial"/>
       </x:rPr>
       <x:t xml:space="preserve">)</x:t>
@@ -1256,141 +2402,13 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">피해량은 계수가 아니라 절대값입니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">카드에 적히는 숫자가 곧 이 값입니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. F·I~N</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">열 자동 계산</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">분류에 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">'</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">광역</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">'</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">이 포함되면 잡몹전 기대 피해에 평균 적 수가 곱해집니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">스킬명</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">분류</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">코스트</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
         <x:b/>
         <x:sz val="10"/>
         <x:color rgb="FFFFFFFF"/>
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t xml:space="preserve">캐스팅</x:t>
+      <x:t xml:space="preserve">누적 </x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -1399,7 +2417,7 @@
         <x:color rgb="FFFFFFFF"/>
         <x:rFont val="Arial"/>
       </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
+      <x:t xml:space="preserve">HP (</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -1409,7 +2427,7 @@
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t xml:space="preserve">초</x:t>
+      <x:t xml:space="preserve">평범</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -1422,2307 +2440,6 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">잠금</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">초</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">피해량</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">타수</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">총 피해량</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">기대 피해 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(1</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">체</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">기대 피해 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">잡몹</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">코스트당 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">보스</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">코스트당 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">잡몹</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">시간당 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">잡몹</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">방어도 부여</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">경직</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">초</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">설계 의도</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">검증</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">코스트</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">검증</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">시간</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SK-A</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">화염탄</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">딜</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">/</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">단일</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">프로토타입 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">단계 구현</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. Skill_Fireball</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SK-B</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">서리화살</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Skill_Frostbolt</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SK-C</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">수정방패</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">방어</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">Skill_CrystalShield. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">방어도 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">120</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">은 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">3</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">단계에서 적용</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SK-D</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">침묵</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">차단</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SK-E</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">연쇄번개</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">Skill_ChainLightning. 5~8</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">일차에 광역으로 전환 검토</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SK-F</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">폭발</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">Skill_Explosion. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">광역 전환 후보</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SK-G</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">관통</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Skill_Pierce</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SK-H</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">불기둥</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">Skill_FlamePillar. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">광역 전환 후보</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">밸런스 검증 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">딜 카드만</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">잡몹전 기준</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">코스트당 최대</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">차단</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">·</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">방어 카드는 제외됨</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">코스트당 최소</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">코스트당 비율</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">목표 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1.30 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">이하</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">시간당 최대</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">잠금 시간 대비 효율</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">시간당 최소</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">시간당 비율</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">딜</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">/</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">단일 장수</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">목표 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">4</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">딜</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">/</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">광역 장수</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">차단 카드 장수</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">목표 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">3</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">방어 카드 장수</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">두 비율이 모두 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1.3 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">이하여야 합니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">한쪽만 맞추면 무조건 채용되는 카드가 생깁니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">함정</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">: </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">차단</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">·</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">방어 카드에 딜을 붙이면 트레이드오프가 사라집니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">대응 카드는 딜을 포기하는 대가여야 합니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">단일 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">/ </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">광역 설계</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">손익분기는 적 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">2</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">체</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">같은 코스트라면 광역 피해량은 단일 피해량의 절반입니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">L</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">열</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">보스 기준</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">과 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">M</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">열</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">잡몹 기준</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">의 격차가 크면 그 카드는 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">'</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">상황용</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">'</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">입니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">격차가 없으면 범용입니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">보스전은 적 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">체이므로 광역기는 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">L</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">열 값만 나옵니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">덱 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">8</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">장에 상황용을 몇 장 넣을지가 결정이 됩니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">광역기의 대가는 코스트가 아니라 캐스팅 시간</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(0.8~1.2</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">초</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">입니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">코스트를 올리면 피해량도 비례해 올리세요</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="13"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">덱 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="13"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">8</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="13"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">장 구성 시뮬레이션</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">B</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">열에 스킬명만 입력하면 나머지는 자동 계산됩니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">스킬 시트의 스킬명과 정확히 일치해야 합니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">슬롯</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">기대 피해</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">위치</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">대응카드 코스트기준</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">대응카드 잠금기준</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">검증</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">덱 총 코스트</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">덱 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">사이클 총 잠금 시간</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">초</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">사이클 시간보다 크면 코스트가 아니라 잠금이 병목입니다</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">덱 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">사이클 총 기대 피해</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">목표 전투 시간 대비 사이클 수</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">목표 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1.0~1.5</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">회</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">대응 카드 장수 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">차단</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">+</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">방어</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">권장 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">2~3</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">장</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">이 시트의 목적</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">앞쪽에 캐스팅 긴 카드를 몰아두면 코스트가 넘쳐도 못 끌어옵니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">덱 순서 자체가 설계 결정입니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">적 스펙</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">F</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">열</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">방어감소율</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">), I</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">열</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">예상 처치 시간</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">은 자동 계산</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">담당 색상</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">방어감소율</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">차단 가능</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">교육 의도</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">잡몹 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">A</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">초록</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">대응 불필요한 공격을 먼저 보여줌</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">잡몹 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">B</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">주황</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">가능</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">차단 카드의 존재와 사용 타이밍</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">잡몹 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">C</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">빨강</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">불가</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">방어도 카드의 존재</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">A·B·C</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">는 프로토타입 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">2</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">단계 구현값입니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. 4</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">열은 공격력이 아니라 피해량입니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFC00000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">담당 색상</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">: </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">초록</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">=</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">대응 불필요 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">/ </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">주황</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">=</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">차단 대상 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">/ </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">빨강</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">=</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">방어도 대상</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="13"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">런 전체 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="13"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">HP </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="13"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">예산</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">전투</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">구성</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">완벽 대응 시 피해</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">평범 대응 시 피해</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">누적 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">HP (</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">완벽</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">누적 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">HP (</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">평범</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">판정</x:t>
   </x:si>
   <x:si>
@@ -3736,65 +2453,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">포션 총 회복량</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">런 전체 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">3</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">회 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">x </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">최대 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">HP 50%</x:t>
-    </x:r>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">감당 가능 총 피해</x:t>
@@ -5253,32 +3911,32 @@
       <x:c r="A11" s="7" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B11" s="6" t="s">
-        <x:v>13</x:v>
+      <x:c r="B11" s="6" t="str">
+        <x:v>구현 스킬 11종 계산. 미구현 3종은 03 초안 참조</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="29.850000381469727" hidden="0">
       <x:c r="A12" s="7" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="B12" s="6" t="s">
-        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0">
       <x:c r="A13" s="7" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B13" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>현재 A·B·C. 주 공격 기준, 전체 패턴은 04 참조</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0">
       <x:c r="A14" s="7" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0">
@@ -5288,38 +3946,38 @@
     </x:row>
     <x:row r="18" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A18" s="8" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B18" s="8" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C18" s="8" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B18" s="8" t="s">
+      <x:c r="D18" s="8" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="C18" s="8" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D18" s="8" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0">
       <x:c r="A19" s="9" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B19" s="10" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="D19" s="12" t="s">
-        <x:v>26</x:v>
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="D19" s="12" t="str">
+        <x:v>10 A25·T21. 패시브 없는 기본값</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0">
       <x:c r="A20" s="9" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B20" s="10" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
         <x:v>100</x:v>
@@ -5330,10 +3988,10 @@
     </x:row>
     <x:row r="21" ht="15" hidden="0">
       <x:c r="A21" s="9" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="10" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
         <x:v>0</x:v>
@@ -5344,25 +4002,25 @@
     </x:row>
     <x:row r="22" ht="15" hidden="0">
       <x:c r="A22" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B22" s="10" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C22" s="13" t="n">
         <x:f aca="0">C21/(C21+C20)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="10" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0">
       <x:c r="A23" s="9" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B23" s="10" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C23" s="11" t="n">
         <x:v>0.8</x:v>
@@ -5373,10 +4031,10 @@
     </x:row>
     <x:row r="24" ht="15" hidden="0">
       <x:c r="A24" s="9" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B24" s="10" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
         <x:v>10</x:v>
@@ -5387,7 +4045,7 @@
     </x:row>
     <x:row r="25" ht="15" hidden="0">
       <x:c r="A25" s="9" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B25" s="12"/>
       <x:c r="C25" s="11" t="n">
@@ -5399,24 +4057,24 @@
     </x:row>
     <x:row r="26" ht="29.850000381469727" hidden="0">
       <x:c r="A26" s="9" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B26" s="10" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="D26" s="10" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0">
       <x:c r="A27" s="9" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B27" s="10" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
         <x:v>45</x:v>
@@ -5427,10 +4085,10 @@
     </x:row>
     <x:row r="28" ht="15" hidden="0">
       <x:c r="A28" s="9" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B28" s="10" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
         <x:v>180</x:v>
@@ -5441,30 +4099,30 @@
     </x:row>
     <x:row r="29" ht="15" hidden="0">
       <x:c r="A29" s="9" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B29" s="10" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B29" s="10" t="str">
+        <x:v>최대 HP의 30%씩 회복</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D29" s="10" t="s">
-        <x:v>47</x:v>
+      <x:c r="D29" s="10" t="str">
+        <x:v>10 A8·A28. 시작 3개, 보충 없음</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0">
       <x:c r="A30" s="9" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B30" s="10" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B30" s="10" t="str">
+        <x:v>정식 런 계획의 광역 피해 참고값</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="D30" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="D30" s="10" t="str">
+        <x:v>5전투 계획의 잡몹전 평균. 현재 시연은 B→C→B+C</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0">
@@ -5474,7 +4132,7 @@
     </x:row>
     <x:row r="32" ht="15" hidden="0">
       <x:c r="A32" s="14" t="str">
-        <x:v>2026-09-17: 계산 전제·접근 시간·빈 입력 표시 정정. 기록: 07 D-05.</x:v>
+        <x:v>2026-09-23: 현재 스킬·치명타·포션·HP 시험값 반영. 이전 파일은 보관/2026-09-23_정정전.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5495,37 +4153,37 @@
   <x:sheetData>
     <x:row r="1" ht="16.149999618530273" hidden="0">
       <x:c r="A1" s="15" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0">
       <x:c r="A2" s="2" t="str">
-        <x:v>현재 프로토타입 조건. E열 기대 크리 배율 자동 계산.</x:v>
+        <x:v>현재 기본값. E열은 반올림 전 평균 배율, 실제 기대 피해는 스킬 J열.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A4" s="8" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B4" s="16" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C4" s="8" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D4" s="8" t="str">
         <x:v>적용 크리율</x:v>
       </x:c>
       <x:c r="E4" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F4" s="8" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="17" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B5" s="17" t="n">
         <x:v>500</x:v>
@@ -5534,14 +4192,14 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D5" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="E5" s="19" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(D5)),"",1+D5*('범례'!$C$19-1))</x:f>
-        <x:v>1</x:v>
+        <x:v>1.075</x:v>
       </x:c>
       <x:c r="F5" s="34" t="str">
-        <x:v>현재 크리 미구현(12). 계산 0%; 기획 15%는 10 참조.</x:v>
+        <x:v>기본 크리율 15%. 패시브 제외, 10 A25·A28</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0">
@@ -5566,12 +4224,12 @@
     </x:row>
     <x:row r="9" ht="15" hidden="0">
       <x:c r="A9" s="21" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0">
-      <x:c r="A10" s="14" t="s">
-        <x:v>59</x:v>
+      <x:c r="A10" s="14" t="str">
+        <x:v>공격력 없음. 타격·적마다 크리 판정 후 피해 반올림. 전체 피해는 각 타격 합산.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5602,589 +4260,606 @@
   <x:sheetData>
     <x:row r="1" ht="20.100000381469727" hidden="0">
       <x:c r="A1" s="15" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0">
-      <x:c r="A2" s="2" t="s">
-        <x:v>61</x:v>
+      <x:c r="A2" s="2" t="str">
+        <x:v>현재 구현 11종, 미구현 3종 수치는 비움. 10 A20·A23·A25 기준, 패시브·과잉 피해·시전 취소 제외.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A4" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D4" s="8" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E4" s="8" t="str">
+        <x:v>시전/채널(초)</x:v>
+      </x:c>
+      <x:c r="F4" s="8" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G4" s="8" t="str">
+        <x:v>1타 피해</x:v>
+      </x:c>
+      <x:c r="H4" s="8" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I4" s="8" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J4" s="8" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K4" s="8" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="s">
+      <x:c r="L4" s="8" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C4" s="8" t="s">
+      <x:c r="M4" s="8" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="s">
+      <x:c r="N4" s="8" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="s">
+      <x:c r="O4" s="8" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="F4" s="8" t="s">
+      <x:c r="P4" s="8" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G4" s="8" t="s">
+      <x:c r="Q4" s="8" t="str">
+        <x:v>구현·발동 방식</x:v>
+      </x:c>
+      <x:c r="R4" s="8" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="H4" s="8" t="s">
+      <x:c r="S4" s="8" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="I4" s="8" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="J4" s="8" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="K4" s="8" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="L4" s="8" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="M4" s="8" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="N4" s="8" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="O4" s="8" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="P4" s="8" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="Q4" s="8" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="R4" s="8" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="S4" s="8" t="s">
-        <x:v>80</x:v>
-      </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0">
-      <x:c r="A5" s="11" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B5" s="17" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C5" s="17" t="s">
-        <x:v>83</x:v>
+      <x:c r="A5" s="11" t="str">
+        <x:v>SK01</x:v>
+      </x:c>
+      <x:c r="B5" s="17" t="str">
+        <x:v>파이어볼</x:v>
+      </x:c>
+      <x:c r="C5" s="17" t="str">
+        <x:v>딜/단일</x:v>
       </x:c>
       <x:c r="D5" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E5" s="17" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="22" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(E5)),"",MAX(E5,'범례'!$C$26))</x:f>
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="G5" s="17" t="n">
-        <x:v>100</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H5" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I5" s="19" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(G5)),"",G5*H5)</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J5" s="23" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(I5)),"",I5*(1-'범례'!$C$22)*'직업'!$E$5)</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K5" s="23" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(H5))),"",G5*MAX(1,H5))</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J5" s="41" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(H5))),"",IF(G5&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G5*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G5*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H5)))</x:f>
+        <x:v>32.25</x:v>
+      </x:c>
+      <x:c r="K5" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J5)),"",J5*IF(ISNUMBER(SEARCH("광역",$C5)),'범례'!$C$30,1))</x:f>
-        <x:v>100</x:v>
+        <x:v>32.25</x:v>
       </x:c>
       <x:c r="L5" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J5)),NOT(ISNUMBER(D5)),D5=0),"",J5/D5)</x:f>
-        <x:v>33.333333333333336</x:v>
+        <x:v>32.25</x:v>
       </x:c>
       <x:c r="M5" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K5)),NOT(ISNUMBER(D5)),D5=0),"",K5/D5)</x:f>
-        <x:v>33.333333333333336</x:v>
+        <x:v>32.25</x:v>
       </x:c>
       <x:c r="N5" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K5)),NOT(ISNUMBER(F5)),F5=0),"",K5/F5)</x:f>
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="O5" s="17"/>
-      <x:c r="P5" s="17"/>
-      <x:c r="Q5" s="20" t="s">
-        <x:v>84</x:v>
+        <x:v>80.625</x:v>
+      </x:c>
+      <x:c r="O5" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P5" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q5" s="20" t="str">
+        <x:v>시작 덱. 일반 시전</x:v>
       </x:c>
       <x:c r="R5" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C5,1)="딜",ISNUMBER(M5)),M5,"")</x:f>
-        <x:v>33.333333333333336</x:v>
+        <x:v>32.25</x:v>
       </x:c>
       <x:c r="S5" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C5,1)="딜",ISNUMBER(N5)),N5,"")</x:f>
-        <x:v>250</x:v>
+        <x:v>80.625</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0">
-      <x:c r="A6" s="11" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B6" s="17" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C6" s="17" t="s">
-        <x:v>83</x:v>
+      <x:c r="A6" s="11" t="str">
+        <x:v>SK02</x:v>
+      </x:c>
+      <x:c r="B6" s="17" t="str">
+        <x:v>아이스애로우</x:v>
+      </x:c>
+      <x:c r="C6" s="17" t="str">
+        <x:v>딜/단일</x:v>
       </x:c>
       <x:c r="D6" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E6" s="17" t="n">
-        <x:v>0.3</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="F6" s="22" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(E6)),"",MAX(E6,'범례'!$C$26))</x:f>
-        <x:v>0.4</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="G6" s="17" t="n">
-        <x:v>120</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H6" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I6" s="19" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(G6)),"",G6*H6)</x:f>
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="J6" s="23" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(I6)),"",I6*(1-'범례'!$C$22)*'직업'!$E$5)</x:f>
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="K6" s="23" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G6)),NOT(ISNUMBER(H6))),"",G6*MAX(1,H6))</x:f>
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="J6" s="41" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G6)),NOT(ISNUMBER(H6))),"",IF(G6&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G6*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G6*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H6)))</x:f>
+        <x:v>188.5</x:v>
+      </x:c>
+      <x:c r="K6" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J6)),"",J6*IF(ISNUMBER(SEARCH("광역",$C6)),'범례'!$C$30,1))</x:f>
-        <x:v>120</x:v>
+        <x:v>188.5</x:v>
       </x:c>
       <x:c r="L6" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J6)),NOT(ISNUMBER(D6)),D6=0),"",J6/D6)</x:f>
-        <x:v>30</x:v>
+        <x:v>37.7</x:v>
       </x:c>
       <x:c r="M6" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K6)),NOT(ISNUMBER(D6)),D6=0),"",K6/D6)</x:f>
-        <x:v>30</x:v>
+        <x:v>37.7</x:v>
       </x:c>
       <x:c r="N6" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K6)),NOT(ISNUMBER(F6)),F6=0),"",K6/F6)</x:f>
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="O6" s="17"/>
-      <x:c r="P6" s="17"/>
-      <x:c r="Q6" s="24" t="s">
-        <x:v>87</x:v>
+        <x:v>67.32142857142857</x:v>
+      </x:c>
+      <x:c r="O6" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P6" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q6" s="24" t="str">
+        <x:v>시작 덱. 채널링 0.5초마다, 사망 후딜 0.3초</x:v>
       </x:c>
       <x:c r="R6" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C6,1)="딜",ISNUMBER(M6)),M6,"")</x:f>
-        <x:v>30</x:v>
+        <x:v>37.7</x:v>
       </x:c>
       <x:c r="S6" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C6,1)="딜",ISNUMBER(N6)),N6,"")</x:f>
-        <x:v>300</x:v>
+        <x:v>67.32142857142857</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0">
-      <x:c r="A7" s="11" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="B7" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>90</x:v>
+      <x:c r="A7" s="11" t="str">
+        <x:v>SK03</x:v>
+      </x:c>
+      <x:c r="B7" s="17" t="str">
+        <x:v>매직 커터</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="str">
+        <x:v>딜/단일</x:v>
       </x:c>
       <x:c r="D7" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E7" s="17" t="n">
-        <x:v>0.2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F7" s="22" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(E7)),"",MAX(E7,'범례'!$C$26))</x:f>
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="G7" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H7" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I7" s="19" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(G7)),"",G7*H7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J7" s="23" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(I7)),"",I7*(1-'범례'!$C$22)*'직업'!$E$5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K7" s="23" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G7)),NOT(ISNUMBER(H7))),"",G7*MAX(1,H7))</x:f>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J7" s="41" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G7)),NOT(ISNUMBER(H7))),"",IF(G7&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G7*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G7*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H7)))</x:f>
+        <x:v>64.5</x:v>
+      </x:c>
+      <x:c r="K7" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J7)),"",J7*IF(ISNUMBER(SEARCH("광역",$C7)),'범례'!$C$30,1))</x:f>
-        <x:v>0</x:v>
+        <x:v>64.5</x:v>
       </x:c>
       <x:c r="L7" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J7)),NOT(ISNUMBER(D7)),D7=0),"",J7/D7)</x:f>
-        <x:v>0</x:v>
+        <x:v>32.25</x:v>
       </x:c>
       <x:c r="M7" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K7)),NOT(ISNUMBER(D7)),D7=0),"",K7/D7)</x:f>
-        <x:v>0</x:v>
+        <x:v>32.25</x:v>
       </x:c>
       <x:c r="N7" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K7)),NOT(ISNUMBER(F7)),F7=0),"",K7/F7)</x:f>
+        <x:v>161.25</x:v>
+      </x:c>
+      <x:c r="O7" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O7" s="17" t="n">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="P7" s="17"/>
-      <x:c r="Q7" s="24" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="R7" s="22" t="str">
+      <x:c r="P7" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q7" s="24" t="str">
+        <x:v>시작 덱. 일반 시전</x:v>
+      </x:c>
+      <x:c r="R7" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C7,1)="딜",ISNUMBER(M7)),M7,"")</x:f>
-      </x:c>
-      <x:c r="S7" s="22" t="str">
+        <x:v>32.25</x:v>
+      </x:c>
+      <x:c r="S7" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C7,1)="딜",ISNUMBER(N7)),N7,"")</x:f>
+        <x:v>161.25</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0">
-      <x:c r="A8" s="11" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B8" s="17" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C8" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D8" s="17">
-        <x:v>2</x:v>
+      <x:c r="A8" s="11" t="str">
+        <x:v>SK04</x:v>
+      </x:c>
+      <x:c r="B8" s="17" t="str">
+        <x:v>파이어 필라</x:v>
+      </x:c>
+      <x:c r="C8" s="17" t="str">
+        <x:v>딜/광역</x:v>
+      </x:c>
+      <x:c r="D8" s="17" t="n">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E8" s="17" t="n">
-        <x:v>0.2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F8" s="22" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(E8)),"",MAX(E8,'범례'!$C$26))</x:f>
-        <x:v>0.4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H8" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I8" s="19" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(G8)),"",G8*H8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J8" s="23" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(I8)),"",I8*(1-'범례'!$C$22)*'직업'!$E$5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K8" s="23" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G8)),NOT(ISNUMBER(H8))),"",G8*MAX(1,H8))</x:f>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J8" s="41" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G8)),NOT(ISNUMBER(H8))),"",IF(G8&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G8*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G8*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H8)))</x:f>
+        <x:v>53.75</x:v>
+      </x:c>
+      <x:c r="K8" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J8)),"",J8*IF(ISNUMBER(SEARCH("광역",$C8)),'범례'!$C$30,1))</x:f>
-        <x:v>0</x:v>
+        <x:v>120.9375</x:v>
       </x:c>
       <x:c r="L8" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J8)),NOT(ISNUMBER(D8)),D8=0),"",J8/D8)</x:f>
-        <x:v>0</x:v>
+        <x:v>13.4375</x:v>
       </x:c>
       <x:c r="M8" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K8)),NOT(ISNUMBER(D8)),D8=0),"",K8/D8)</x:f>
-        <x:v>0</x:v>
+        <x:v>30.234375</x:v>
       </x:c>
       <x:c r="N8" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K8)),NOT(ISNUMBER(F8)),F8=0),"",K8/F8)</x:f>
+        <x:v>120.9375</x:v>
+      </x:c>
+      <x:c r="O8" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O8" s="17"/>
-      <x:c r="P8" s="17">
-        <x:v>2.5</x:v>
+      <x:c r="P8" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Q8" s="24" t="str">
-        <x:v>구현·검증 기록: 07 D-04. 사양: 10 A14~A16.</x:v>
-      </x:c>
-      <x:c r="R8" s="22" t="str">
+        <x:v>시작 덱. 일반 시전</x:v>
+      </x:c>
+      <x:c r="R8" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C8,1)="딜",ISNUMBER(M8)),M8,"")</x:f>
-      </x:c>
-      <x:c r="S8" s="22" t="str">
+        <x:v>30.234375</x:v>
+      </x:c>
+      <x:c r="S8" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C8,1)="딜",ISNUMBER(N8)),N8,"")</x:f>
+        <x:v>120.9375</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0">
-      <x:c r="A9" s="11" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="B9" s="17" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C9" s="17" t="s">
-        <x:v>83</x:v>
+      <x:c r="A9" s="11" t="str">
+        <x:v>SK05</x:v>
+      </x:c>
+      <x:c r="B9" s="17" t="str">
+        <x:v>라이트닝 스피어</x:v>
+      </x:c>
+      <x:c r="C9" s="17" t="str">
+        <x:v>딜/단일</x:v>
       </x:c>
       <x:c r="D9" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E9" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="F9" s="22" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(E9)),"",MAX(E9,'범례'!$C$26))</x:f>
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="G9" s="17" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H9" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G9" s="17" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H9" s="17" t="n">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="I9" s="19" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(G9)),"",G9*H9)</x:f>
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="J9" s="23" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(I9)),"",I9*(1-'범례'!$C$22)*'직업'!$E$5)</x:f>
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="K9" s="23" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G9)),NOT(ISNUMBER(H9))),"",G9*MAX(1,H9))</x:f>
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="J9" s="41" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G9)),NOT(ISNUMBER(H9))),"",IF(G9&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G9*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G9*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H9)))</x:f>
+        <x:v>145.2</x:v>
+      </x:c>
+      <x:c r="K9" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J9)),"",J9*IF(ISNUMBER(SEARCH("광역",$C9)),'범례'!$C$30,1))</x:f>
-        <x:v>150</x:v>
+        <x:v>145.2</x:v>
       </x:c>
       <x:c r="L9" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J9)),NOT(ISNUMBER(D9)),D9=0),"",J9/D9)</x:f>
-        <x:v>25</x:v>
+        <x:v>36.3</x:v>
       </x:c>
       <x:c r="M9" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K9)),NOT(ISNUMBER(D9)),D9=0),"",K9/D9)</x:f>
-        <x:v>25</x:v>
+        <x:v>36.3</x:v>
       </x:c>
       <x:c r="N9" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K9)),NOT(ISNUMBER(F9)),F9=0),"",K9/F9)</x:f>
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="O9" s="17"/>
-      <x:c r="P9" s="17"/>
-      <x:c r="Q9" s="24" t="s">
-        <x:v>97</x:v>
+        <x:v>181.49999999999997</x:v>
+      </x:c>
+      <x:c r="O9" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P9" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q9" s="24" t="str">
+        <x:v>시작 덱. 일반 시전</x:v>
       </x:c>
       <x:c r="R9" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C9,1)="딜",ISNUMBER(M9)),M9,"")</x:f>
-        <x:v>25</x:v>
+        <x:v>36.3</x:v>
       </x:c>
       <x:c r="S9" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C9,1)="딜",ISNUMBER(N9)),N9,"")</x:f>
-        <x:v>150</x:v>
+        <x:v>181.49999999999997</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0">
-      <x:c r="A10" s="11" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="B10" s="17" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>83</x:v>
+      <x:c r="A10" s="11" t="str">
+        <x:v>SK06</x:v>
+      </x:c>
+      <x:c r="B10" s="17" t="str">
+        <x:v>매직 스파크</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="str">
+        <x:v>딜/광역</x:v>
       </x:c>
       <x:c r="D10" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E10" s="17" t="n">
-        <x:v>0.8</x:v>
+        <x:v>2.2</x:v>
       </x:c>
       <x:c r="F10" s="22" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(E10)),"",MAX(E10,'범례'!$C$26))</x:f>
-        <x:v>0.8</x:v>
+        <x:v>2.2</x:v>
       </x:c>
       <x:c r="G10" s="17" t="n">
-        <x:v>110</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H10" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I10" s="19" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(G10)),"",G10*H10)</x:f>
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="J10" s="23" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(I10)),"",I10*(1-'범례'!$C$22)*'직업'!$E$5)</x:f>
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="K10" s="23" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G10)),NOT(ISNUMBER(H10))),"",G10*MAX(1,H10))</x:f>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J10" s="41" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G10)),NOT(ISNUMBER(H10))),"",IF(G10&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G10*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G10*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H10)))</x:f>
+        <x:v>43.6</x:v>
+      </x:c>
+      <x:c r="K10" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J10)),"",J10*IF(ISNUMBER(SEARCH("광역",$C10)),'범례'!$C$30,1))</x:f>
-        <x:v>110</x:v>
+        <x:v>98.10000000000001</x:v>
       </x:c>
       <x:c r="L10" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J10)),NOT(ISNUMBER(D10)),D10=0),"",J10/D10)</x:f>
-        <x:v>22</x:v>
+        <x:v>14.533333333333333</x:v>
       </x:c>
       <x:c r="M10" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K10)),NOT(ISNUMBER(D10)),D10=0),"",K10/D10)</x:f>
-        <x:v>22</x:v>
+        <x:v>32.7</x:v>
       </x:c>
       <x:c r="N10" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K10)),NOT(ISNUMBER(F10)),F10=0),"",K10/F10)</x:f>
-        <x:v>137.5</x:v>
-      </x:c>
-      <x:c r="O10" s="17"/>
-      <x:c r="P10" s="17"/>
-      <x:c r="Q10" s="24" t="s">
-        <x:v>100</x:v>
+        <x:v>44.59090909090909</x:v>
+      </x:c>
+      <x:c r="O10" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P10" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q10" s="24" t="str">
+        <x:v>시작 덱. 채널링 0.25초마다</x:v>
       </x:c>
       <x:c r="R10" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C10,1)="딜",ISNUMBER(M10)),M10,"")</x:f>
-        <x:v>22</x:v>
+        <x:v>32.7</x:v>
       </x:c>
       <x:c r="S10" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C10,1)="딜",ISNUMBER(N10)),N10,"")</x:f>
-        <x:v>137.5</x:v>
+        <x:v>44.59090909090909</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0">
-      <x:c r="A11" s="11" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="B11" s="17" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>83</x:v>
+      <x:c r="A11" s="11" t="str">
+        <x:v>SK07</x:v>
+      </x:c>
+      <x:c r="B11" s="17" t="str">
+        <x:v>매직 임팩트</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="str">
+        <x:v>딜/단일</x:v>
       </x:c>
       <x:c r="D11" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E11" s="17" t="n">
-        <x:v>0.6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F11" s="22" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(E11)),"",MAX(E11,'범례'!$C$26))</x:f>
-        <x:v>0.6</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="G11" s="17" t="n">
-        <x:v>150</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H11" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I11" s="19" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(G11)),"",G11*H11)</x:f>
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="J11" s="23" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(I11)),"",I11*(1-'범례'!$C$22)*'직업'!$E$5)</x:f>
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="K11" s="23" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G11)),NOT(ISNUMBER(H11))),"",G11*MAX(1,H11))</x:f>
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="J11" s="41" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G11)),NOT(ISNUMBER(H11))),"",IF(G11&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G11*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G11*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H11)))</x:f>
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="K11" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J11)),"",J11*IF(ISNUMBER(SEARCH("광역",$C11)),'범례'!$C$30,1))</x:f>
-        <x:v>150</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="L11" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J11)),NOT(ISNUMBER(D11)),D11=0),"",J11/D11)</x:f>
-        <x:v>30</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="M11" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K11)),NOT(ISNUMBER(D11)),D11=0),"",K11/D11)</x:f>
-        <x:v>30</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="N11" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K11)),NOT(ISNUMBER(F11)),F11=0),"",K11/F11)</x:f>
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="O11" s="17"/>
-      <x:c r="P11" s="17"/>
-      <x:c r="Q11" s="24" t="s">
-        <x:v>103</x:v>
+        <x:v>322.5</x:v>
+      </x:c>
+      <x:c r="O11" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P11" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q11" s="24" t="str">
+        <x:v>보상. 일반 시전</x:v>
       </x:c>
       <x:c r="R11" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C11,1)="딜",ISNUMBER(M11)),M11,"")</x:f>
-        <x:v>30</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="S11" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C11,1)="딜",ISNUMBER(N11)),N11,"")</x:f>
-        <x:v>250</x:v>
+        <x:v>322.5</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0">
-      <x:c r="A12" s="11" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="B12" s="17" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D12" s="17" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E12" s="17" t="n">
-        <x:v>1.2</x:v>
-      </x:c>
-      <x:c r="F12" s="22" t="n">
+      <x:c r="A12" s="11" t="str">
+        <x:v>SK08</x:v>
+      </x:c>
+      <x:c r="B12" s="17" t="str">
+        <x:v>저지먼트</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="str">
+        <x:v>딜/단일</x:v>
+      </x:c>
+      <x:c r="D12" s="17"/>
+      <x:c r="E12" s="17"/>
+      <x:c r="F12" s="22" t="str">
         <x:f aca="0">IF(NOT(ISNUMBER(E12)),"",MAX(E12,'범례'!$C$26))</x:f>
-        <x:v>1.2</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H12" s="17" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I12" s="19" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(G12)),"",G12*H12)</x:f>
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="J12" s="23" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(I12)),"",I12*(1-'범례'!$C$22)*'직업'!$E$5)</x:f>
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="K12" s="23" t="n">
+      </x:c>
+      <x:c r="G12" s="17"/>
+      <x:c r="H12" s="17"/>
+      <x:c r="I12" s="19" t="str">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"",G12*MAX(1,H12))</x:f>
+      </x:c>
+      <x:c r="J12" s="41" t="str">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"",IF(G12&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G12*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G12*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H12)))</x:f>
+      </x:c>
+      <x:c r="K12" s="41" t="str">
         <x:f aca="0">IF(NOT(ISNUMBER(J12)),"",J12*IF(ISNUMBER(SEARCH("광역",$C12)),'범례'!$C$30,1))</x:f>
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="L12" s="22" t="n">
+      </x:c>
+      <x:c r="L12" s="22" t="str">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J12)),NOT(ISNUMBER(D12)),D12=0),"",J12/D12)</x:f>
-        <x:v>25.714285714285715</x:v>
-      </x:c>
-      <x:c r="M12" s="22" t="n">
+      </x:c>
+      <x:c r="M12" s="22" t="str">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K12)),NOT(ISNUMBER(D12)),D12=0),"",K12/D12)</x:f>
-        <x:v>25.714285714285715</x:v>
-      </x:c>
-      <x:c r="N12" s="22" t="n">
+      </x:c>
+      <x:c r="N12" s="22" t="str">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K12)),NOT(ISNUMBER(F12)),F12=0),"",K12/F12)</x:f>
-        <x:v>150</x:v>
       </x:c>
       <x:c r="O12" s="17"/>
       <x:c r="P12" s="17"/>
-      <x:c r="Q12" s="24" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="R12" s="22" t="n">
+      <x:c r="Q12" s="24" t="str">
+        <x:v>미구현. 수치는 03 초안 참조</x:v>
+      </x:c>
+      <x:c r="R12" s="22" t="str">
         <x:f aca="0">IF(AND(LEFT($C12,1)="딜",ISNUMBER(M12)),M12,"")</x:f>
-        <x:v>25.714285714285715</x:v>
-      </x:c>
-      <x:c r="S12" s="22" t="n">
+      </x:c>
+      <x:c r="S12" s="22" t="str">
         <x:f aca="0">IF(AND(LEFT($C12,1)="딜",ISNUMBER(N12)),N12,"")</x:f>
-        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0">
-      <x:c r="A13" s="17"/>
-      <x:c r="B13" s="17"/>
-      <x:c r="C13" s="17"/>
+      <x:c r="A13" s="17" t="str">
+        <x:v>SK09</x:v>
+      </x:c>
+      <x:c r="B13" s="17" t="str">
+        <x:v>블리자드</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="str">
+        <x:v>딜/광역</x:v>
+      </x:c>
       <x:c r="D13" s="17"/>
       <x:c r="E13" s="17"/>
       <x:c r="F13" s="22" t="str">
@@ -6193,12 +4868,12 @@
       <x:c r="G13" s="17"/>
       <x:c r="H13" s="17"/>
       <x:c r="I13" s="19" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(G13)),"",G13*H13)</x:f>
-      </x:c>
-      <x:c r="J13" s="23" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(I13)),"",I13*(1-'범례'!$C$22)*'직업'!$E$5)</x:f>
-      </x:c>
-      <x:c r="K13" s="23" t="str">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"",G13*MAX(1,H13))</x:f>
+      </x:c>
+      <x:c r="J13" s="41" t="str">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"",IF(G13&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G13*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G13*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H13)))</x:f>
+      </x:c>
+      <x:c r="K13" s="41" t="str">
         <x:f aca="0">IF(NOT(ISNUMBER(J13)),"",J13*IF(ISNUMBER(SEARCH("광역",$C13)),'범례'!$C$30,1))</x:f>
       </x:c>
       <x:c r="L13" s="22" t="str">
@@ -6212,7 +4887,9 @@
       </x:c>
       <x:c r="O13" s="17"/>
       <x:c r="P13" s="17"/>
-      <x:c r="Q13" s="20"/>
+      <x:c r="Q13" s="20" t="str">
+        <x:v>미구현. 수치는 03 초안 참조</x:v>
+      </x:c>
       <x:c r="R13" s="22" t="str">
         <x:f aca="0">IF(AND(LEFT($C13,1)="딜",ISNUMBER(M13)),M13,"")</x:f>
       </x:c>
@@ -6221,76 +4898,132 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0">
-      <x:c r="A14" s="17"/>
-      <x:c r="B14" s="17"/>
-      <x:c r="C14" s="17"/>
-      <x:c r="D14" s="17"/>
-      <x:c r="E14" s="17"/>
-      <x:c r="F14" s="22" t="str">
+      <x:c r="A14" s="17" t="str">
+        <x:v>SK10</x:v>
+      </x:c>
+      <x:c r="B14" s="17" t="str">
+        <x:v>다크 이럽션</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="str">
+        <x:v>딜/광역</x:v>
+      </x:c>
+      <x:c r="D14" s="17" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F14" s="22" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(E14)),"",MAX(E14,'범례'!$C$26))</x:f>
-      </x:c>
-      <x:c r="G14" s="17"/>
-      <x:c r="H14" s="17"/>
-      <x:c r="I14" s="19" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(G14)),"",G14*H14)</x:f>
-      </x:c>
-      <x:c r="J14" s="23" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(I14)),"",I14*(1-'범례'!$C$22)*'직업'!$E$5)</x:f>
-      </x:c>
-      <x:c r="K14" s="23" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H14" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I14" s="19" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G14)),NOT(ISNUMBER(H14))),"",G14*MAX(1,H14))</x:f>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J14" s="41" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G14)),NOT(ISNUMBER(H14))),"",IF(G14&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G14*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G14*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H14)))</x:f>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K14" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J14)),"",J14*IF(ISNUMBER(SEARCH("광역",$C14)),'범례'!$C$30,1))</x:f>
-      </x:c>
-      <x:c r="L14" s="22" t="str">
+        <x:v>96.75</x:v>
+      </x:c>
+      <x:c r="L14" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J14)),NOT(ISNUMBER(D14)),D14=0),"",J14/D14)</x:f>
-      </x:c>
-      <x:c r="M14" s="22" t="str">
+        <x:v>21.5</x:v>
+      </x:c>
+      <x:c r="M14" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K14)),NOT(ISNUMBER(D14)),D14=0),"",K14/D14)</x:f>
-      </x:c>
-      <x:c r="N14" s="22" t="str">
+        <x:v>48.375</x:v>
+      </x:c>
+      <x:c r="N14" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K14)),NOT(ISNUMBER(F14)),F14=0),"",K14/F14)</x:f>
-      </x:c>
-      <x:c r="O14" s="17"/>
-      <x:c r="P14" s="17"/>
-      <x:c r="Q14" s="20"/>
-      <x:c r="R14" s="22" t="str">
+        <x:v>193.5</x:v>
+      </x:c>
+      <x:c r="O14" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P14" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q14" s="20" t="str">
+        <x:v>보상. 일반 시전</x:v>
+      </x:c>
+      <x:c r="R14" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C14,1)="딜",ISNUMBER(M14)),M14,"")</x:f>
-      </x:c>
-      <x:c r="S14" s="22" t="str">
+        <x:v>48.375</x:v>
+      </x:c>
+      <x:c r="S14" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C14,1)="딜",ISNUMBER(N14)),N14,"")</x:f>
+        <x:v>193.5</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0">
-      <x:c r="A15" s="17"/>
-      <x:c r="B15" s="17"/>
-      <x:c r="C15" s="17"/>
-      <x:c r="D15" s="17"/>
-      <x:c r="E15" s="17"/>
-      <x:c r="F15" s="22" t="str">
+      <x:c r="A15" s="17" t="str">
+        <x:v>SK11</x:v>
+      </x:c>
+      <x:c r="B15" s="17" t="str">
+        <x:v>침묵</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="str">
+        <x:v>차단</x:v>
+      </x:c>
+      <x:c r="D15" s="17" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="F15" s="22" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(E15)),"",MAX(E15,'범례'!$C$26))</x:f>
-      </x:c>
-      <x:c r="G15" s="17"/>
-      <x:c r="H15" s="17"/>
-      <x:c r="I15" s="19" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(G15)),"",G15*H15)</x:f>
-      </x:c>
-      <x:c r="J15" s="23" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(I15)),"",I15*(1-'범례'!$C$22)*'직업'!$E$5)</x:f>
-      </x:c>
-      <x:c r="K15" s="23" t="str">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I15" s="19" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G15)),NOT(ISNUMBER(H15))),"",G15*MAX(1,H15))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J15" s="41" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G15)),NOT(ISNUMBER(H15))),"",IF(G15&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G15*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G15*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H15)))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J15)),"",J15*IF(ISNUMBER(SEARCH("광역",$C15)),'범례'!$C$30,1))</x:f>
-      </x:c>
-      <x:c r="L15" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L15" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J15)),NOT(ISNUMBER(D15)),D15=0),"",J15/D15)</x:f>
-      </x:c>
-      <x:c r="M15" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K15)),NOT(ISNUMBER(D15)),D15=0),"",K15/D15)</x:f>
-      </x:c>
-      <x:c r="N15" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K15)),NOT(ISNUMBER(F15)),F15=0),"",K15/F15)</x:f>
-      </x:c>
-      <x:c r="O15" s="17"/>
-      <x:c r="P15" s="17"/>
-      <x:c r="Q15" s="20"/>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O15" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P15" s="17" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="Q15" s="20" t="str">
+        <x:v>시작 덱. 일반 시전, 캐스팅 중 대상만</x:v>
+      </x:c>
       <x:c r="R15" s="22" t="str">
         <x:f aca="0">IF(AND(LEFT($C15,1)="딜",ISNUMBER(M15)),M15,"")</x:f>
       </x:c>
@@ -6299,37 +5032,64 @@
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0">
-      <x:c r="A16" s="17"/>
-      <x:c r="B16" s="17"/>
-      <x:c r="C16" s="17"/>
-      <x:c r="D16" s="17"/>
-      <x:c r="E16" s="17"/>
-      <x:c r="F16" s="22" t="str">
+      <x:c r="A16" s="17" t="str">
+        <x:v>SK12</x:v>
+      </x:c>
+      <x:c r="B16" s="17" t="str">
+        <x:v>제압</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="str">
+        <x:v>차단</x:v>
+      </x:c>
+      <x:c r="D16" s="17" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="F16" s="22" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(E16)),"",MAX(E16,'범례'!$C$26))</x:f>
-      </x:c>
-      <x:c r="G16" s="17"/>
-      <x:c r="H16" s="17"/>
-      <x:c r="I16" s="19" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(G16)),"",G16*H16)</x:f>
-      </x:c>
-      <x:c r="J16" s="23" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(I16)),"",I16*(1-'범례'!$C$22)*'직업'!$E$5)</x:f>
-      </x:c>
-      <x:c r="K16" s="23" t="str">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H16" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I16" s="19" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G16)),NOT(ISNUMBER(H16))),"",G16*MAX(1,H16))</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J16" s="41" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G16)),NOT(ISNUMBER(H16))),"",IF(G16&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G16*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G16*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H16)))</x:f>
+        <x:v>32.25</x:v>
+      </x:c>
+      <x:c r="K16" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J16)),"",J16*IF(ISNUMBER(SEARCH("광역",$C16)),'범례'!$C$30,1))</x:f>
-      </x:c>
-      <x:c r="L16" s="22" t="str">
+        <x:v>32.25</x:v>
+      </x:c>
+      <x:c r="L16" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J16)),NOT(ISNUMBER(D16)),D16=0),"",J16/D16)</x:f>
-      </x:c>
-      <x:c r="M16" s="22" t="str">
+        <x:v>16.125</x:v>
+      </x:c>
+      <x:c r="M16" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K16)),NOT(ISNUMBER(D16)),D16=0),"",K16/D16)</x:f>
-      </x:c>
-      <x:c r="N16" s="22" t="str">
+        <x:v>16.125</x:v>
+      </x:c>
+      <x:c r="N16" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K16)),NOT(ISNUMBER(F16)),F16=0),"",K16/F16)</x:f>
-      </x:c>
-      <x:c r="O16" s="17"/>
-      <x:c r="P16" s="17"/>
-      <x:c r="Q16" s="20"/>
+        <x:v>80.625</x:v>
+      </x:c>
+      <x:c r="O16" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P16" s="17" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="Q16" s="20" t="str">
+        <x:v>보상. 일반 시전, 피해+차단</x:v>
+      </x:c>
       <x:c r="R16" s="22" t="str">
         <x:f aca="0">IF(AND(LEFT($C16,1)="딜",ISNUMBER(M16)),M16,"")</x:f>
       </x:c>
@@ -6338,37 +5098,64 @@
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0">
-      <x:c r="A17" s="17"/>
-      <x:c r="B17" s="17"/>
-      <x:c r="C17" s="17"/>
-      <x:c r="D17" s="17"/>
-      <x:c r="E17" s="17"/>
-      <x:c r="F17" s="22" t="str">
+      <x:c r="A17" s="17" t="str">
+        <x:v>SK13</x:v>
+      </x:c>
+      <x:c r="B17" s="17" t="str">
+        <x:v>매직아머</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="str">
+        <x:v>방어</x:v>
+      </x:c>
+      <x:c r="D17" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E17" s="17" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="F17" s="22" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(E17)),"",MAX(E17,'범례'!$C$26))</x:f>
-      </x:c>
-      <x:c r="G17" s="17"/>
-      <x:c r="H17" s="17"/>
-      <x:c r="I17" s="19" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(G17)),"",G17*H17)</x:f>
-      </x:c>
-      <x:c r="J17" s="23" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(I17)),"",I17*(1-'범례'!$C$22)*'직업'!$E$5)</x:f>
-      </x:c>
-      <x:c r="K17" s="23" t="str">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I17" s="19" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G17)),NOT(ISNUMBER(H17))),"",G17*MAX(1,H17))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="41" t="n">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G17)),NOT(ISNUMBER(H17))),"",IF(G17&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G17*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G17*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H17)))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K17" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J17)),"",J17*IF(ISNUMBER(SEARCH("광역",$C17)),'범례'!$C$30,1))</x:f>
-      </x:c>
-      <x:c r="L17" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J17)),NOT(ISNUMBER(D17)),D17=0),"",J17/D17)</x:f>
-      </x:c>
-      <x:c r="M17" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K17)),NOT(ISNUMBER(D17)),D17=0),"",K17/D17)</x:f>
-      </x:c>
-      <x:c r="N17" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N17" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K17)),NOT(ISNUMBER(F17)),F17=0),"",K17/F17)</x:f>
-      </x:c>
-      <x:c r="O17" s="17"/>
-      <x:c r="P17" s="17"/>
-      <x:c r="Q17" s="20"/>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O17" s="17" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="P17" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q17" s="20" t="str">
+        <x:v>시작 덱. 일반 시전</x:v>
+      </x:c>
       <x:c r="R17" s="22" t="str">
         <x:f aca="0">IF(AND(LEFT($C17,1)="딜",ISNUMBER(M17)),M17,"")</x:f>
       </x:c>
@@ -6377,9 +5164,15 @@
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0">
-      <x:c r="A18" s="17"/>
-      <x:c r="B18" s="17"/>
-      <x:c r="C18" s="17"/>
+      <x:c r="A18" s="17" t="str">
+        <x:v>SK14</x:v>
+      </x:c>
+      <x:c r="B18" s="17" t="str">
+        <x:v>생츄어리</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="str">
+        <x:v>방어</x:v>
+      </x:c>
       <x:c r="D18" s="17"/>
       <x:c r="E18" s="17"/>
       <x:c r="F18" s="22" t="str">
@@ -6388,12 +5181,12 @@
       <x:c r="G18" s="17"/>
       <x:c r="H18" s="17"/>
       <x:c r="I18" s="19" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(G18)),"",G18*H18)</x:f>
-      </x:c>
-      <x:c r="J18" s="23" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(I18)),"",I18*(1-'범례'!$C$22)*'직업'!$E$5)</x:f>
-      </x:c>
-      <x:c r="K18" s="23" t="str">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G18)),NOT(ISNUMBER(H18))),"",G18*MAX(1,H18))</x:f>
+      </x:c>
+      <x:c r="J18" s="41" t="str">
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G18)),NOT(ISNUMBER(H18))),"",IF(G18&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G18*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G18*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H18)))</x:f>
+      </x:c>
+      <x:c r="K18" s="41" t="str">
         <x:f aca="0">IF(NOT(ISNUMBER(J18)),"",J18*IF(ISNUMBER(SEARCH("광역",$C18)),'범례'!$C$30,1))</x:f>
       </x:c>
       <x:c r="L18" s="22" t="str">
@@ -6407,7 +5200,9 @@
       </x:c>
       <x:c r="O18" s="17"/>
       <x:c r="P18" s="17"/>
-      <x:c r="Q18" s="20"/>
+      <x:c r="Q18" s="20" t="str">
+        <x:v>미구현. 수치는 03 초안 참조</x:v>
+      </x:c>
       <x:c r="R18" s="22" t="str">
         <x:f aca="0">IF(AND(LEFT($C18,1)="딜",ISNUMBER(M18)),M18,"")</x:f>
       </x:c>
@@ -6416,81 +5211,81 @@
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0">
-      <x:c r="A22" s="3" t="s">
-        <x:v>107</x:v>
+      <x:c r="A22" s="3" t="str">
+        <x:v>구현 딜 카드 비교 (잡몹전 평균 적 수 기준)</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="29.850000381469727" hidden="0">
       <x:c r="A23" s="10" t="s">
-        <x:v>108</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B23" s="22" t="n">
         <x:f aca="0">IFERROR(MAX(R5:R18),"")</x:f>
-        <x:v>33.333333333333336</x:v>
+        <x:v>48.375</x:v>
       </x:c>
       <x:c r="C23" s="25" t="s">
-        <x:v>109</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="29.850000381469727" hidden="0">
       <x:c r="A24" s="10" t="s">
-        <x:v>110</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B24" s="22" t="n">
         <x:f aca="0">IFERROR(MIN(R5:R18),"")</x:f>
-        <x:v>22</x:v>
+        <x:v>30.234375</x:v>
       </x:c>
       <x:c r="C24" s="25"/>
     </x:row>
     <x:row r="25" ht="29.850000381469727" hidden="0">
       <x:c r="A25" s="10" t="s">
-        <x:v>111</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B25" s="19" t="n">
         <x:f aca="0">IFERROR(B23/B24,"")</x:f>
-        <x:v>1.5151515151515154</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="C25" s="25" t="s">
-        <x:v>112</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="29.850000381469727" hidden="0">
       <x:c r="A26" s="10" t="s">
-        <x:v>113</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B26" s="22" t="n">
         <x:f aca="0">IFERROR(MAX(S5:S18),"")</x:f>
-        <x:v>300</x:v>
+        <x:v>322.5</x:v>
       </x:c>
       <x:c r="C26" s="25" t="s">
-        <x:v>114</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="29.850000381469727" hidden="0">
       <x:c r="A27" s="10" t="s">
-        <x:v>115</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B27" s="22" t="n">
         <x:f aca="0">IFERROR(MIN(S5:S18),"")</x:f>
-        <x:v>137.5</x:v>
+        <x:v>44.59090909090909</x:v>
       </x:c>
       <x:c r="C27" s="25"/>
     </x:row>
     <x:row r="28" ht="29.850000381469727" hidden="0">
       <x:c r="A28" s="10" t="s">
-        <x:v>116</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B28" s="19" t="n">
         <x:f aca="0">IFERROR(B26/B27,"")</x:f>
-        <x:v>2.1818181818181817</x:v>
+        <x:v>7.232415902140672</x:v>
       </x:c>
       <x:c r="C28" s="25" t="s">
-        <x:v>112</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="29.850000381469727" hidden="0">
       <x:c r="A29" s="10" t="s">
-        <x:v>117</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B29" s="23" t="n">
         <x:f aca="0">COUNTIF(C5:C18,"딜/단일")</x:f>
@@ -6498,83 +5293,83 @@
       </x:c>
       <x:c r="C29" s="25" t="inlineStr">
         <x:is>
-          <x:t>목표 6</x:t>
+          <x:t xml:space="preserve">목표 6</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="30" ht="29.850000381469727" hidden="0">
       <x:c r="A30" s="10" t="s">
-        <x:v>119</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B30" s="23" t="n">
         <x:f aca="0">COUNTIF(C5:C18,"딜/광역")</x:f>
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C30" s="25" t="s">
-        <x:v>118</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="29.850000381469727" hidden="0">
       <x:c r="A31" s="10" t="s">
-        <x:v>120</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B31" s="23" t="n">
         <x:f aca="0">COUNTIF(C5:C18,"차단")</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C31" s="25" t="inlineStr">
         <x:is>
-          <x:t>목표 2</x:t>
+          <x:t xml:space="preserve">목표 2</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="32" ht="29.850000381469727" hidden="0">
       <x:c r="A32" s="10" t="s">
-        <x:v>122</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B32" s="23" t="n">
         <x:f aca="0">COUNTIF(C5:C18,"방어")</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C32" s="25" t="inlineStr">
         <x:is>
-          <x:t>목표 2</x:t>
+          <x:t xml:space="preserve">목표 2</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0">
-      <x:c r="A34" s="14" t="s">
-        <x:v>123</x:v>
+      <x:c r="A34" s="14" t="str">
+        <x:v>비율은 참고 지표. 시전 취소·대상 수·실제 사용 장면과 함께 판단.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="15" hidden="0">
-      <x:c r="A35" s="14" t="s">
-        <x:v>124</x:v>
+      <x:c r="A35" s="14" t="str">
+        <x:v>제압은 피해+차단의 승인 예외. 10 A23 참조.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="15" hidden="0">
       <x:c r="A37" s="3" t="s">
-        <x:v>125</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="128.35000610351562" hidden="0">
-      <x:c r="A38" s="25" t="s">
-        <x:v>126</x:v>
+      <x:c r="A38" s="25" t="str">
+        <x:v>단일/광역 기본 방향은 10 T11. 현재 카드별 예외는 A20·A23.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="166.39999389648438" hidden="0">
       <x:c r="A39" s="26" t="s">
-        <x:v>127</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="153.6999969482422" hidden="0">
       <x:c r="A40" s="25" t="s">
-        <x:v>128</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="164.14999389648438" hidden="0">
-      <x:c r="A41" s="25" t="s">
-        <x:v>129</x:v>
+      <x:c r="A41" s="25" t="str">
+        <x:v>광역 시전 시간은 현재 카드별 값을 따름. 채널링은 중단 시 남은 피해 미발생.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6600,35 +5395,35 @@
   <x:sheetData>
     <x:row r="1" ht="20.100000381469727" hidden="0">
       <x:c r="A1" s="15" t="s">
-        <x:v>130</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0">
       <x:c r="A2" s="21" t="s">
-        <x:v>131</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A4" s="8" t="s">
-        <x:v>132</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B4" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C4" s="8" t="s">
-        <x:v>64</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D4" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E4" s="8" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F4" s="8" t="s">
-        <x:v>133</x:v>
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F4" s="8" t="str">
+        <x:v>기대 피해(1체)</x:v>
       </x:c>
       <x:c r="G4" s="8" t="s">
-        <x:v>134</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H4" s="8" t="str">
         <x:v>앞 카드 코스트 합</x:v>
@@ -6640,18 +5435,18 @@
         <x:v>앞 카드 잠금 합(초)</x:v>
       </x:c>
       <x:c r="K4" s="8" t="s">
-        <x:v>135</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="L4" s="8" t="s">
-        <x:v>136</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0">
       <x:c r="A5" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="17" t="s">
-        <x:v>82</x:v>
+      <x:c r="B5" s="17" t="str">
+        <x:v>파이어볼</x:v>
       </x:c>
       <x:c r="C5" s="27" t="str">
         <x:f aca="0">IFERROR(INDEX('스킬'!$C:$C,MATCH($B5,'스킬'!$B:$B,0)),"")</x:f>
@@ -6659,15 +5454,15 @@
       </x:c>
       <x:c r="D5" s="23" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$D:$D,MATCH($B5,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E5" s="22" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$F:$F,MATCH($B5,'스킬'!$B:$B,0)),"")</x:f>
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="F5" s="23" t="n">
+      <x:c r="F5" s="41" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$J:$J,MATCH($B5,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>100</x:v>
+        <x:v>32.25</x:v>
       </x:c>
       <x:c r="G5" s="27" t="str">
         <x:f aca="0">IF($A5&lt;=4,"손패","대기열")</x:f>
@@ -6696,12 +5491,12 @@
       <x:c r="A6" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B6" s="17" t="s">
-        <x:v>86</x:v>
+      <x:c r="B6" s="17" t="str">
+        <x:v>파이어 필라</x:v>
       </x:c>
       <x:c r="C6" s="27" t="str">
         <x:f aca="0">IFERROR(INDEX('스킬'!$C:$C,MATCH($B6,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>딜/단일</x:v>
+        <x:v>딜/광역</x:v>
       </x:c>
       <x:c r="D6" s="23" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$D:$D,MATCH($B6,'스킬'!$B:$B,0)),"")</x:f>
@@ -6709,11 +5504,11 @@
       </x:c>
       <x:c r="E6" s="22" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$F:$F,MATCH($B6,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="F6" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F6" s="41" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$J:$J,MATCH($B6,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>120</x:v>
+        <x:v>53.75</x:v>
       </x:c>
       <x:c r="G6" s="27" t="str">
         <x:f aca="0">IF($A6&lt;=4,"손패","대기열")</x:f>
@@ -6742,22 +5537,22 @@
       <x:c r="A7" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B7" s="17" t="s">
-        <x:v>89</x:v>
+      <x:c r="B7" s="17" t="str">
+        <x:v>침묵</x:v>
       </x:c>
       <x:c r="C7" s="27" t="str">
         <x:f aca="0">IFERROR(INDEX('스킬'!$C:$C,MATCH($B7,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>방어</x:v>
+        <x:v>차단</x:v>
       </x:c>
       <x:c r="D7" s="23" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$D:$D,MATCH($B7,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E7" s="22" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$F:$F,MATCH($B7,'스킬'!$B:$B,0)),"")</x:f>
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="F7" s="23" t="n">
+      <x:c r="F7" s="41" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$J:$J,MATCH($B7,'스킬'!$B:$B,0)),"")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6790,22 +5585,22 @@
       <x:c r="A8" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B8" s="17" t="s">
-        <x:v>93</x:v>
+      <x:c r="B8" s="17" t="str">
+        <x:v>매직아머</x:v>
       </x:c>
       <x:c r="C8" s="27" t="str">
         <x:f aca="0">IFERROR(INDEX('스킬'!$C:$C,MATCH($B8,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>차단</x:v>
+        <x:v>방어</x:v>
       </x:c>
       <x:c r="D8" s="23" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$D:$D,MATCH($B8,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E8" s="22" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$F:$F,MATCH($B8,'스킬'!$B:$B,0)),"")</x:f>
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="F8" s="23" t="n">
+      <x:c r="F8" s="41" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$J:$J,MATCH($B8,'스킬'!$B:$B,0)),"")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6838,24 +5633,24 @@
       <x:c r="A9" s="27" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B9" s="17" t="s">
-        <x:v>96</x:v>
+      <x:c r="B9" s="17" t="str">
+        <x:v>매직 스파크</x:v>
       </x:c>
       <x:c r="C9" s="27" t="str">
         <x:f aca="0">IFERROR(INDEX('스킬'!$C:$C,MATCH($B9,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>딜/단일</x:v>
+        <x:v>딜/광역</x:v>
       </x:c>
       <x:c r="D9" s="23" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$D:$D,MATCH($B9,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E9" s="22" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$F:$F,MATCH($B9,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F9" s="23" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="F9" s="41" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$J:$J,MATCH($B9,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>150</x:v>
+        <x:v>43.6</x:v>
       </x:c>
       <x:c r="G9" s="27" t="str">
         <x:f aca="0">IF($A9&lt;=4,"손패","대기열")</x:f>
@@ -6863,11 +5658,11 @@
       </x:c>
       <x:c r="H9" s="23" t="n">
         <x:f aca="0">SUM(D5:D5)</x:f>
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I9" s="22" t="n">
         <x:f aca="0">IFERROR(H9/'범례'!$C$23,"")</x:f>
-        <x:v>3.75</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="J9" s="22" t="n">
         <x:f aca="0">SUM(E5:E5)</x:f>
@@ -6884,8 +5679,8 @@
       <x:c r="A10" s="27" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B10" s="17" t="s">
-        <x:v>99</x:v>
+      <x:c r="B10" s="17" t="str">
+        <x:v>라이트닝 스피어</x:v>
       </x:c>
       <x:c r="C10" s="27" t="str">
         <x:f aca="0">IFERROR(INDEX('스킬'!$C:$C,MATCH($B10,'스킬'!$B:$B,0)),"")</x:f>
@@ -6893,15 +5688,15 @@
       </x:c>
       <x:c r="D10" s="23" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$D:$D,MATCH($B10,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E10" s="22" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$F:$F,MATCH($B10,'스킬'!$B:$B,0)),"")</x:f>
         <x:v>0.8</x:v>
       </x:c>
-      <x:c r="F10" s="23" t="n">
+      <x:c r="F10" s="41" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$J:$J,MATCH($B10,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>110</x:v>
+        <x:v>145.2</x:v>
       </x:c>
       <x:c r="G10" s="27" t="str">
         <x:f aca="0">IF($A10&lt;=4,"손패","대기열")</x:f>
@@ -6909,15 +5704,15 @@
       </x:c>
       <x:c r="H10" s="23" t="n">
         <x:f aca="0">SUM(D5:D6)</x:f>
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I10" s="22" t="n">
         <x:f aca="0">IFERROR(H10/'범례'!$C$23,"")</x:f>
-        <x:v>8.75</x:v>
+        <x:v>6.25</x:v>
       </x:c>
       <x:c r="J10" s="22" t="n">
         <x:f aca="0">SUM(E5:E6)</x:f>
-        <x:v>0.8</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="K10" s="22" t="str">
         <x:f aca="0">IF(OR(C10="차단",C10="방어"),I10,"")</x:f>
@@ -6930,8 +5725,8 @@
       <x:c r="A11" s="27" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B11" s="17" t="s">
-        <x:v>102</x:v>
+      <x:c r="B11" s="17" t="str">
+        <x:v>매직 커터</x:v>
       </x:c>
       <x:c r="C11" s="27" t="str">
         <x:f aca="0">IFERROR(INDEX('스킬'!$C:$C,MATCH($B11,'스킬'!$B:$B,0)),"")</x:f>
@@ -6939,15 +5734,15 @@
       </x:c>
       <x:c r="D11" s="23" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$D:$D,MATCH($B11,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E11" s="22" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$F:$F,MATCH($B11,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>0.6</x:v>
-      </x:c>
-      <x:c r="F11" s="23" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="F11" s="41" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$J:$J,MATCH($B11,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>150</x:v>
+        <x:v>64.5</x:v>
       </x:c>
       <x:c r="G11" s="27" t="str">
         <x:f aca="0">IF($A11&lt;=4,"손패","대기열")</x:f>
@@ -6955,15 +5750,15 @@
       </x:c>
       <x:c r="H11" s="23" t="n">
         <x:f aca="0">SUM(D5:D7)</x:f>
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I11" s="22" t="n">
         <x:f aca="0">IFERROR(H11/'범례'!$C$23,"")</x:f>
-        <x:v>12.5</x:v>
+        <x:v>8.75</x:v>
       </x:c>
       <x:c r="J11" s="22" t="n">
         <x:f aca="0">SUM(E5:E7)</x:f>
-        <x:v>1.2000000000000002</x:v>
+        <x:v>1.7999999999999998</x:v>
       </x:c>
       <x:c r="K11" s="22" t="str">
         <x:f aca="0">IF(OR(C11="차단",C11="방어"),I11,"")</x:f>
@@ -6976,8 +5771,8 @@
       <x:c r="A12" s="27" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B12" s="17" t="s">
-        <x:v>105</x:v>
+      <x:c r="B12" s="17" t="str">
+        <x:v>아이스애로우</x:v>
       </x:c>
       <x:c r="C12" s="27" t="str">
         <x:f aca="0">IFERROR(INDEX('스킬'!$C:$C,MATCH($B12,'스킬'!$B:$B,0)),"")</x:f>
@@ -6985,15 +5780,15 @@
       </x:c>
       <x:c r="D12" s="23" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$D:$D,MATCH($B12,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E12" s="22" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$F:$F,MATCH($B12,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>1.2</x:v>
-      </x:c>
-      <x:c r="F12" s="23" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="F12" s="41" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$J:$J,MATCH($B12,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>180</x:v>
+        <x:v>188.5</x:v>
       </x:c>
       <x:c r="G12" s="27" t="str">
         <x:f aca="0">IF($A12&lt;=4,"손패","대기열")</x:f>
@@ -7001,15 +5796,15 @@
       </x:c>
       <x:c r="H12" s="23" t="n">
         <x:f aca="0">SUM(D5:D8)</x:f>
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I12" s="22" t="n">
         <x:f aca="0">IFERROR(H12/'범례'!$C$23,"")</x:f>
-        <x:v>15</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="J12" s="22" t="n">
         <x:f aca="0">SUM(E5:E8)</x:f>
-        <x:v>1.6</x:v>
+        <x:v>2.1999999999999997</x:v>
       </x:c>
       <x:c r="K12" s="22" t="str">
         <x:f aca="0">IF(OR(C12="차단",C12="방어"),I12,"")</x:f>
@@ -7020,16 +5815,16 @@
     </x:row>
     <x:row r="15" ht="15" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>137</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="30" hidden="0" customHeight="1">
       <x:c r="A16" s="10" t="s">
-        <x:v>138</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B16" s="23" t="n">
         <x:f aca="0">SUM(D5:D12)</x:f>
-        <x:v>35</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D16" s="38"/>
       <x:c r="E16" s="39"/>
@@ -7047,7 +5842,7 @@
       </x:c>
       <x:c r="B17" s="41" t="n">
         <x:f aca="0">IFERROR(B16/'범례'!$C$23,"")</x:f>
-        <x:v>43.75</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D17" s="38" t="str">
         <x:v>총 코스트/회복량. 실제 첫 순환은 10 참조</x:v>
@@ -7063,14 +5858,14 @@
     </x:row>
     <x:row r="18" ht="30" hidden="0" customHeight="1">
       <x:c r="A18" s="10" t="s">
-        <x:v>139</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B18" s="22" t="n">
         <x:f aca="0">SUM(E5:E12)</x:f>
-        <x:v>5.2</x:v>
+        <x:v>8.4</x:v>
       </x:c>
       <x:c r="D18" s="40" t="s">
-        <x:v>140</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E18" s="39"/>
       <x:c r="F18" s="39"/>
@@ -7082,12 +5877,12 @@
       <x:c r="L18" s="39"/>
     </x:row>
     <x:row r="19" ht="30" hidden="0" customHeight="1">
-      <x:c r="A19" s="10" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="B19" s="23" t="n">
+      <x:c r="A19" s="10" t="str">
+        <x:v>1체 기준 덱 총 기대 피해</x:v>
+      </x:c>
+      <x:c r="B19" s="41" t="n">
         <x:f aca="0">SUM(F5:F12)</x:f>
-        <x:v>810</x:v>
+        <x:v>527.8</x:v>
       </x:c>
       <x:c r="D19" s="38"/>
       <x:c r="E19" s="39"/>
@@ -7101,11 +5896,11 @@
     </x:row>
     <x:row r="20" ht="30" hidden="0" customHeight="1">
       <x:c r="A20" s="10" t="str">
-        <x:v>회복량 기준 평균 피해/초</x:v>
-      </x:c>
-      <x:c r="B20" s="22" t="n">
+        <x:v>1체 기준 회복량당 피해/초</x:v>
+      </x:c>
+      <x:c r="B20" s="41" t="n">
         <x:f aca="0">IFERROR(B19/B17,"")</x:f>
-        <x:v>18.514285714285716</x:v>
+        <x:v>17.59333333333333</x:v>
       </x:c>
       <x:c r="D20" s="38" t="str">
         <x:v>기절·초과피해·입력 순서 미포함; 실측 아님</x:v>
@@ -7121,14 +5916,14 @@
     </x:row>
     <x:row r="21" ht="30" hidden="0" customHeight="1">
       <x:c r="A21" s="10" t="s">
-        <x:v>142</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B21" s="19" t="n">
         <x:f aca="0">IFERROR('범례'!$C$27/B17,"")</x:f>
-        <x:v>1.0285714285714285</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="D21" s="38" t="s">
-        <x:v>143</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E21" s="39"/>
       <x:c r="F21" s="39"/>
@@ -7141,14 +5936,14 @@
     </x:row>
     <x:row r="22" ht="30" hidden="0" customHeight="1">
       <x:c r="A22" s="10" t="s">
-        <x:v>144</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B22" s="23" t="n">
         <x:f aca="0">COUNTIF(C5:C12,"차단")+COUNTIF(C5:C12,"방어")</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="D22" s="38" t="s">
-        <x:v>145</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E22" s="39"/>
       <x:c r="F22" s="39"/>
@@ -7201,7 +5996,7 @@
     </x:row>
     <x:row r="28" ht="15" hidden="0">
       <x:c r="A28" s="3" t="s">
-        <x:v>146</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="25" hidden="0" customHeight="1">
@@ -7254,7 +6049,7 @@
     </x:row>
     <x:row r="32" ht="25" hidden="0" customHeight="1">
       <x:c r="A32" s="38" t="str">
-        <x:v>예: 코스트 10에서 화염탄→서리화살 입력 0/0.4초. 6번 카드 진입 0.4초, 잠금 종료 0.8초.</x:v>
+        <x:v>예: 코스트 10에서 파이어볼→파이어 필라 입력 0/0.4초. 6번 카드 진입 0.4초, 잠금 종료 1.4초.</x:v>
       </x:c>
       <x:c r="B32" s="39"/>
       <x:c r="C32" s="39"/>
@@ -7270,7 +6065,7 @@
     </x:row>
     <x:row r="33" ht="25" hidden="0" customHeight="1">
       <x:c r="A33" s="38" t="str">
-        <x:v>코스트 0이면 위 두 입력에 8.75초 충전 필요. 손패 진입과 사용 가능 시점을 구분.</x:v>
+        <x:v>코스트 0에서 두 카드 비용 5를 모으는 데 6.25초. 손패 진입·다음 입력·효과 시점은 별도.</x:v>
       </x:c>
       <x:c r="B33" s="39"/>
       <x:c r="C33" s="39"/>
@@ -7286,7 +6081,7 @@
     </x:row>
     <x:row r="34" ht="25" hidden="0" customHeight="1">
       <x:c r="A34" s="38" t="s">
-        <x:v>147</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B34" s="39"/>
       <x:c r="C34" s="39"/>
@@ -7337,55 +6132,55 @@
   <x:sheetData>
     <x:row r="1" ht="16.149999618530273" hidden="0">
       <x:c r="A1" s="15" t="s">
-        <x:v>148</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0">
       <x:c r="A2" s="21" t="s">
-        <x:v>149</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="8" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B4" s="8" t="s">
-        <x:v>150</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C4" s="16" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D4" s="8" t="s">
-        <x:v>68</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E4" s="8" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F4" s="8" t="s">
-        <x:v>151</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G4" s="8" t="s">
-        <x:v>66</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H4" s="8" t="s">
-        <x:v>152</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I4" s="37" t="str">
         <x:v>회복량 기준 참고 시간</x:v>
       </x:c>
       <x:c r="J4" s="8" t="s">
-        <x:v>153</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0">
       <x:c r="A5" s="17" t="s">
-        <x:v>154</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B5" s="17" t="s">
-        <x:v>155</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C5" s="17" t="n">
-        <x:v>300</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D5" s="17" t="n">
         <x:v>30</x:v>
@@ -7407,21 +6202,21 @@
       </x:c>
       <x:c r="I5" s="22" t="n">
         <x:f aca="0">IFERROR(C5/'덱시뮬'!$B$20,"")</x:f>
-        <x:v>16.203703703703702</x:v>
-      </x:c>
-      <x:c r="J5" s="20" t="s">
-        <x:v>156</x:v>
+        <x:v>25.57787040545662</x:v>
+      </x:c>
+      <x:c r="J5" s="20" t="str">
+        <x:v>일반 공격. 필요하면 차단 가능</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0">
       <x:c r="A6" s="17" t="s">
-        <x:v>157</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B6" s="17" t="s">
-        <x:v>158</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C6" s="17" t="n">
-        <x:v>300</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D6" s="17" t="n">
         <x:v>40</x:v>
@@ -7437,25 +6232,25 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H6" s="17" t="s">
-        <x:v>159</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I6" s="22" t="n">
         <x:f aca="0">IFERROR(C6/'덱시뮬'!$B$20,"")</x:f>
-        <x:v>16.203703703703702</x:v>
+        <x:v>25.57787040545662</x:v>
       </x:c>
       <x:c r="J6" s="20" t="s">
-        <x:v>160</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0">
       <x:c r="A7" s="17" t="s">
-        <x:v>161</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B7" s="17" t="s">
-        <x:v>162</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C7" s="17" t="n">
-        <x:v>300</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D7" s="17" t="n">
         <x:v>150</x:v>
@@ -7471,14 +6266,14 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H7" s="17" t="s">
-        <x:v>163</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="I7" s="22" t="n">
         <x:f aca="0">IFERROR(C7/'덱시뮬'!$B$20,"")</x:f>
-        <x:v>16.203703703703702</x:v>
+        <x:v>28.419856006062908</x:v>
       </x:c>
       <x:c r="J7" s="20" t="s">
-        <x:v>164</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0">
@@ -7530,13 +6325,13 @@
       <x:c r="J10" s="20"/>
     </x:row>
     <x:row r="13" ht="15" hidden="0">
-      <x:c r="A13" s="28" t="s">
-        <x:v>165</x:v>
+      <x:c r="A13" s="28" t="str">
+        <x:v>A·B 450, C 500은 임시 HP. 원복은 각 300. 10 적 HP 시험 참조.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0">
-      <x:c r="A14" s="2" t="s">
-        <x:v>166</x:v>
+      <x:c r="A14" s="2" t="str">
+        <x:v>B·C도 초록 보유. 표는 주 공격만 기입. 초록도 차단 가능, 전체 패턴은 04 참조.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0">
@@ -7563,38 +6358,38 @@
   <x:sheetData>
     <x:row r="1" ht="20.100000381469727" hidden="0">
       <x:c r="A1" s="15" t="s">
-        <x:v>167</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0">
       <x:c r="A2" s="21" t="str">
-        <x:v>5전투 예상 피해를 모두 입력해야 합계·여유 계산. 현재 포션 미구현; 향후 런 기획용.</x:v>
+        <x:v>정식 5전투 계획용. 현재 시연 3전투와 구분. 피해 입력 전 합계·여유는 미확인.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A4" s="8" t="s">
-        <x:v>168</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B4" s="8" t="s">
-        <x:v>169</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C4" s="8" t="s">
-        <x:v>170</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D4" s="8" t="s">
-        <x:v>171</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E4" s="8" t="s">
-        <x:v>172</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F4" s="8" t="s">
-        <x:v>173</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G4" s="8" t="s">
-        <x:v>174</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="H4" s="8" t="s">
-        <x:v>175</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0">
@@ -7689,12 +6484,12 @@
     </x:row>
     <x:row r="12" ht="15" hidden="0">
       <x:c r="A12" s="3" t="s">
-        <x:v>137</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="30" hidden="0" customHeight="1">
       <x:c r="A13" s="10" t="s">
-        <x:v>176</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B13" s="23" t="str">
         <x:f aca="0">IF(COUNT(C5:C9)&lt;5,"",SUM(C5:C9))</x:f>
@@ -7707,7 +6502,7 @@
     </x:row>
     <x:row r="14" ht="30" hidden="0" customHeight="1">
       <x:c r="A14" s="10" t="s">
-        <x:v>177</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B14" s="23" t="str">
         <x:f aca="0">IF(COUNT(D5:D9)&lt;5,"",SUM(D5:D9))</x:f>
@@ -7720,14 +6515,14 @@
     </x:row>
     <x:row r="15" ht="30" hidden="0" customHeight="1">
       <x:c r="A15" s="10" t="s">
-        <x:v>178</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B15" s="23" t="n">
-        <x:f aca="0">IFERROR('직업'!$B$5*0.5*'범례'!$C$29,"")</x:f>
-        <x:v>750</x:v>
-      </x:c>
-      <x:c r="D15" s="38" t="s">
-        <x:v>179</x:v>
+        <x:f aca="0">IFERROR(INT('직업'!$B$5*0.3+0.5)*'범례'!$C$29,"")</x:f>
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="D15" s="38" t="str">
+        <x:v>포션 3개 × 최대 HP 30%. 패시브 제외</x:v>
       </x:c>
       <x:c r="E15" s="39"/>
       <x:c r="F15" s="39"/>
@@ -7736,14 +6531,14 @@
     </x:row>
     <x:row r="16" ht="30" hidden="0" customHeight="1">
       <x:c r="A16" s="10" t="s">
-        <x:v>180</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B16" s="23" t="n">
         <x:f aca="0">IFERROR('직업'!$B$5+B15,"")</x:f>
-        <x:v>1250</x:v>
+        <x:v>950</x:v>
       </x:c>
       <x:c r="D16" s="38" t="str">
-        <x:v>포션 초과 회복 손실이 없다는 이론 상한</x:v>
+        <x:v>기본 HP+포션. 초과 회복 손실 없는 이론 상한</x:v>
       </x:c>
       <x:c r="E16" s="39"/>
       <x:c r="F16" s="39"/>
@@ -7752,13 +6547,13 @@
     </x:row>
     <x:row r="17" ht="30" hidden="0" customHeight="1">
       <x:c r="A17" s="10" t="s">
-        <x:v>181</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B17" s="23" t="str">
         <x:f aca="0">IF(NOT(ISNUMBER(B13)),"",B16-B13)</x:f>
       </x:c>
       <x:c r="D17" s="38" t="s">
-        <x:v>182</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E17" s="39"/>
       <x:c r="F17" s="39"/>
@@ -7767,13 +6562,13 @@
     </x:row>
     <x:row r="18" ht="30" hidden="0" customHeight="1">
       <x:c r="A18" s="10" t="s">
-        <x:v>183</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B18" s="23" t="str">
         <x:f aca="0">IF(NOT(ISNUMBER(B14)),"",B16-B14)</x:f>
       </x:c>
       <x:c r="D18" s="38" t="s">
-        <x:v>184</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E18" s="39"/>
       <x:c r="F18" s="39"/>
@@ -7782,13 +6577,13 @@
     </x:row>
     <x:row r="19" ht="30" hidden="0" customHeight="1">
       <x:c r="A19" s="10" t="s">
-        <x:v>185</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B19" s="23" t="str">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(B13)),NOT(ISNUMBER(B14))),"",B14-B13)</x:f>
       </x:c>
       <x:c r="D19" s="38" t="s">
-        <x:v>186</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E19" s="39"/>
       <x:c r="F19" s="39"/>
@@ -7797,7 +6592,7 @@
     </x:row>
     <x:row r="22" ht="15" hidden="0">
       <x:c r="A22" s="3" t="s">
-        <x:v>187</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="25" hidden="0" customHeight="1">
@@ -7814,7 +6609,7 @@
     </x:row>
     <x:row r="24" ht="25" hidden="0" customHeight="1">
       <x:c r="A24" s="40" t="s">
-        <x:v>188</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B24" s="39"/>
       <x:c r="C24" s="39"/>
@@ -7826,7 +6621,7 @@
     </x:row>
     <x:row r="25" ht="25" hidden="0" customHeight="1">
       <x:c r="A25" s="40" t="s">
-        <x:v>189</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B25" s="39"/>
       <x:c r="C25" s="39"/>
@@ -7867,38 +6662,38 @@
   <x:sheetData>
     <x:row r="1" ht="16.149999618530273" hidden="0">
       <x:c r="A1" s="15" t="s">
-        <x:v>190</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0">
       <x:c r="A2" s="21" t="s">
-        <x:v>191</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A4" s="8" t="s">
-        <x:v>192</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B4" s="8" t="s">
-        <x:v>169</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C4" s="8" t="s">
-        <x:v>193</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D4" s="8" t="s">
-        <x:v>194</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E4" s="8" t="s">
-        <x:v>195</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="F4" s="8" t="s">
-        <x:v>196</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G4" s="8" t="s">
-        <x:v>197</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H4" s="8" t="s">
-        <x:v>198</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0">
@@ -7906,7 +6701,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="30" t="s">
-        <x:v>199</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C5" s="29" t="n">
         <x:v>40</x:v>
@@ -7923,10 +6718,10 @@
         <x:v>0.45</x:v>
       </x:c>
       <x:c r="G5" s="33" t="s">
-        <x:v>200</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H5" s="33" t="s">
-        <x:v>201</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0">
@@ -8015,19 +6810,19 @@
     </x:row>
     <x:row r="14" ht="39.54999923706055" hidden="0">
       <x:c r="A14" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C14" s="27" t="n">
         <x:f aca="0">IFERROR(SUM(C6:C11),"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E14" s="25" t="s">
-        <x:v>203</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>204</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C15" s="27" t="n">
         <x:f aca="0">IFERROR(SUM(D6:D11),"")</x:f>

--- a/Docs/밸런스시트.xlsx
+++ b/Docs/밸런스시트.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범례" sheetId="1" r:id="R5d69d4cccbff4223"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직업" sheetId="2" r:id="Rf18344cfc67c4f76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="스킬" sheetId="3" r:id="Rc906251a3d3e47f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="덱시뮬" sheetId="4" r:id="R8a8a9ba6881045d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="적" sheetId="5" r:id="R129acdc605d54390"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HP예산" sheetId="6" r:id="Re96747d556624d08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인카운터" sheetId="7" r:id="R105d4fd406f24aff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범례" sheetId="1" r:id="R888d575dab3d42f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직업" sheetId="2" r:id="Rfeebacd51dab4c5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="스킬" sheetId="3" r:id="R731f5bed22634e2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="덱시뮬" sheetId="4" r:id="Raf582e8328524313"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="적" sheetId="5" r:id="Ra49b0f18f5084e2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HP예산" sheetId="6" r:id="R40db24864e644129"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인카운터" sheetId="7" r:id="Rc3f4d1a56d47446a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -744,42 +744,6 @@
         <x:family val="2"/>
       </x:rPr>
       <x:t xml:space="preserve">보스</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">포션 횟수 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">런 전체</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -4098,22 +4062,22 @@
       </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0">
-      <x:c r="A29" s="9" t="s">
-        <x:v>43</x:v>
+      <x:c r="A29" s="9" t="str">
+        <x:v>기본 포션 횟수</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
         <x:v>최대 HP의 30%씩 회복</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D29" s="10" t="str">
-        <x:v>10 A8·A28. 시작 3개, 보충 없음</x:v>
+        <x:v>10 A8·A28. 시작 1개, PS01 최대치·현재 +1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0">
       <x:c r="A30" s="9" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
         <x:v>정식 런 계획의 광역 피해 참고값</x:v>
@@ -4153,7 +4117,7 @@
   <x:sheetData>
     <x:row r="1" ht="16.149999618530273" hidden="0">
       <x:c r="A1" s="15" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0">
@@ -4163,27 +4127,27 @@
     </x:row>
     <x:row r="4" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A4" s="8" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B4" s="16" t="s">
+      <x:c r="C4" s="8" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="D4" s="8" t="str">
         <x:v>적용 크리율</x:v>
       </x:c>
       <x:c r="E4" s="8" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F4" s="8" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="F4" s="8" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="17" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B5" s="17" t="n">
         <x:v>500</x:v>
@@ -4224,7 +4188,7 @@
     </x:row>
     <x:row r="9" ht="15" hidden="0">
       <x:c r="A9" s="21" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0">
@@ -4260,7 +4224,7 @@
   <x:sheetData>
     <x:row r="1" ht="20.100000381469727" hidden="0">
       <x:c r="A1" s="15" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0">
@@ -4270,61 +4234,61 @@
     </x:row>
     <x:row r="4" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A4" s="16" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="s">
+      <x:c r="C4" s="8" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="C4" s="8" t="s">
+      <x:c r="D4" s="8" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="D4" s="8" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="E4" s="8" t="str">
         <x:v>시전/채널(초)</x:v>
       </x:c>
       <x:c r="F4" s="8" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G4" s="8" t="str">
         <x:v>1타 피해</x:v>
       </x:c>
       <x:c r="H4" s="8" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I4" s="8" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="I4" s="8" t="s">
+      <x:c r="J4" s="8" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="J4" s="8" t="s">
+      <x:c r="K4" s="8" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="K4" s="8" t="s">
+      <x:c r="L4" s="8" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="L4" s="8" t="s">
+      <x:c r="M4" s="8" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="M4" s="8" t="s">
+      <x:c r="N4" s="8" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="N4" s="8" t="s">
+      <x:c r="O4" s="8" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="O4" s="8" t="s">
+      <x:c r="P4" s="8" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="P4" s="8" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="Q4" s="8" t="str">
         <x:v>구현·발동 방식</x:v>
       </x:c>
       <x:c r="R4" s="8" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="S4" s="8" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="S4" s="8" t="s">
-        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0">
@@ -5217,19 +5181,19 @@
     </x:row>
     <x:row r="23" ht="29.850000381469727" hidden="0">
       <x:c r="A23" s="10" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B23" s="22" t="n">
         <x:f aca="0">IFERROR(MAX(R5:R18),"")</x:f>
         <x:v>48.375</x:v>
       </x:c>
       <x:c r="C23" s="25" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="29.850000381469727" hidden="0">
       <x:c r="A24" s="10" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B24" s="22" t="n">
         <x:f aca="0">IFERROR(MIN(R5:R18),"")</x:f>
@@ -5239,31 +5203,31 @@
     </x:row>
     <x:row r="25" ht="29.850000381469727" hidden="0">
       <x:c r="A25" s="10" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B25" s="19" t="n">
         <x:f aca="0">IFERROR(B23/B24,"")</x:f>
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="C25" s="25" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="29.850000381469727" hidden="0">
       <x:c r="A26" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B26" s="22" t="n">
         <x:f aca="0">IFERROR(MAX(S5:S18),"")</x:f>
         <x:v>322.5</x:v>
       </x:c>
       <x:c r="C26" s="25" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="29.850000381469727" hidden="0">
       <x:c r="A27" s="10" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B27" s="22" t="n">
         <x:f aca="0">IFERROR(MIN(S5:S18),"")</x:f>
@@ -5273,19 +5237,19 @@
     </x:row>
     <x:row r="28" ht="29.850000381469727" hidden="0">
       <x:c r="A28" s="10" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B28" s="19" t="n">
         <x:f aca="0">IFERROR(B26/B27,"")</x:f>
         <x:v>7.232415902140672</x:v>
       </x:c>
       <x:c r="C28" s="25" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="29.850000381469727" hidden="0">
       <x:c r="A29" s="10" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B29" s="23" t="n">
         <x:f aca="0">COUNTIF(C5:C18,"딜/단일")</x:f>
@@ -5299,19 +5263,19 @@
     </x:row>
     <x:row r="30" ht="29.850000381469727" hidden="0">
       <x:c r="A30" s="10" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B30" s="23" t="n">
         <x:f aca="0">COUNTIF(C5:C18,"딜/광역")</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="C30" s="25" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="29.850000381469727" hidden="0">
       <x:c r="A31" s="10" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B31" s="23" t="n">
         <x:f aca="0">COUNTIF(C5:C18,"차단")</x:f>
@@ -5325,7 +5289,7 @@
     </x:row>
     <x:row r="32" ht="29.850000381469727" hidden="0">
       <x:c r="A32" s="10" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B32" s="23" t="n">
         <x:f aca="0">COUNTIF(C5:C18,"방어")</x:f>
@@ -5349,7 +5313,7 @@
     </x:row>
     <x:row r="37" ht="15" hidden="0">
       <x:c r="A37" s="3" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="128.35000610351562" hidden="0">
@@ -5359,12 +5323,12 @@
     </x:row>
     <x:row r="39" ht="166.39999389648438" hidden="0">
       <x:c r="A39" s="26" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="153.6999969482422" hidden="0">
       <x:c r="A40" s="25" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="164.14999389648438" hidden="0">
@@ -5395,35 +5359,35 @@
   <x:sheetData>
     <x:row r="1" ht="20.100000381469727" hidden="0">
       <x:c r="A1" s="15" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0">
       <x:c r="A2" s="21" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A4" s="8" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B4" s="8" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="C4" s="8" t="s">
+      <x:c r="D4" s="8" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="s">
+      <x:c r="E4" s="8" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="E4" s="8" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="F4" s="8" t="str">
         <x:v>기대 피해(1체)</x:v>
       </x:c>
       <x:c r="G4" s="8" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H4" s="8" t="str">
         <x:v>앞 카드 코스트 합</x:v>
@@ -5435,10 +5399,10 @@
         <x:v>앞 카드 잠금 합(초)</x:v>
       </x:c>
       <x:c r="K4" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="L4" s="8" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="L4" s="8" t="s">
-        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0">
@@ -5815,12 +5779,12 @@
     </x:row>
     <x:row r="15" ht="15" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="30" hidden="0" customHeight="1">
       <x:c r="A16" s="10" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B16" s="23" t="n">
         <x:f aca="0">SUM(D5:D12)</x:f>
@@ -5858,14 +5822,14 @@
     </x:row>
     <x:row r="18" ht="30" hidden="0" customHeight="1">
       <x:c r="A18" s="10" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B18" s="22" t="n">
         <x:f aca="0">SUM(E5:E12)</x:f>
         <x:v>8.4</x:v>
       </x:c>
       <x:c r="D18" s="40" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E18" s="39"/>
       <x:c r="F18" s="39"/>
@@ -5916,14 +5880,14 @@
     </x:row>
     <x:row r="21" ht="30" hidden="0" customHeight="1">
       <x:c r="A21" s="10" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B21" s="19" t="n">
         <x:f aca="0">IFERROR('범례'!$C$27/B17,"")</x:f>
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="D21" s="38" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E21" s="39"/>
       <x:c r="F21" s="39"/>
@@ -5936,14 +5900,14 @@
     </x:row>
     <x:row r="22" ht="30" hidden="0" customHeight="1">
       <x:c r="A22" s="10" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B22" s="23" t="n">
         <x:f aca="0">COUNTIF(C5:C12,"차단")+COUNTIF(C5:C12,"방어")</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="D22" s="38" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E22" s="39"/>
       <x:c r="F22" s="39"/>
@@ -5996,7 +5960,7 @@
     </x:row>
     <x:row r="28" ht="15" hidden="0">
       <x:c r="A28" s="3" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="25" hidden="0" customHeight="1">
@@ -6081,7 +6045,7 @@
     </x:row>
     <x:row r="34" ht="25" hidden="0" customHeight="1">
       <x:c r="A34" s="38" t="s">
-        <x:v>102</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B34" s="39"/>
       <x:c r="C34" s="39"/>
@@ -6132,52 +6096,52 @@
   <x:sheetData>
     <x:row r="1" ht="16.149999618530273" hidden="0">
       <x:c r="A1" s="15" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0">
       <x:c r="A2" s="21" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="8" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="s">
+      <x:c r="D4" s="8" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C4" s="16" t="s">
+      <x:c r="E4" s="8" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="s">
+      <x:c r="F4" s="8" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F4" s="8" t="s">
+      <x:c r="G4" s="8" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G4" s="8" t="s">
+      <x:c r="H4" s="8" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="H4" s="8" t="s">
-        <x:v>109</x:v>
       </x:c>
       <x:c r="I4" s="37" t="str">
         <x:v>회복량 기준 참고 시간</x:v>
       </x:c>
       <x:c r="J4" s="8" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0">
       <x:c r="A5" s="17" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B5" s="17" t="s">
         <x:v>111</x:v>
-      </x:c>
-      <x:c r="B5" s="17" t="s">
-        <x:v>112</x:v>
       </x:c>
       <x:c r="C5" s="17" t="n">
         <x:v>450</x:v>
@@ -6210,10 +6174,10 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0">
       <x:c r="A6" s="17" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B6" s="17" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="B6" s="17" t="s">
-        <x:v>114</x:v>
       </x:c>
       <x:c r="C6" s="17" t="n">
         <x:v>450</x:v>
@@ -6232,22 +6196,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H6" s="17" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="I6" s="22" t="n">
         <x:f aca="0">IFERROR(C6/'덱시뮬'!$B$20,"")</x:f>
         <x:v>25.57787040545662</x:v>
       </x:c>
       <x:c r="J6" s="20" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0">
       <x:c r="A7" s="17" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B7" s="17" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="B7" s="17" t="s">
-        <x:v>118</x:v>
       </x:c>
       <x:c r="C7" s="17" t="n">
         <x:v>500</x:v>
@@ -6266,14 +6230,14 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H7" s="17" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I7" s="22" t="n">
         <x:f aca="0">IFERROR(C7/'덱시뮬'!$B$20,"")</x:f>
         <x:v>28.419856006062908</x:v>
       </x:c>
       <x:c r="J7" s="20" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0">
@@ -6358,7 +6322,7 @@
   <x:sheetData>
     <x:row r="1" ht="20.100000381469727" hidden="0">
       <x:c r="A1" s="15" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0">
@@ -6368,28 +6332,28 @@
     </x:row>
     <x:row r="4" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A4" s="8" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="s">
+      <x:c r="C4" s="8" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="C4" s="8" t="s">
+      <x:c r="D4" s="8" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="s">
+      <x:c r="E4" s="8" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="s">
+      <x:c r="F4" s="8" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="F4" s="8" t="s">
+      <x:c r="G4" s="8" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="G4" s="8" t="s">
+      <x:c r="H4" s="8" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="H4" s="8" t="s">
-        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0">
@@ -6484,12 +6448,12 @@
     </x:row>
     <x:row r="12" ht="15" hidden="0">
       <x:c r="A12" s="3" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="30" hidden="0" customHeight="1">
       <x:c r="A13" s="10" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B13" s="23" t="str">
         <x:f aca="0">IF(COUNT(C5:C9)&lt;5,"",SUM(C5:C9))</x:f>
@@ -6502,7 +6466,7 @@
     </x:row>
     <x:row r="14" ht="30" hidden="0" customHeight="1">
       <x:c r="A14" s="10" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B14" s="23" t="str">
         <x:f aca="0">IF(COUNT(D5:D9)&lt;5,"",SUM(D5:D9))</x:f>
@@ -6515,14 +6479,14 @@
     </x:row>
     <x:row r="15" ht="30" hidden="0" customHeight="1">
       <x:c r="A15" s="10" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B15" s="23" t="n">
         <x:f aca="0">IFERROR(INT('직업'!$B$5*0.3+0.5)*'범례'!$C$29,"")</x:f>
-        <x:v>450</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D15" s="38" t="str">
-        <x:v>포션 3개 × 최대 HP 30%. 패시브 제외</x:v>
+        <x:v>기본 포션 1개 × 최대 HP 30%. PS01 제외</x:v>
       </x:c>
       <x:c r="E15" s="39"/>
       <x:c r="F15" s="39"/>
@@ -6531,11 +6495,11 @@
     </x:row>
     <x:row r="16" ht="30" hidden="0" customHeight="1">
       <x:c r="A16" s="10" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B16" s="23" t="n">
         <x:f aca="0">IFERROR('직업'!$B$5+B15,"")</x:f>
-        <x:v>950</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="D16" s="38" t="str">
         <x:v>기본 HP+포션. 초과 회복 손실 없는 이론 상한</x:v>
@@ -6547,13 +6511,13 @@
     </x:row>
     <x:row r="17" ht="30" hidden="0" customHeight="1">
       <x:c r="A17" s="10" t="s">
-        <x:v>134</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B17" s="23" t="str">
         <x:f aca="0">IF(NOT(ISNUMBER(B13)),"",B16-B13)</x:f>
       </x:c>
       <x:c r="D17" s="38" t="s">
-        <x:v>135</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E17" s="39"/>
       <x:c r="F17" s="39"/>
@@ -6562,13 +6526,13 @@
     </x:row>
     <x:row r="18" ht="30" hidden="0" customHeight="1">
       <x:c r="A18" s="10" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B18" s="23" t="str">
         <x:f aca="0">IF(NOT(ISNUMBER(B14)),"",B16-B14)</x:f>
       </x:c>
       <x:c r="D18" s="38" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E18" s="39"/>
       <x:c r="F18" s="39"/>
@@ -6577,13 +6541,13 @@
     </x:row>
     <x:row r="19" ht="30" hidden="0" customHeight="1">
       <x:c r="A19" s="10" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B19" s="23" t="str">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(B13)),NOT(ISNUMBER(B14))),"",B14-B13)</x:f>
       </x:c>
       <x:c r="D19" s="38" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E19" s="39"/>
       <x:c r="F19" s="39"/>
@@ -6592,7 +6556,7 @@
     </x:row>
     <x:row r="22" ht="15" hidden="0">
       <x:c r="A22" s="3" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="25" hidden="0" customHeight="1">
@@ -6609,7 +6573,7 @@
     </x:row>
     <x:row r="24" ht="25" hidden="0" customHeight="1">
       <x:c r="A24" s="40" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B24" s="39"/>
       <x:c r="C24" s="39"/>
@@ -6621,7 +6585,7 @@
     </x:row>
     <x:row r="25" ht="25" hidden="0" customHeight="1">
       <x:c r="A25" s="40" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B25" s="39"/>
       <x:c r="C25" s="39"/>
@@ -6662,38 +6626,38 @@
   <x:sheetData>
     <x:row r="1" ht="16.149999618530273" hidden="0">
       <x:c r="A1" s="15" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0">
       <x:c r="A2" s="21" t="s">
-        <x:v>144</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A4" s="8" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="s">
+      <x:c r="D4" s="8" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="s">
+      <x:c r="E4" s="8" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="s">
+      <x:c r="F4" s="8" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="F4" s="8" t="s">
+      <x:c r="G4" s="8" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="G4" s="8" t="s">
+      <x:c r="H4" s="8" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="H4" s="8" t="s">
-        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0">
@@ -6701,7 +6665,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="30" t="s">
-        <x:v>152</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C5" s="29" t="n">
         <x:v>40</x:v>
@@ -6718,10 +6682,10 @@
         <x:v>0.45</x:v>
       </x:c>
       <x:c r="G5" s="33" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H5" s="33" t="s">
         <x:v>153</x:v>
-      </x:c>
-      <x:c r="H5" s="33" t="s">
-        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0">
@@ -6810,19 +6774,19 @@
     </x:row>
     <x:row r="14" ht="39.54999923706055" hidden="0">
       <x:c r="A14" s="3" t="s">
-        <x:v>155</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C14" s="27" t="n">
         <x:f aca="0">IFERROR(SUM(C6:C11),"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E14" s="25" t="s">
-        <x:v>156</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C15" s="27" t="n">
         <x:f aca="0">IFERROR(SUM(D6:D11),"")</x:f>

--- a/Docs/밸런스시트.xlsx
+++ b/Docs/밸런스시트.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범례" sheetId="1" r:id="R888d575dab3d42f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직업" sheetId="2" r:id="Rfeebacd51dab4c5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="스킬" sheetId="3" r:id="R731f5bed22634e2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="덱시뮬" sheetId="4" r:id="Raf582e8328524313"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="적" sheetId="5" r:id="Ra49b0f18f5084e2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HP예산" sheetId="6" r:id="R40db24864e644129"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인카운터" sheetId="7" r:id="Rc3f4d1a56d47446a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범례" sheetId="1" r:id="R89ff24ec21f642a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직업" sheetId="2" r:id="Reb75669ae9374e1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="스킬" sheetId="3" r:id="R61212b5ddc65493a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="덱시뮬" sheetId="4" r:id="R45e6d679c58d4ff1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="적" sheetId="5" r:id="R3caf11fee9ff4174"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HP예산" sheetId="6" r:id="Rb970658e670b4919"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인카운터" sheetId="7" r:id="R48b7006a0c914ba3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3876,7 +3876,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B11" s="6" t="str">
-        <x:v>구현 스킬 11종 계산. 미구현 3종은 03 초안 참조</x:v>
+        <x:v>구현 스킬 14종 계산. 10 A20·A23·A29</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="29.850000381469727" hidden="0">
@@ -3892,7 +3892,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B13" s="6" t="str">
-        <x:v>현재 A·B·C. 주 공격 기준, 전체 패턴은 04 참조</x:v>
+        <x:v>A·B·C·D 데이터. 전체 패턴·편성은 04 참조</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0">
@@ -4096,7 +4096,7 @@
     </x:row>
     <x:row r="32" ht="15" hidden="0">
       <x:c r="A32" s="14" t="str">
-        <x:v>2026-09-23: 현재 스킬·치명타·포션·HP 시험값 반영. 이전 파일은 보관/2026-09-23_정정전.</x:v>
+        <x:v>2026-09-28: 신규 3종·적 HP 반영. 원본 10 A29·A30.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4229,7 +4229,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0">
       <x:c r="A2" s="2" t="str">
-        <x:v>현재 구현 11종, 미구현 3종 수치는 비움. 10 A20·A23·A25 기준, 패시브·과잉 피해·시전 취소 제외.</x:v>
+        <x:v>현재 구현 14종. 10 A20·A23·A25·A29 기준, 패시브·과잉 피해·시전 취소 제외.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="31.5" hidden="0" customHeight="1">
@@ -4777,41 +4777,62 @@
       <x:c r="C12" s="17" t="str">
         <x:v>딜/단일</x:v>
       </x:c>
-      <x:c r="D12" s="17"/>
-      <x:c r="E12" s="17"/>
-      <x:c r="F12" s="22" t="str">
+      <x:c r="D12" s="17" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="n">
+        <x:v>2.75</x:v>
+      </x:c>
+      <x:c r="F12" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(E12)),"",MAX(E12,'범례'!$C$26))</x:f>
-      </x:c>
-      <x:c r="G12" s="17"/>
-      <x:c r="H12" s="17"/>
-      <x:c r="I12" s="19" t="str">
+        <x:v>2.75</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="n">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="H12" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I12" s="19" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"",G12*MAX(1,H12))</x:f>
-      </x:c>
-      <x:c r="J12" s="41" t="str">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="J12" s="41" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"",IF(G12&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G12*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G12*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H12)))</x:f>
-      </x:c>
-      <x:c r="K12" s="41" t="str">
+        <x:v>392.45</x:v>
+      </x:c>
+      <x:c r="K12" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J12)),"",J12*IF(ISNUMBER(SEARCH("광역",$C12)),'범례'!$C$30,1))</x:f>
-      </x:c>
-      <x:c r="L12" s="22" t="str">
+        <x:v>392.45</x:v>
+      </x:c>
+      <x:c r="L12" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J12)),NOT(ISNUMBER(D12)),D12=0),"",J12/D12)</x:f>
-      </x:c>
-      <x:c r="M12" s="22" t="str">
+        <x:v>65.40833333333333</x:v>
+      </x:c>
+      <x:c r="M12" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K12)),NOT(ISNUMBER(D12)),D12=0),"",K12/D12)</x:f>
-      </x:c>
-      <x:c r="N12" s="22" t="str">
+        <x:v>65.40833333333333</x:v>
+      </x:c>
+      <x:c r="N12" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K12)),NOT(ISNUMBER(F12)),F12=0),"",K12/F12)</x:f>
-      </x:c>
-      <x:c r="O12" s="17"/>
-      <x:c r="P12" s="17"/>
+        <x:v>142.70909090909092</x:v>
+      </x:c>
+      <x:c r="O12" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P12" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="Q12" s="24" t="str">
-        <x:v>미구현. 수치는 03 초안 참조</x:v>
-      </x:c>
-      <x:c r="R12" s="22" t="str">
+        <x:v>보상. 일반 시전</x:v>
+      </x:c>
+      <x:c r="R12" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C12,1)="딜",ISNUMBER(M12)),M12,"")</x:f>
-      </x:c>
-      <x:c r="S12" s="22" t="str">
+        <x:v>65.40833333333333</x:v>
+      </x:c>
+      <x:c r="S12" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C12,1)="딜",ISNUMBER(N12)),N12,"")</x:f>
+        <x:v>142.70909090909092</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0">
@@ -4824,41 +4845,62 @@
       <x:c r="C13" s="17" t="str">
         <x:v>딜/광역</x:v>
       </x:c>
-      <x:c r="D13" s="17"/>
-      <x:c r="E13" s="17"/>
-      <x:c r="F13" s="22" t="str">
+      <x:c r="D13" s="17" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F13" s="22" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(E13)),"",MAX(E13,'범례'!$C$26))</x:f>
-      </x:c>
-      <x:c r="G13" s="17"/>
-      <x:c r="H13" s="17"/>
-      <x:c r="I13" s="19" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H13" s="17" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I13" s="19" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"",G13*MAX(1,H13))</x:f>
-      </x:c>
-      <x:c r="J13" s="41" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J13" s="41" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"",IF(G13&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G13*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G13*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H13)))</x:f>
-      </x:c>
-      <x:c r="K13" s="41" t="str">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="K13" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J13)),"",J13*IF(ISNUMBER(SEARCH("광역",$C13)),'범례'!$C$30,1))</x:f>
-      </x:c>
-      <x:c r="L13" s="22" t="str">
+        <x:v>193.5</x:v>
+      </x:c>
+      <x:c r="L13" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J13)),NOT(ISNUMBER(D13)),D13=0),"",J13/D13)</x:f>
-      </x:c>
-      <x:c r="M13" s="22" t="str">
+        <x:v>17.2</x:v>
+      </x:c>
+      <x:c r="M13" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K13)),NOT(ISNUMBER(D13)),D13=0),"",K13/D13)</x:f>
-      </x:c>
-      <x:c r="N13" s="22" t="str">
+        <x:v>38.7</x:v>
+      </x:c>
+      <x:c r="N13" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K13)),NOT(ISNUMBER(F13)),F13=0),"",K13/F13)</x:f>
-      </x:c>
-      <x:c r="O13" s="17"/>
-      <x:c r="P13" s="17"/>
+        <x:v>193.5</x:v>
+      </x:c>
+      <x:c r="O13" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P13" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="Q13" s="20" t="str">
-        <x:v>미구현. 수치는 03 초안 참조</x:v>
-      </x:c>
-      <x:c r="R13" s="22" t="str">
+        <x:v>보상. 일반 시전, 광역</x:v>
+      </x:c>
+      <x:c r="R13" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C13,1)="딜",ISNUMBER(M13)),M13,"")</x:f>
-      </x:c>
-      <x:c r="S13" s="22" t="str">
+        <x:v>38.7</x:v>
+      </x:c>
+      <x:c r="S13" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C13,1)="딜",ISNUMBER(N13)),N13,"")</x:f>
+        <x:v>193.5</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0">
@@ -5137,35 +5179,54 @@
       <x:c r="C18" s="17" t="str">
         <x:v>방어</x:v>
       </x:c>
-      <x:c r="D18" s="17"/>
-      <x:c r="E18" s="17"/>
-      <x:c r="F18" s="22" t="str">
+      <x:c r="D18" s="17" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="F18" s="22" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(E18)),"",MAX(E18,'범례'!$C$26))</x:f>
-      </x:c>
-      <x:c r="G18" s="17"/>
-      <x:c r="H18" s="17"/>
-      <x:c r="I18" s="19" t="str">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="G18" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I18" s="19" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(G18)),NOT(ISNUMBER(H18))),"",G18*MAX(1,H18))</x:f>
-      </x:c>
-      <x:c r="J18" s="41" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="41" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(G18)),NOT(ISNUMBER(H18))),"",IF(G18&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G18*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G18*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H18)))</x:f>
-      </x:c>
-      <x:c r="K18" s="41" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K18" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J18)),"",J18*IF(ISNUMBER(SEARCH("광역",$C18)),'범례'!$C$30,1))</x:f>
-      </x:c>
-      <x:c r="L18" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L18" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J18)),NOT(ISNUMBER(D18)),D18=0),"",J18/D18)</x:f>
-      </x:c>
-      <x:c r="M18" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M18" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K18)),NOT(ISNUMBER(D18)),D18=0),"",K18/D18)</x:f>
-      </x:c>
-      <x:c r="N18" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N18" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K18)),NOT(ISNUMBER(F18)),F18=0),"",K18/F18)</x:f>
-      </x:c>
-      <x:c r="O18" s="17"/>
-      <x:c r="P18" s="17"/>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O18" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P18" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="Q18" s="20" t="str">
-        <x:v>미구현. 수치는 03 초안 참조</x:v>
+        <x:v>보상. 채널링 중 무적·기절 면역</x:v>
       </x:c>
       <x:c r="R18" s="22" t="str">
         <x:f aca="0">IF(AND(LEFT($C18,1)="딜",ISNUMBER(M18)),M18,"")</x:f>
@@ -5185,7 +5246,7 @@
       </x:c>
       <x:c r="B23" s="22" t="n">
         <x:f aca="0">IFERROR(MAX(R5:R18),"")</x:f>
-        <x:v>48.375</x:v>
+        <x:v>65.40833333333333</x:v>
       </x:c>
       <x:c r="C23" s="25" t="s">
         <x:v>70</x:v>
@@ -5207,7 +5268,7 @@
       </x:c>
       <x:c r="B25" s="19" t="n">
         <x:f aca="0">IFERROR(B23/B24,"")</x:f>
-        <x:v>1.6</x:v>
+        <x:v>2.1633763996554696</x:v>
       </x:c>
       <x:c r="C25" s="25" t="s">
         <x:v>73</x:v>
@@ -5318,7 +5379,7 @@
     </x:row>
     <x:row r="38" ht="128.35000610351562" hidden="0">
       <x:c r="A38" s="25" t="str">
-        <x:v>단일/광역 기본 방향은 10 T11. 현재 카드별 예외는 A20·A23.</x:v>
+        <x:v>단일/광역 기본 방향은 10 T11. 카드별 예외는 A20·A23·A29.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="166.39999389648438" hidden="0">
@@ -6144,7 +6205,7 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="C5" s="17" t="n">
-        <x:v>450</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="D5" s="17" t="n">
         <x:v>30</x:v>
@@ -6166,7 +6227,7 @@
       </x:c>
       <x:c r="I5" s="22" t="n">
         <x:f aca="0">IFERROR(C5/'덱시뮬'!$B$20,"")</x:f>
-        <x:v>25.57787040545662</x:v>
+        <x:v>19.893899204244036</x:v>
       </x:c>
       <x:c r="J5" s="20" t="str">
         <x:v>일반 공격. 필요하면 차단 가능</x:v>
@@ -6180,7 +6241,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="C6" s="17" t="n">
-        <x:v>450</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="D6" s="17" t="n">
         <x:v>40</x:v>
@@ -6200,7 +6261,7 @@
       </x:c>
       <x:c r="I6" s="22" t="n">
         <x:f aca="0">IFERROR(C6/'덱시뮬'!$B$20,"")</x:f>
-        <x:v>25.57787040545662</x:v>
+        <x:v>17.051913603637743</x:v>
       </x:c>
       <x:c r="J6" s="20" t="s">
         <x:v>115</x:v>
@@ -6241,20 +6302,38 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0">
-      <x:c r="A8" s="17"/>
-      <x:c r="B8" s="17"/>
-      <x:c r="C8" s="17"/>
-      <x:c r="D8" s="17"/>
-      <x:c r="E8" s="17"/>
-      <x:c r="F8" s="13" t="str">
+      <x:c r="A8" s="17" t="str">
+        <x:v>잡몹 D</x:v>
+      </x:c>
+      <x:c r="B8" s="17" t="str">
+        <x:v>초록·주황·빨강</x:v>
+      </x:c>
+      <x:c r="C8" s="17" t="n">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="D8" s="17" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="E8" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F8" s="13" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(E8)),"",E8/(E8+'범례'!$C$20))</x:f>
-      </x:c>
-      <x:c r="G8" s="17"/>
-      <x:c r="H8" s="17"/>
-      <x:c r="I8" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="17" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="H8" s="17" t="str">
+        <x:v>초록·주황 가능</x:v>
+      </x:c>
+      <x:c r="I8" s="22" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(C8)),"",C8/'덱시뮬'!$B$20)</x:f>
-      </x:c>
-      <x:c r="J8" s="20"/>
+        <x:v>45.47176960970065</x:v>
+      </x:c>
+      <x:c r="J8" s="20" t="str">
+        <x:v>D 데이터 생성. 전투 편성 미연결</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0">
       <x:c r="A9" s="17"/>
@@ -6290,12 +6369,12 @@
     </x:row>
     <x:row r="13" ht="15" hidden="0">
       <x:c r="A13" s="28" t="str">
-        <x:v>A·B 450, C 500은 임시 HP. 원복은 각 300. 10 적 HP 시험 참조.</x:v>
+        <x:v>현재 HP 원본: 10 A30. 이전 임시 시험은 종료.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0">
       <x:c r="A14" s="2" t="str">
-        <x:v>B·C도 초록 보유. 표는 주 공격만 기입. 초록도 차단 가능, 전체 패턴은 04 참조.</x:v>
+        <x:v>B·C·D도 초록 보유. 피해·시전은 주 공격 기준. 전체 패턴은 04 참조.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0">

--- a/Docs/밸런스시트.xlsx
+++ b/Docs/밸런스시트.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범례" sheetId="1" r:id="R89ff24ec21f642a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직업" sheetId="2" r:id="Reb75669ae9374e1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="스킬" sheetId="3" r:id="R61212b5ddc65493a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="덱시뮬" sheetId="4" r:id="R45e6d679c58d4ff1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="적" sheetId="5" r:id="R3caf11fee9ff4174"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HP예산" sheetId="6" r:id="Rb970658e670b4919"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인카운터" sheetId="7" r:id="R48b7006a0c914ba3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범례" sheetId="1" r:id="Rc8fb24d91c9a438e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직업" sheetId="2" r:id="R855449ec65df41d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="스킬" sheetId="3" r:id="R3e05465a2e3044e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="덱시뮬" sheetId="4" r:id="R73872ad332c7406f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="적" sheetId="5" r:id="R695e1d28c69e4dc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HP예산" sheetId="6" r:id="R8d0df99e061347ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인카운터" sheetId="7" r:id="Ra01ae031fdf747c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -925,12 +925,175 @@
     <x:r>
       <x:rPr>
         <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">기대 피해 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(1</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">체</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">기대 피해 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">잡몹</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">코스트당 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">잡몹</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">시간당 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">잡몹</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">방어도 부여</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
         <x:sz val="10"/>
         <x:color rgb="FFFFFFFF"/>
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t xml:space="preserve">기대 피해 </x:t>
+      <x:t xml:space="preserve">경직</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -939,7 +1102,7 @@
         <x:color rgb="FFFFFFFF"/>
         <x:rFont val="Arial"/>
       </x:rPr>
-      <x:t xml:space="preserve">(1</x:t>
+      <x:t xml:space="preserve">(</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -949,7 +1112,7 @@
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t xml:space="preserve">체</x:t>
+      <x:t xml:space="preserve">초</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -970,7 +1133,7 @@
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t xml:space="preserve">기대 피해 </x:t>
+      <x:t xml:space="preserve">검증</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -989,7 +1152,7 @@
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t xml:space="preserve">잡몹</x:t>
+      <x:t xml:space="preserve">코스트</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -1010,7 +1173,7 @@
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t xml:space="preserve">코스트당 </x:t>
+      <x:t xml:space="preserve">검증</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -1029,7 +1192,7 @@
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t xml:space="preserve">보스</x:t>
+      <x:t xml:space="preserve">시간</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -1042,20 +1205,665 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
+    <x:t xml:space="preserve">코스트당 최대</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">차단</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">·</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">방어 카드는 제외됨</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">코스트당 최소</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">코스트당 비율</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">목표 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">1.30 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">이하</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">시간당 최대</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">잠금 시간 대비 효율</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">시간당 최소</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">시간당 비율</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">딜</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">/</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">단일 장수</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">딜</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">/</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">광역 장수</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">목표 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">4</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">차단 카드 장수</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">방어 카드 장수</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">단일 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">/ </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">광역 설계</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="13"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">덱 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="13"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">8</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="13"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">장 구성 시뮬레이션</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">B</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">열에 스킬명만 입력하면 나머지는 자동 계산됩니다</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">. </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">스킬 시트의 스킬명과 정확히 일치해야 합니다</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">.</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">슬롯</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">위치</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">대응카드 코스트기준</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">대응카드 잠금기준</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">검증</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">덱 총 코스트</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">덱 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">1</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">사이클 총 잠금 시간</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">초</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">1</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">사이클 시간보다 크면 코스트가 아니라 잠금이 병목입니다</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">목표 전투 시간 대비 사이클 수</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">목표 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">1.0~1.5</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">회</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">대응 카드 장수 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">차단</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">+</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">방어</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">권장 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">2~3</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">장</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">이 시트의 목적</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">앞쪽에 캐스팅 긴 카드를 몰아두면 코스트가 넘쳐도 못 끌어옵니다</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">. </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">덱 순서 자체가 설계 결정입니다</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">.</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">적 스펙</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">F</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">열</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">방어감소율</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">), I</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">열</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">예상 처치 시간</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">은 자동 계산</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="9"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">.</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">담당 색상</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">피해량</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">방어감소율</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
         <x:color rgb="FFFFFFFF"/>
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
-      <x:t xml:space="preserve">코스트당 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
+      <x:t xml:space="preserve">캐스팅</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
         <x:color rgb="FFFFFFFF"/>
         <x:rFont val="Arial"/>
       </x:rPr>
@@ -1064,18 +1872,765 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
         <x:color rgb="FFFFFFFF"/>
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
+      <x:t xml:space="preserve">초</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">차단 가능</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">교육 의도</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">초록</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">주황</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">가능</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">차단 카드의 존재와 사용 타이밍</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">빨강</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">불가</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1300"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">런 전체 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1300"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">HP </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1300"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">예산</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">전투</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">구성</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">완벽 대응 시 피해</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">평범 대응 시 피해</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">누적 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">HP (</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">완벽</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">누적 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">HP (</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">평범</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">판정</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">총 피해 — 완벽 대응</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">총 피해 — 평범 대응</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">포션 총 회복량</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">감당 가능 총 피해</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">완벽 대응 여유</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">클수록 쉬움</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">. </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">목표 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">600 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">이상</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">평범 대응 여유</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">목표 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">0~200. </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">음수면 평범한 플레이로 클리어 불가</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">대응 성공의 가치</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">이 값이 클수록 방어 카드가 의미 있음</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">. </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">목표 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">300 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">이상</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">설계 목표</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">'</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">대응 성공의 가치</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">'</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">가 작으면 방어 카드를 넣을 이유가 없습니다</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">. </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">빨강 공격 피해를 키우세요</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">.</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">'</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">평범 대응 여유</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">'</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">가 크게 음수면 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">2~3</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">전투에서 이미 클리어가 불가능해집니다</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">. </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">적 피해를 낮추세요</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">.</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">인카운터 구성 및 실측</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">번호</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">목표 시간</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">초</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">실측 시간</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">초</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">차이</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">초</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">오차율</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">신규 요소</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">수정 내용과 근거</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">예시</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">) </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
       <x:t xml:space="preserve">잡몹</x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">A ×2</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">기본 루프</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">목표 대비 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">45% </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">초과</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">. </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">적 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">HP 300→220 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">하향 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Arial"/>
+      </x:rPr>
+      <x:t xml:space="preserve">(18</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">일차</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:i/>
+        <x:sz val="900"/>
+        <x:color rgb="FF808080"/>
         <x:rFont val="Arial"/>
       </x:rPr>
       <x:t xml:space="preserve">)</x:t>
@@ -1085,18 +2640,18 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">시간당 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">총 목표 전투 시간</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
       </x:rPr>
       <x:t xml:space="preserve">(</x:t>
@@ -1104,42 +2659,39 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">잡몹</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">초</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
       </x:rPr>
       <x:t xml:space="preserve">)</x:t>
     </x:r>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">방어도 부여</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">경직</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
+        <x:rFont val="Noto Sans CJK SC"/>
+        <x:family val="2"/>
+      </x:rPr>
+      <x:t xml:space="preserve">총 실측 전투 시간</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:b/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
       </x:rPr>
       <x:t xml:space="preserve">(</x:t>
@@ -1147,8 +2699,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Noto Sans CJK SC"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1157,2103 +2709,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">검증</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">코스트</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">검증</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">시간</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">코스트당 최대</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">차단</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">·</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">방어 카드는 제외됨</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">코스트당 최소</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">코스트당 비율</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">목표 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1.30 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">이하</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">시간당 최대</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">잠금 시간 대비 효율</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">시간당 최소</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">시간당 비율</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">딜</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">/</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">단일 장수</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">딜</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">/</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">광역 장수</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">목표 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">4</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">차단 카드 장수</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">방어 카드 장수</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">단일 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">/ </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">광역 설계</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">L</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">열</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">보스 기준</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">과 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">M</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">열</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">잡몹 기준</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">의 격차가 크면 그 카드는 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">'</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">상황용</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">'</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">입니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">격차가 없으면 범용입니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">보스전은 적 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">체이므로 광역기는 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">L</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">열 값만 나옵니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">덱 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">8</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">장에 상황용을 몇 장 넣을지가 결정이 됩니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="13"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">덱 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="13"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">8</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="13"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">장 구성 시뮬레이션</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">B</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">열에 스킬명만 입력하면 나머지는 자동 계산됩니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">스킬 시트의 스킬명과 정확히 일치해야 합니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">슬롯</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">위치</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">대응카드 코스트기준</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">대응카드 잠금기준</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">검증</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">덱 총 코스트</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">덱 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">사이클 총 잠금 시간</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">초</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">사이클 시간보다 크면 코스트가 아니라 잠금이 병목입니다</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">목표 전투 시간 대비 사이클 수</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">목표 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1.0~1.5</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">회</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">대응 카드 장수 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">차단</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">+</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">방어</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="1000"/>
-        <x:color rgb="FF000000"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">권장 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">2~3</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">장</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">이 시트의 목적</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">앞쪽에 캐스팅 긴 카드를 몰아두면 코스트가 넘쳐도 못 끌어옵니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">덱 순서 자체가 설계 결정입니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">적 스펙</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">F</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">열</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">방어감소율</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">), I</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">열</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">예상 처치 시간</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">은 자동 계산</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">담당 색상</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">피해량</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">방어감소율</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">캐스팅</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">초</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">차단 가능</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">교육 의도</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">잡몹 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">A</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">초록</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">잡몹 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">B</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">주황</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">가능</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">차단 카드의 존재와 사용 타이밍</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">잡몹 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="10"/>
-        <x:color rgb="FF0000FF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">C</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">빨강</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">불가</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">방어도 카드의 존재</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="13"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">런 전체 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="13"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">HP </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="13"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">예산</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">전투</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">구성</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">완벽 대응 시 피해</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">평범 대응 시 피해</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">누적 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">HP (</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">완벽</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">누적 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">HP (</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">평범</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">판정</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">총 피해 — 완벽 대응</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">총 피해 — 평범 대응</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">포션 총 회복량</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">감당 가능 총 피해</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">완벽 대응 여유</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">클수록 쉬움</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">목표 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">600 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">이상</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">평범 대응 여유</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">목표 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">0~200. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">음수면 평범한 플레이로 클리어 불가</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">대응 성공의 가치</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">이 값이 클수록 방어 카드가 의미 있음</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">목표 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">300 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">이상</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">설계 목표</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">'</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">대응 성공의 가치</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">'</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">가 작으면 방어 카드를 넣을 이유가 없습니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">빨강 공격 피해를 키우세요</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">'</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">평범 대응 여유</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">'</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">가 크게 음수면 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">2~3</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">전투에서 이미 클리어가 불가능해집니다</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">적 피해를 낮추세요</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="900"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">인카운터 구성 및 실측</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">D</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">열</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">실측</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">은 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">18</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">일차에 스톱워치로 측정해 기입</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. E·F</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">열은 자동 계산</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">번호</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">목표 시간</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">초</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">실측 시간</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">초</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">차이</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">초</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:color rgb="FFFFFFFF"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">오차율</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">신규 요소</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">수정 내용과 근거</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">예시</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">) </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">잡몹</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">A ×2</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">기본 루프</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">목표 대비 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">45% </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">초과</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">. </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">적 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">HP 300→220 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">하향 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(18</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">일차</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">총 목표 전투 시간</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">초</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">목표</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">: </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">전투 합계 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">6~7</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">분 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(360~420</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">초</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:i/>
-        <x:sz val="9"/>
-        <x:color rgb="FF808080"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">총 실측 전투 시간</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Arial"/>
-      </x:rPr>
-      <x:t xml:space="preserve">(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
-        <x:rFont val="Noto Sans CJK SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">초</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
       </x:rPr>
       <x:t xml:space="preserve">)</x:t>
@@ -4069,10 +3526,10 @@
         <x:v>최대 HP의 30%씩 회복</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D29" s="10" t="str">
-        <x:v>10 A8·A28. 시작 1개, PS01 최대치·현재 +1</x:v>
+        <x:v>10 A46. 시작 3/3, PS01 최대치·현재 +1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0">
@@ -4080,13 +3537,13 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>정식 런 계획의 광역 피해 참고값</x:v>
+        <x:v>튜토리얼 제외 A+B / C / A+B+C</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
-        <x:v>2.25</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D30" s="10" t="str">
-        <x:v>5전투 계획의 잡몹전 평균. 현재 시연은 B→C→B+C</x:v>
+        <x:v>(2+1+3)/3=2. 10 A32·A34</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0">
@@ -4096,7 +3553,7 @@
     </x:row>
     <x:row r="32" ht="15" hidden="0">
       <x:c r="A32" s="14" t="str">
-        <x:v>2026-09-28: 신규 3종·적 HP 반영. 원본 10 A29·A30.</x:v>
+        <x:v>2026-10-07: 포션 3/3·전투 구성·적 피해 갱신. 10 A32·A33·A38·A43·A46.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4266,29 +3723,29 @@
       <x:c r="K4" s="8" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="L4" s="8" t="s">
+      <x:c r="L4" s="8" t="str">
+        <x:v>코스트당 (1체)</x:v>
+      </x:c>
+      <x:c r="M4" s="8" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="M4" s="8" t="s">
+      <x:c r="N4" s="8" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="N4" s="8" t="s">
+      <x:c r="O4" s="8" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="O4" s="8" t="s">
+      <x:c r="P4" s="8" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="P4" s="8" t="s">
-        <x:v>66</x:v>
       </x:c>
       <x:c r="Q4" s="8" t="str">
         <x:v>구현·발동 방식</x:v>
       </x:c>
       <x:c r="R4" s="8" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="S4" s="8" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="S4" s="8" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0">
@@ -4531,7 +3988,7 @@
       </x:c>
       <x:c r="K8" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J8)),"",J8*IF(ISNUMBER(SEARCH("광역",$C8)),'범례'!$C$30,1))</x:f>
-        <x:v>120.9375</x:v>
+        <x:v>107.5</x:v>
       </x:c>
       <x:c r="L8" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J8)),NOT(ISNUMBER(D8)),D8=0),"",J8/D8)</x:f>
@@ -4539,11 +3996,11 @@
       </x:c>
       <x:c r="M8" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K8)),NOT(ISNUMBER(D8)),D8=0),"",K8/D8)</x:f>
-        <x:v>30.234375</x:v>
+        <x:v>26.875</x:v>
       </x:c>
       <x:c r="N8" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K8)),NOT(ISNUMBER(F8)),F8=0),"",K8/F8)</x:f>
-        <x:v>120.9375</x:v>
+        <x:v>107.5</x:v>
       </x:c>
       <x:c r="O8" s="17" t="n">
         <x:v>0</x:v>
@@ -4556,11 +4013,11 @@
       </x:c>
       <x:c r="R8" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C8,1)="딜",ISNUMBER(M8)),M8,"")</x:f>
-        <x:v>30.234375</x:v>
+        <x:v>26.875</x:v>
       </x:c>
       <x:c r="S8" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C8,1)="딜",ISNUMBER(N8)),N8,"")</x:f>
-        <x:v>120.9375</x:v>
+        <x:v>107.5</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0">
@@ -4667,7 +4124,7 @@
       </x:c>
       <x:c r="K10" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J10)),"",J10*IF(ISNUMBER(SEARCH("광역",$C10)),'범례'!$C$30,1))</x:f>
-        <x:v>98.10000000000001</x:v>
+        <x:v>87.2</x:v>
       </x:c>
       <x:c r="L10" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J10)),NOT(ISNUMBER(D10)),D10=0),"",J10/D10)</x:f>
@@ -4675,11 +4132,11 @@
       </x:c>
       <x:c r="M10" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K10)),NOT(ISNUMBER(D10)),D10=0),"",K10/D10)</x:f>
-        <x:v>32.7</x:v>
+        <x:v>29.066666666666666</x:v>
       </x:c>
       <x:c r="N10" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K10)),NOT(ISNUMBER(F10)),F10=0),"",K10/F10)</x:f>
-        <x:v>44.59090909090909</x:v>
+        <x:v>39.63636363636363</x:v>
       </x:c>
       <x:c r="O10" s="17" t="n">
         <x:v>0</x:v>
@@ -4692,11 +4149,11 @@
       </x:c>
       <x:c r="R10" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C10,1)="딜",ISNUMBER(M10)),M10,"")</x:f>
-        <x:v>32.7</x:v>
+        <x:v>29.066666666666666</x:v>
       </x:c>
       <x:c r="S10" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C10,1)="딜",ISNUMBER(N10)),N10,"")</x:f>
-        <x:v>44.59090909090909</x:v>
+        <x:v>39.63636363636363</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0">
@@ -4871,7 +4328,7 @@
       </x:c>
       <x:c r="K13" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J13)),"",J13*IF(ISNUMBER(SEARCH("광역",$C13)),'범례'!$C$30,1))</x:f>
-        <x:v>193.5</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="L13" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J13)),NOT(ISNUMBER(D13)),D13=0),"",J13/D13)</x:f>
@@ -4879,11 +4336,11 @@
       </x:c>
       <x:c r="M13" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K13)),NOT(ISNUMBER(D13)),D13=0),"",K13/D13)</x:f>
-        <x:v>38.7</x:v>
+        <x:v>34.4</x:v>
       </x:c>
       <x:c r="N13" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K13)),NOT(ISNUMBER(F13)),F13=0),"",K13/F13)</x:f>
-        <x:v>193.5</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="O13" s="17" t="n">
         <x:v>0</x:v>
@@ -4896,11 +4353,11 @@
       </x:c>
       <x:c r="R13" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C13,1)="딜",ISNUMBER(M13)),M13,"")</x:f>
-        <x:v>38.7</x:v>
+        <x:v>34.4</x:v>
       </x:c>
       <x:c r="S13" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C13,1)="딜",ISNUMBER(N13)),N13,"")</x:f>
-        <x:v>193.5</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0">
@@ -4939,7 +4396,7 @@
       </x:c>
       <x:c r="K14" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J14)),"",J14*IF(ISNUMBER(SEARCH("광역",$C14)),'범례'!$C$30,1))</x:f>
-        <x:v>96.75</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="L14" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J14)),NOT(ISNUMBER(D14)),D14=0),"",J14/D14)</x:f>
@@ -4947,11 +4404,11 @@
       </x:c>
       <x:c r="M14" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K14)),NOT(ISNUMBER(D14)),D14=0),"",K14/D14)</x:f>
-        <x:v>48.375</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="N14" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K14)),NOT(ISNUMBER(F14)),F14=0),"",K14/F14)</x:f>
-        <x:v>193.5</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="O14" s="17" t="n">
         <x:v>0</x:v>
@@ -4964,11 +4421,11 @@
       </x:c>
       <x:c r="R14" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C14,1)="딜",ISNUMBER(M14)),M14,"")</x:f>
-        <x:v>48.375</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="S14" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C14,1)="딜",ISNUMBER(N14)),N14,"")</x:f>
-        <x:v>193.5</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0">
@@ -5242,75 +4699,75 @@
     </x:row>
     <x:row r="23" ht="29.850000381469727" hidden="0">
       <x:c r="A23" s="10" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B23" s="22" t="n">
         <x:f aca="0">IFERROR(MAX(R5:R18),"")</x:f>
         <x:v>65.40833333333333</x:v>
       </x:c>
       <x:c r="C23" s="25" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="29.850000381469727" hidden="0">
       <x:c r="A24" s="10" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B24" s="22" t="n">
         <x:f aca="0">IFERROR(MIN(R5:R18),"")</x:f>
-        <x:v>30.234375</x:v>
+        <x:v>26.875</x:v>
       </x:c>
       <x:c r="C24" s="25"/>
     </x:row>
     <x:row r="25" ht="29.850000381469727" hidden="0">
       <x:c r="A25" s="10" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B25" s="19" t="n">
         <x:f aca="0">IFERROR(B23/B24,"")</x:f>
-        <x:v>2.1633763996554696</x:v>
+        <x:v>2.433798449612403</x:v>
       </x:c>
       <x:c r="C25" s="25" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="29.850000381469727" hidden="0">
       <x:c r="A26" s="10" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B26" s="22" t="n">
         <x:f aca="0">IFERROR(MAX(S5:S18),"")</x:f>
         <x:v>322.5</x:v>
       </x:c>
       <x:c r="C26" s="25" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="29.850000381469727" hidden="0">
       <x:c r="A27" s="10" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B27" s="22" t="n">
         <x:f aca="0">IFERROR(MIN(S5:S18),"")</x:f>
-        <x:v>44.59090909090909</x:v>
+        <x:v>39.63636363636363</x:v>
       </x:c>
       <x:c r="C27" s="25"/>
     </x:row>
     <x:row r="28" ht="29.850000381469727" hidden="0">
       <x:c r="A28" s="10" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B28" s="19" t="n">
         <x:f aca="0">IFERROR(B26/B27,"")</x:f>
-        <x:v>7.232415902140672</x:v>
+        <x:v>8.136467889908257</x:v>
       </x:c>
       <x:c r="C28" s="25" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="29.850000381469727" hidden="0">
       <x:c r="A29" s="10" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B29" s="23" t="n">
         <x:f aca="0">COUNTIF(C5:C18,"딜/단일")</x:f>
@@ -5324,19 +4781,19 @@
     </x:row>
     <x:row r="30" ht="29.850000381469727" hidden="0">
       <x:c r="A30" s="10" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B30" s="23" t="n">
         <x:f aca="0">COUNTIF(C5:C18,"딜/광역")</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="C30" s="25" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="29.850000381469727" hidden="0">
       <x:c r="A31" s="10" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B31" s="23" t="n">
         <x:f aca="0">COUNTIF(C5:C18,"차단")</x:f>
@@ -5350,7 +4807,7 @@
     </x:row>
     <x:row r="32" ht="29.850000381469727" hidden="0">
       <x:c r="A32" s="10" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B32" s="23" t="n">
         <x:f aca="0">COUNTIF(C5:C18,"방어")</x:f>
@@ -5374,28 +4831,100 @@
     </x:row>
     <x:row r="37" ht="15" hidden="0">
       <x:c r="A37" s="3" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="128.35000610351562" hidden="0">
-      <x:c r="A38" s="25" t="str">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="22" hidden="0" customHeight="1">
+      <x:c r="A38" s="38" t="str">
         <x:v>단일/광역 기본 방향은 10 T11. 카드별 예외는 A20·A23·A29.</x:v>
       </x:c>
-    </x:row>
-    <x:row r="39" ht="166.39999389648438" hidden="0">
-      <x:c r="A39" s="26" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" ht="153.6999969482422" hidden="0">
-      <x:c r="A40" s="25" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" ht="164.14999389648438" hidden="0">
-      <x:c r="A41" s="25" t="str">
+      <x:c r="B38" s="39"/>
+      <x:c r="C38" s="39"/>
+      <x:c r="D38" s="39"/>
+      <x:c r="E38" s="39"/>
+      <x:c r="F38" s="39"/>
+      <x:c r="G38" s="39"/>
+      <x:c r="H38" s="39"/>
+      <x:c r="I38" s="39"/>
+      <x:c r="J38" s="39"/>
+      <x:c r="K38" s="39"/>
+      <x:c r="L38" s="39"/>
+      <x:c r="M38" s="39"/>
+      <x:c r="N38" s="39"/>
+      <x:c r="O38" s="39"/>
+      <x:c r="P38" s="39"/>
+      <x:c r="Q38" s="39"/>
+      <x:c r="R38" s="39"/>
+      <x:c r="S38" s="39"/>
+    </x:row>
+    <x:row r="39" ht="22" hidden="0" customHeight="1">
+      <x:c r="A39" s="40" t="str">
+        <x:v>L열은 1체, M열은 일반 전투 평균 적 수 기준. 실제 대상 수·시전 시간을 함께 비교.</x:v>
+      </x:c>
+      <x:c r="B39" s="39"/>
+      <x:c r="C39" s="39"/>
+      <x:c r="D39" s="39"/>
+      <x:c r="E39" s="39"/>
+      <x:c r="F39" s="39"/>
+      <x:c r="G39" s="39"/>
+      <x:c r="H39" s="39"/>
+      <x:c r="I39" s="39"/>
+      <x:c r="J39" s="39"/>
+      <x:c r="K39" s="39"/>
+      <x:c r="L39" s="39"/>
+      <x:c r="M39" s="39"/>
+      <x:c r="N39" s="39"/>
+      <x:c r="O39" s="39"/>
+      <x:c r="P39" s="39"/>
+      <x:c r="Q39" s="39"/>
+      <x:c r="R39" s="39"/>
+      <x:c r="S39" s="39"/>
+    </x:row>
+    <x:row r="40" ht="22" hidden="0" customHeight="1">
+      <x:c r="A40" s="38" t="str">
+        <x:v>보스전은 본체 1체+오브 최대 2체. 광역 가치는 활성 오브 수에 따라 달라짐(10 A43).</x:v>
+      </x:c>
+      <x:c r="B40" s="39"/>
+      <x:c r="C40" s="39"/>
+      <x:c r="D40" s="39"/>
+      <x:c r="E40" s="39"/>
+      <x:c r="F40" s="39"/>
+      <x:c r="G40" s="39"/>
+      <x:c r="H40" s="39"/>
+      <x:c r="I40" s="39"/>
+      <x:c r="J40" s="39"/>
+      <x:c r="K40" s="39"/>
+      <x:c r="L40" s="39"/>
+      <x:c r="M40" s="39"/>
+      <x:c r="N40" s="39"/>
+      <x:c r="O40" s="39"/>
+      <x:c r="P40" s="39"/>
+      <x:c r="Q40" s="39"/>
+      <x:c r="R40" s="39"/>
+      <x:c r="S40" s="39"/>
+    </x:row>
+    <x:row r="41" ht="22" hidden="0" customHeight="1">
+      <x:c r="A41" s="38" t="str">
         <x:v>광역 시전 시간은 현재 카드별 값을 따름. 채널링은 중단 시 남은 피해 미발생.</x:v>
       </x:c>
+      <x:c r="B41" s="39"/>
+      <x:c r="C41" s="39"/>
+      <x:c r="D41" s="39"/>
+      <x:c r="E41" s="39"/>
+      <x:c r="F41" s="39"/>
+      <x:c r="G41" s="39"/>
+      <x:c r="H41" s="39"/>
+      <x:c r="I41" s="39"/>
+      <x:c r="J41" s="39"/>
+      <x:c r="K41" s="39"/>
+      <x:c r="L41" s="39"/>
+      <x:c r="M41" s="39"/>
+      <x:c r="N41" s="39"/>
+      <x:c r="O41" s="39"/>
+      <x:c r="P41" s="39"/>
+      <x:c r="Q41" s="39"/>
+      <x:c r="R41" s="39"/>
+      <x:c r="S41" s="39"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5420,17 +4949,17 @@
   <x:sheetData>
     <x:row r="1" ht="20.100000381469727" hidden="0">
       <x:c r="A1" s="15" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0">
       <x:c r="A2" s="21" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A4" s="8" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B4" s="8" t="s">
         <x:v>54</x:v>
@@ -5448,7 +4977,7 @@
         <x:v>기대 피해(1체)</x:v>
       </x:c>
       <x:c r="G4" s="8" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H4" s="8" t="str">
         <x:v>앞 카드 코스트 합</x:v>
@@ -5460,10 +4989,10 @@
         <x:v>앞 카드 잠금 합(초)</x:v>
       </x:c>
       <x:c r="K4" s="8" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="L4" s="8" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0">
@@ -5840,12 +5369,12 @@
     </x:row>
     <x:row r="15" ht="15" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="30" hidden="0" customHeight="1">
       <x:c r="A16" s="10" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B16" s="23" t="n">
         <x:f aca="0">SUM(D5:D12)</x:f>
@@ -5883,14 +5412,14 @@
     </x:row>
     <x:row r="18" ht="30" hidden="0" customHeight="1">
       <x:c r="A18" s="10" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B18" s="22" t="n">
         <x:f aca="0">SUM(E5:E12)</x:f>
         <x:v>8.4</x:v>
       </x:c>
       <x:c r="D18" s="40" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E18" s="39"/>
       <x:c r="F18" s="39"/>
@@ -5941,14 +5470,14 @@
     </x:row>
     <x:row r="21" ht="30" hidden="0" customHeight="1">
       <x:c r="A21" s="10" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B21" s="19" t="n">
         <x:f aca="0">IFERROR('범례'!$C$27/B17,"")</x:f>
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="D21" s="38" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E21" s="39"/>
       <x:c r="F21" s="39"/>
@@ -5961,14 +5490,14 @@
     </x:row>
     <x:row r="22" ht="30" hidden="0" customHeight="1">
       <x:c r="A22" s="10" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B22" s="23" t="n">
         <x:f aca="0">COUNTIF(C5:C12,"차단")+COUNTIF(C5:C12,"방어")</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="D22" s="38" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E22" s="39"/>
       <x:c r="F22" s="39"/>
@@ -6021,7 +5550,7 @@
     </x:row>
     <x:row r="28" ht="15" hidden="0">
       <x:c r="A28" s="3" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="25" hidden="0" customHeight="1">
@@ -6106,7 +5635,7 @@
     </x:row>
     <x:row r="34" ht="25" hidden="0" customHeight="1">
       <x:c r="A34" s="38" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B34" s="39"/>
       <x:c r="C34" s="39"/>
@@ -6157,12 +5686,12 @@
   <x:sheetData>
     <x:row r="1" ht="16.149999618530273" hidden="0">
       <x:c r="A1" s="15" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0">
       <x:c r="A2" s="21" t="s">
-        <x:v>103</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -6170,45 +5699,45 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B4" s="8" t="s">
-        <x:v>104</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C4" s="16" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="D4" s="8" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E4" s="8" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="F4" s="8" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G4" s="8" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H4" s="8" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="I4" s="37" t="str">
         <x:v>회복량 기준 참고 시간</x:v>
       </x:c>
       <x:c r="J4" s="8" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0">
-      <x:c r="A5" s="17" t="s">
-        <x:v>110</x:v>
+      <x:c r="A5" s="17" t="str">
+        <x:v>약탈자 A</x:v>
       </x:c>
       <x:c r="B5" s="17" t="s">
-        <x:v>111</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C5" s="17" t="n">
         <x:v>350</x:v>
       </x:c>
       <x:c r="D5" s="17" t="n">
-        <x:v>30</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E5" s="17" t="n">
         <x:v>0</x:v>
@@ -6234,11 +5763,11 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0">
-      <x:c r="A6" s="17" t="s">
-        <x:v>112</x:v>
+      <x:c r="A6" s="17" t="str">
+        <x:v>궁병 B</x:v>
       </x:c>
       <x:c r="B6" s="17" t="s">
-        <x:v>113</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C6" s="17" t="n">
         <x:v>300</x:v>
@@ -6257,28 +5786,28 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H6" s="17" t="s">
-        <x:v>114</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I6" s="22" t="n">
         <x:f aca="0">IFERROR(C6/'덱시뮬'!$B$20,"")</x:f>
         <x:v>17.051913603637743</x:v>
       </x:c>
       <x:c r="J6" s="20" t="s">
-        <x:v>115</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0">
-      <x:c r="A7" s="17" t="s">
-        <x:v>116</x:v>
+      <x:c r="A7" s="17" t="str">
+        <x:v>우두머리 C</x:v>
       </x:c>
       <x:c r="B7" s="17" t="s">
-        <x:v>117</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C7" s="17" t="n">
         <x:v>500</x:v>
       </x:c>
       <x:c r="D7" s="17" t="n">
-        <x:v>150</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E7" s="17" t="n">
         <x:v>0</x:v>
@@ -6291,14 +5820,14 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H7" s="17" t="s">
-        <x:v>118</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="I7" s="22" t="n">
         <x:f aca="0">IFERROR(C7/'덱시뮬'!$B$20,"")</x:f>
         <x:v>28.419856006062908</x:v>
       </x:c>
-      <x:c r="J7" s="20" t="s">
-        <x:v>119</x:v>
+      <x:c r="J7" s="20" t="str">
+        <x:v>빨강: 방어력 20 기준 200. 방어도 보유 시 100 후 흡수</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0">
@@ -6369,7 +5898,7 @@
     </x:row>
     <x:row r="13" ht="15" hidden="0">
       <x:c r="A13" s="28" t="str">
-        <x:v>현재 HP 원본: 10 A30. 이전 임시 시험은 종료.</x:v>
+        <x:v>현재 HP·피해·명칭: 10 A30·A33·A38. 튜토리얼·보스·오브는 04 참조.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0">
@@ -6401,70 +5930,76 @@
   <x:sheetData>
     <x:row r="1" ht="20.100000381469727" hidden="0">
       <x:c r="A1" s="15" t="s">
-        <x:v>120</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0">
       <x:c r="A2" s="21" t="str">
-        <x:v>정식 5전투 계획용. 현재 시연 3전투와 구분. 피해 입력 전 합계·여유는 미확인.</x:v>
+        <x:v>튜토리얼 뒤 HP·포션 초기화. 런 예산은 일반 4전투만 합산. 피해 입력 전 결과 미확인.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A4" s="8" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D4" s="8" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="E4" s="8" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="F4" s="8" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G4" s="8" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H4" s="8" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="B4" s="8" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="D4" s="8" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="E4" s="8" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="F4" s="8" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="G4" s="8" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H4" s="8" t="s">
-        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0">
       <x:c r="A5" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B5" s="20"/>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>튜토리얼</x:v>
+      </x:c>
       <x:c r="C5" s="17"/>
       <x:c r="D5" s="17"/>
       <x:c r="E5" s="23" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(C5)),"",IF(A5=1,'직업'!$B$5-C5,E4-C5))</x:f>
+        <x:f aca="0">IF(NOT(ISNUMBER(C5)),"",'직업'!$B$5-C5)</x:f>
       </x:c>
       <x:c r="F5" s="23" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(D5)),"",IF(A5=1,'직업'!$B$5-D5,F4-D5))</x:f>
+        <x:f aca="0">IF(NOT(ISNUMBER(D5)),"",'직업'!$B$5-D5)</x:f>
       </x:c>
       <x:c r="G5" s="27" t="str">
         <x:f aca="0">IF(NOT(ISNUMBER(F5)),"",IF(F5&lt;=0,"사망",IF(F5&lt;100,"위험","안전")))</x:f>
       </x:c>
-      <x:c r="H5" s="20"/>
+      <x:c r="H5" s="20" t="str">
+        <x:v>종료 후 초기화. 아래 런 예산에서 제외</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0">
       <x:c r="A6" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B6" s="20"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B6" s="20" t="str">
+        <x:v>A+B</x:v>
+      </x:c>
       <x:c r="C6" s="17"/>
       <x:c r="D6" s="17"/>
       <x:c r="E6" s="23" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(C6)),"",IF(A6=1,'직업'!$B$5-C6,E5-C6))</x:f>
+        <x:f aca="0">IF(NOT(ISNUMBER(C6)),"",'직업'!$B$5-C6)</x:f>
       </x:c>
       <x:c r="F6" s="23" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(D6)),"",IF(A6=1,'직업'!$B$5-D6,F5-D6))</x:f>
+        <x:f aca="0">IF(NOT(ISNUMBER(D6)),"",'직업'!$B$5-D6)</x:f>
       </x:c>
       <x:c r="G6" s="27" t="str">
         <x:f aca="0">IF(NOT(ISNUMBER(F6)),"",IF(F6&lt;=0,"사망",IF(F6&lt;100,"위험","안전")))</x:f>
@@ -6473,16 +6008,18 @@
     </x:row>
     <x:row r="7" ht="15" hidden="0">
       <x:c r="A7" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B7" s="20"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="str">
+        <x:v>C</x:v>
+      </x:c>
       <x:c r="C7" s="17"/>
       <x:c r="D7" s="17"/>
       <x:c r="E7" s="23" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(C7)),"",IF(A7=1,'직업'!$B$5-C7,E6-C7))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(C7)),NOT(ISNUMBER(E6))),"",E6-C7)</x:f>
       </x:c>
       <x:c r="F7" s="23" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(D7)),"",IF(A7=1,'직업'!$B$5-D7,F6-D7))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(D7)),NOT(ISNUMBER(F6))),"",F6-D7)</x:f>
       </x:c>
       <x:c r="G7" s="27" t="str">
         <x:f aca="0">IF(NOT(ISNUMBER(F7)),"",IF(F7&lt;=0,"사망",IF(F7&lt;100,"위험","안전")))</x:f>
@@ -6491,16 +6028,18 @@
     </x:row>
     <x:row r="8" ht="15" hidden="0">
       <x:c r="A8" s="27" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B8" s="20"/>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B8" s="20" t="str">
+        <x:v>A+B+C</x:v>
+      </x:c>
       <x:c r="C8" s="17"/>
       <x:c r="D8" s="17"/>
       <x:c r="E8" s="23" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(C8)),"",IF(A8=1,'직업'!$B$5-C8,E7-C8))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(C8)),NOT(ISNUMBER(E7))),"",E7-C8)</x:f>
       </x:c>
       <x:c r="F8" s="23" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(D8)),"",IF(A8=1,'직업'!$B$5-D8,F7-D8))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(D8)),NOT(ISNUMBER(F7))),"",F7-D8)</x:f>
       </x:c>
       <x:c r="G8" s="27" t="str">
         <x:f aca="0">IF(NOT(ISNUMBER(F8)),"",IF(F8&lt;=0,"사망",IF(F8&lt;100,"위험","안전")))</x:f>
@@ -6509,16 +6048,18 @@
     </x:row>
     <x:row r="9" ht="15" hidden="0">
       <x:c r="A9" s="27" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B9" s="20"/>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B9" s="20" t="str">
+        <x:v>마법사+오브</x:v>
+      </x:c>
       <x:c r="C9" s="17"/>
       <x:c r="D9" s="17"/>
       <x:c r="E9" s="23" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(C9)),"",IF(A9=1,'직업'!$B$5-C9,E8-C9))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(C9)),NOT(ISNUMBER(E8))),"",E8-C9)</x:f>
       </x:c>
       <x:c r="F9" s="23" t="str">
-        <x:f aca="0">IF(NOT(ISNUMBER(D9)),"",IF(A9=1,'직업'!$B$5-D9,F8-D9))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(D9)),NOT(ISNUMBER(F8))),"",F8-D9)</x:f>
       </x:c>
       <x:c r="G9" s="27" t="str">
         <x:f aca="0">IF(NOT(ISNUMBER(F9)),"",IF(F9&lt;=0,"사망",IF(F9&lt;100,"위험","안전")))</x:f>
@@ -6527,15 +6068,15 @@
     </x:row>
     <x:row r="12" ht="15" hidden="0">
       <x:c r="A12" s="3" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="30" hidden="0" customHeight="1">
       <x:c r="A13" s="10" t="s">
-        <x:v>129</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B13" s="23" t="str">
-        <x:f aca="0">IF(COUNT(C5:C9)&lt;5,"",SUM(C5:C9))</x:f>
+        <x:f aca="0">IF(COUNT(C6:C9)&lt;4,"",SUM(C6:C9))</x:f>
       </x:c>
       <x:c r="D13" s="38"/>
       <x:c r="E13" s="39"/>
@@ -6545,10 +6086,10 @@
     </x:row>
     <x:row r="14" ht="30" hidden="0" customHeight="1">
       <x:c r="A14" s="10" t="s">
-        <x:v>130</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B14" s="23" t="str">
-        <x:f aca="0">IF(COUNT(D5:D9)&lt;5,"",SUM(D5:D9))</x:f>
+        <x:f aca="0">IF(COUNT(D6:D9)&lt;4,"",SUM(D6:D9))</x:f>
       </x:c>
       <x:c r="D14" s="38"/>
       <x:c r="E14" s="39"/>
@@ -6558,14 +6099,14 @@
     </x:row>
     <x:row r="15" ht="30" hidden="0" customHeight="1">
       <x:c r="A15" s="10" t="s">
-        <x:v>131</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B15" s="23" t="n">
         <x:f aca="0">IFERROR(INT('직업'!$B$5*0.3+0.5)*'범례'!$C$29,"")</x:f>
-        <x:v>150</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D15" s="38" t="str">
-        <x:v>기본 포션 1개 × 최대 HP 30%. PS01 제외</x:v>
+        <x:v>기본 포션 3개 × 최대 HP 30%. PS01 제외</x:v>
       </x:c>
       <x:c r="E15" s="39"/>
       <x:c r="F15" s="39"/>
@@ -6574,11 +6115,11 @@
     </x:row>
     <x:row r="16" ht="30" hidden="0" customHeight="1">
       <x:c r="A16" s="10" t="s">
-        <x:v>132</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B16" s="23" t="n">
         <x:f aca="0">IFERROR('직업'!$B$5+B15,"")</x:f>
-        <x:v>650</x:v>
+        <x:v>950</x:v>
       </x:c>
       <x:c r="D16" s="38" t="str">
         <x:v>기본 HP+포션. 초과 회복 손실 없는 이론 상한</x:v>
@@ -6590,13 +6131,13 @@
     </x:row>
     <x:row r="17" ht="30" hidden="0" customHeight="1">
       <x:c r="A17" s="10" t="s">
-        <x:v>133</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B17" s="23" t="str">
         <x:f aca="0">IF(NOT(ISNUMBER(B13)),"",B16-B13)</x:f>
       </x:c>
       <x:c r="D17" s="38" t="s">
-        <x:v>134</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E17" s="39"/>
       <x:c r="F17" s="39"/>
@@ -6605,13 +6146,13 @@
     </x:row>
     <x:row r="18" ht="30" hidden="0" customHeight="1">
       <x:c r="A18" s="10" t="s">
-        <x:v>135</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B18" s="23" t="str">
         <x:f aca="0">IF(NOT(ISNUMBER(B14)),"",B16-B14)</x:f>
       </x:c>
       <x:c r="D18" s="38" t="s">
-        <x:v>136</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E18" s="39"/>
       <x:c r="F18" s="39"/>
@@ -6620,13 +6161,13 @@
     </x:row>
     <x:row r="19" ht="30" hidden="0" customHeight="1">
       <x:c r="A19" s="10" t="s">
-        <x:v>137</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B19" s="23" t="str">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(B13)),NOT(ISNUMBER(B14))),"",B14-B13)</x:f>
       </x:c>
       <x:c r="D19" s="38" t="s">
-        <x:v>138</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E19" s="39"/>
       <x:c r="F19" s="39"/>
@@ -6635,7 +6176,7 @@
     </x:row>
     <x:row r="22" ht="15" hidden="0">
       <x:c r="A22" s="3" t="s">
-        <x:v>139</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="25" hidden="0" customHeight="1">
@@ -6652,7 +6193,7 @@
     </x:row>
     <x:row r="24" ht="25" hidden="0" customHeight="1">
       <x:c r="A24" s="40" t="s">
-        <x:v>140</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B24" s="39"/>
       <x:c r="C24" s="39"/>
@@ -6664,7 +6205,7 @@
     </x:row>
     <x:row r="25" ht="25" hidden="0" customHeight="1">
       <x:c r="A25" s="40" t="s">
-        <x:v>141</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B25" s="39"/>
       <x:c r="C25" s="39"/>
@@ -6705,38 +6246,38 @@
   <x:sheetData>
     <x:row r="1" ht="16.149999618530273" hidden="0">
       <x:c r="A1" s="15" t="s">
-        <x:v>142</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0">
-      <x:c r="A2" s="21" t="s">
-        <x:v>143</x:v>
+      <x:c r="A2" s="21" t="str">
+        <x:v>현재 구성: 튜토리얼→A+B→C→A+B+C→보스. 5행은 예시, 실측은 07에 조건과 함께 기록.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A4" s="8" t="s">
-        <x:v>144</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B4" s="8" t="s">
-        <x:v>122</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C4" s="8" t="s">
-        <x:v>145</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D4" s="8" t="s">
-        <x:v>146</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E4" s="8" t="s">
-        <x:v>147</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F4" s="8" t="s">
-        <x:v>148</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G4" s="8" t="s">
-        <x:v>149</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H4" s="8" t="s">
-        <x:v>150</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0">
@@ -6744,7 +6285,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="30" t="s">
-        <x:v>151</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C5" s="29" t="n">
         <x:v>40</x:v>
@@ -6761,15 +6302,19 @@
         <x:v>0.45</x:v>
       </x:c>
       <x:c r="G5" s="33" t="s">
-        <x:v>152</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H5" s="33" t="s">
-        <x:v>153</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0">
-      <x:c r="A6" s="17"/>
-      <x:c r="B6" s="20"/>
+      <x:c r="A6" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B6" s="20" t="str">
+        <x:v>튜토리얼</x:v>
+      </x:c>
       <x:c r="C6" s="17"/>
       <x:c r="D6" s="17"/>
       <x:c r="E6" s="23" t="str">
@@ -6782,8 +6327,12 @@
       <x:c r="H6" s="20"/>
     </x:row>
     <x:row r="7" ht="15" hidden="0">
-      <x:c r="A7" s="17"/>
-      <x:c r="B7" s="20"/>
+      <x:c r="A7" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="str">
+        <x:v>A+B</x:v>
+      </x:c>
       <x:c r="C7" s="17"/>
       <x:c r="D7" s="17"/>
       <x:c r="E7" s="23" t="str">
@@ -6796,8 +6345,12 @@
       <x:c r="H7" s="20"/>
     </x:row>
     <x:row r="8" ht="15" hidden="0">
-      <x:c r="A8" s="17"/>
-      <x:c r="B8" s="20"/>
+      <x:c r="A8" s="17" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B8" s="20" t="str">
+        <x:v>C</x:v>
+      </x:c>
       <x:c r="C8" s="17"/>
       <x:c r="D8" s="17"/>
       <x:c r="E8" s="23" t="str">
@@ -6810,8 +6363,12 @@
       <x:c r="H8" s="20"/>
     </x:row>
     <x:row r="9" ht="15" hidden="0">
-      <x:c r="A9" s="17"/>
-      <x:c r="B9" s="20"/>
+      <x:c r="A9" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B9" s="20" t="str">
+        <x:v>A+B+C</x:v>
+      </x:c>
       <x:c r="C9" s="17"/>
       <x:c r="D9" s="17"/>
       <x:c r="E9" s="23" t="str">
@@ -6824,8 +6381,12 @@
       <x:c r="H9" s="20"/>
     </x:row>
     <x:row r="10" ht="15" hidden="0">
-      <x:c r="A10" s="17"/>
-      <x:c r="B10" s="20"/>
+      <x:c r="A10" s="17" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B10" s="20" t="str">
+        <x:v>마법사+오브</x:v>
+      </x:c>
       <x:c r="C10" s="17"/>
       <x:c r="D10" s="17"/>
       <x:c r="E10" s="23" t="str">
@@ -6853,23 +6414,21 @@
     </x:row>
     <x:row r="14" ht="39.54999923706055" hidden="0">
       <x:c r="A14" s="3" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="n">
-        <x:f aca="0">IFERROR(SUM(C6:C11),"")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E14" s="25" t="s">
-        <x:v>155</x:v>
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="str">
+        <x:f aca="0">IF(COUNT(C6:C10)&lt;5,"",SUM(C6:C10))</x:f>
+      </x:c>
+      <x:c r="E14" s="25" t="str">
+        <x:v>목표 미입력. 초기 시간 목표는 재검토 전</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="n">
-        <x:f aca="0">IFERROR(SUM(D6:D11),"")</x:f>
-        <x:v>0</x:v>
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="str">
+        <x:f aca="0">IF(COUNT(D6:D10)&lt;5,"",SUM(D6:D10))</x:f>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Docs/밸런스시트.xlsx
+++ b/Docs/밸런스시트.xlsx
@@ -4637,7 +4637,7 @@
         <x:v>방어</x:v>
       </x:c>
       <x:c r="D18" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E18" s="17" t="n">
         <x:v>2.5</x:v>

--- a/Docs/밸런스시트.xlsx
+++ b/Docs/밸런스시트.xlsx
@@ -3677,6 +3677,7 @@
     <x:col min="16" max="16" width="10" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="42" hidden="0" customWidth="1"/>
     <x:col min="18" max="19" width="13" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="20.100000381469727" hidden="0">
@@ -3747,6 +3748,9 @@
       <x:c r="S4" s="8" t="s">
         <x:v>67</x:v>
       </x:c>
+      <x:c r="T4" s="8" t="str">
+        <x:v>마지막 추가 피해</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0">
       <x:c r="A5" s="11" t="str">
@@ -3775,11 +3779,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I5" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(H5))),"",G5*MAX(1,H5))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(H5))),"",G5*MAX(1,H5)+T5)</x:f>
         <x:v>30</x:v>
       </x:c>
       <x:c r="J5" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(H5))),"",IF(G5&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G5*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G5*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H5)))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(H5))),"",IF(G5&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G5*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G5*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H5)-1)+((1-'직업'!$D$5)*MAX(1,INT((G5+T5)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G5+T5)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
         <x:v>32.25</x:v>
       </x:c>
       <x:c r="K5" s="41" t="n">
@@ -3815,6 +3819,9 @@
         <x:f aca="0">IF(AND(LEFT($C5,1)="딜",ISNUMBER(N5)),N5,"")</x:f>
         <x:v>80.625</x:v>
       </x:c>
+      <x:c r="T5" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0">
       <x:c r="A6" s="11" t="str">
@@ -3843,11 +3850,11 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I6" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G6)),NOT(ISNUMBER(H6))),"",G6*MAX(1,H6))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G6)),NOT(ISNUMBER(H6))),"",G6*MAX(1,H6)+T6)</x:f>
         <x:v>175</x:v>
       </x:c>
       <x:c r="J6" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G6)),NOT(ISNUMBER(H6))),"",IF(G6&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G6*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G6*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H6)))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G6)),NOT(ISNUMBER(H6))),"",IF(G6&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G6*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G6*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H6)-1)+((1-'직업'!$D$5)*MAX(1,INT((G6+T6)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G6+T6)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
         <x:v>188.5</x:v>
       </x:c>
       <x:c r="K6" s="41" t="n">
@@ -3883,6 +3890,9 @@
         <x:f aca="0">IF(AND(LEFT($C6,1)="딜",ISNUMBER(N6)),N6,"")</x:f>
         <x:v>67.32142857142857</x:v>
       </x:c>
+      <x:c r="T6" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0">
       <x:c r="A7" s="11" t="str">
@@ -3911,11 +3921,11 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I7" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G7)),NOT(ISNUMBER(H7))),"",G7*MAX(1,H7))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G7)),NOT(ISNUMBER(H7))),"",G7*MAX(1,H7)+T7)</x:f>
         <x:v>60</x:v>
       </x:c>
       <x:c r="J7" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G7)),NOT(ISNUMBER(H7))),"",IF(G7&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G7*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G7*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H7)))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G7)),NOT(ISNUMBER(H7))),"",IF(G7&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G7*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G7*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H7)-1)+((1-'직업'!$D$5)*MAX(1,INT((G7+T7)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G7+T7)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
         <x:v>64.5</x:v>
       </x:c>
       <x:c r="K7" s="41" t="n">
@@ -3951,6 +3961,9 @@
         <x:f aca="0">IF(AND(LEFT($C7,1)="딜",ISNUMBER(N7)),N7,"")</x:f>
         <x:v>161.25</x:v>
       </x:c>
+      <x:c r="T7" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0">
       <x:c r="A8" s="11" t="str">
@@ -3973,34 +3986,34 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="17" t="n">
-        <x:v>50</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H8" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I8" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G8)),NOT(ISNUMBER(H8))),"",G8*MAX(1,H8))</x:f>
-        <x:v>50</x:v>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G8)),NOT(ISNUMBER(H8))),"",G8*MAX(1,H8)+T8)</x:f>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="J8" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G8)),NOT(ISNUMBER(H8))),"",IF(G8&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G8*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G8*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H8)))</x:f>
-        <x:v>53.75</x:v>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G8)),NOT(ISNUMBER(H8))),"",IF(G8&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G8*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G8*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H8)-1)+((1-'직업'!$D$5)*MAX(1,INT((G8+T8)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G8+T8)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
+        <x:v>96.75</x:v>
       </x:c>
       <x:c r="K8" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J8)),"",J8*IF(ISNUMBER(SEARCH("광역",$C8)),'범례'!$C$30,1))</x:f>
-        <x:v>107.5</x:v>
+        <x:v>193.5</x:v>
       </x:c>
       <x:c r="L8" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J8)),NOT(ISNUMBER(D8)),D8=0),"",J8/D8)</x:f>
-        <x:v>13.4375</x:v>
+        <x:v>24.1875</x:v>
       </x:c>
       <x:c r="M8" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K8)),NOT(ISNUMBER(D8)),D8=0),"",K8/D8)</x:f>
-        <x:v>26.875</x:v>
+        <x:v>48.375</x:v>
       </x:c>
       <x:c r="N8" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K8)),NOT(ISNUMBER(F8)),F8=0),"",K8/F8)</x:f>
-        <x:v>107.5</x:v>
+        <x:v>193.5</x:v>
       </x:c>
       <x:c r="O8" s="17" t="n">
         <x:v>0</x:v>
@@ -4013,11 +4026,14 @@
       </x:c>
       <x:c r="R8" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C8,1)="딜",ISNUMBER(M8)),M8,"")</x:f>
-        <x:v>26.875</x:v>
+        <x:v>48.375</x:v>
       </x:c>
       <x:c r="S8" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C8,1)="딜",ISNUMBER(N8)),N8,"")</x:f>
-        <x:v>107.5</x:v>
+        <x:v>193.5</x:v>
+      </x:c>
+      <x:c r="T8" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0">
@@ -4047,11 +4063,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I9" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G9)),NOT(ISNUMBER(H9))),"",G9*MAX(1,H9))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G9)),NOT(ISNUMBER(H9))),"",G9*MAX(1,H9)+T9)</x:f>
         <x:v>135</x:v>
       </x:c>
       <x:c r="J9" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G9)),NOT(ISNUMBER(H9))),"",IF(G9&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G9*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G9*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H9)))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G9)),NOT(ISNUMBER(H9))),"",IF(G9&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G9*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G9*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H9)-1)+((1-'직업'!$D$5)*MAX(1,INT((G9+T9)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G9+T9)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
         <x:v>145.2</x:v>
       </x:c>
       <x:c r="K9" s="41" t="n">
@@ -4087,6 +4103,9 @@
         <x:f aca="0">IF(AND(LEFT($C9,1)="딜",ISNUMBER(N9)),N9,"")</x:f>
         <x:v>181.49999999999997</x:v>
       </x:c>
+      <x:c r="T9" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0">
       <x:c r="A10" s="11" t="str">
@@ -4109,34 +4128,34 @@
         <x:v>2.2</x:v>
       </x:c>
       <x:c r="G10" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H10" s="17" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="I10" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G10)),NOT(ISNUMBER(H10))),"",G10*MAX(1,H10))</x:f>
-        <x:v>40</x:v>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G10)),NOT(ISNUMBER(H10))),"",G10*MAX(1,H10)+T10)</x:f>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J10" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G10)),NOT(ISNUMBER(H10))),"",IF(G10&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G10*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G10*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H10)))</x:f>
-        <x:v>43.6</x:v>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G10)),NOT(ISNUMBER(H10))),"",IF(G10&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G10*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G10*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H10)-1)+((1-'직업'!$D$5)*MAX(1,INT((G10+T10)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G10+T10)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K10" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J10)),"",J10*IF(ISNUMBER(SEARCH("광역",$C10)),'범례'!$C$30,1))</x:f>
-        <x:v>87.2</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="L10" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J10)),NOT(ISNUMBER(D10)),D10=0),"",J10/D10)</x:f>
-        <x:v>14.533333333333333</x:v>
+        <x:v>28.666666666666668</x:v>
       </x:c>
       <x:c r="M10" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K10)),NOT(ISNUMBER(D10)),D10=0),"",K10/D10)</x:f>
-        <x:v>29.066666666666666</x:v>
+        <x:v>57.333333333333336</x:v>
       </x:c>
       <x:c r="N10" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K10)),NOT(ISNUMBER(F10)),F10=0),"",K10/F10)</x:f>
-        <x:v>39.63636363636363</x:v>
+        <x:v>78.18181818181817</x:v>
       </x:c>
       <x:c r="O10" s="17" t="n">
         <x:v>0</x:v>
@@ -4149,11 +4168,14 @@
       </x:c>
       <x:c r="R10" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C10,1)="딜",ISNUMBER(M10)),M10,"")</x:f>
-        <x:v>29.066666666666666</x:v>
+        <x:v>57.333333333333336</x:v>
       </x:c>
       <x:c r="S10" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C10,1)="딜",ISNUMBER(N10)),N10,"")</x:f>
-        <x:v>39.63636363636363</x:v>
+        <x:v>78.18181818181817</x:v>
+      </x:c>
+      <x:c r="T10" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0">
@@ -4183,28 +4205,28 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I11" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G11)),NOT(ISNUMBER(H11))),"",G11*MAX(1,H11))</x:f>
-        <x:v>120</x:v>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G11)),NOT(ISNUMBER(H11))),"",G11*MAX(1,H11)+T11)</x:f>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="J11" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G11)),NOT(ISNUMBER(H11))),"",IF(G11&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G11*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G11*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H11)))</x:f>
-        <x:v>129</x:v>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G11)),NOT(ISNUMBER(H11))),"",IF(G11&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G11*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G11*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H11)-1)+((1-'직업'!$D$5)*MAX(1,INT((G11+T11)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G11+T11)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
+        <x:v>139.75</x:v>
       </x:c>
       <x:c r="K11" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J11)),"",J11*IF(ISNUMBER(SEARCH("광역",$C11)),'범례'!$C$30,1))</x:f>
-        <x:v>129</x:v>
+        <x:v>139.75</x:v>
       </x:c>
       <x:c r="L11" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J11)),NOT(ISNUMBER(D11)),D11=0),"",J11/D11)</x:f>
-        <x:v>43</x:v>
+        <x:v>46.583333333333336</x:v>
       </x:c>
       <x:c r="M11" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K11)),NOT(ISNUMBER(D11)),D11=0),"",K11/D11)</x:f>
-        <x:v>43</x:v>
+        <x:v>46.583333333333336</x:v>
       </x:c>
       <x:c r="N11" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K11)),NOT(ISNUMBER(F11)),F11=0),"",K11/F11)</x:f>
-        <x:v>322.5</x:v>
+        <x:v>349.375</x:v>
       </x:c>
       <x:c r="O11" s="17" t="n">
         <x:v>0</x:v>
@@ -4217,11 +4239,14 @@
       </x:c>
       <x:c r="R11" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C11,1)="딜",ISNUMBER(M11)),M11,"")</x:f>
-        <x:v>43</x:v>
+        <x:v>46.583333333333336</x:v>
       </x:c>
       <x:c r="S11" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C11,1)="딜",ISNUMBER(N11)),N11,"")</x:f>
-        <x:v>322.5</x:v>
+        <x:v>349.375</x:v>
+      </x:c>
+      <x:c r="T11" s="17" t="n">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0">
@@ -4235,7 +4260,7 @@
         <x:v>딜/단일</x:v>
       </x:c>
       <x:c r="D12" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E12" s="17" t="n">
         <x:v>2.75</x:v>
@@ -4251,11 +4276,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"",G12*MAX(1,H12))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"",G12*MAX(1,H12)+T12)</x:f>
         <x:v>365</x:v>
       </x:c>
       <x:c r="J12" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"",IF(G12&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G12*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G12*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H12)))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"",IF(G12&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G12*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G12*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H12)-1)+((1-'직업'!$D$5)*MAX(1,INT((G12+T12)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G12+T12)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
         <x:v>392.45</x:v>
       </x:c>
       <x:c r="K12" s="41" t="n">
@@ -4264,11 +4289,11 @@
       </x:c>
       <x:c r="L12" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J12)),NOT(ISNUMBER(D12)),D12=0),"",J12/D12)</x:f>
-        <x:v>65.40833333333333</x:v>
+        <x:v>56.06428571428571</x:v>
       </x:c>
       <x:c r="M12" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K12)),NOT(ISNUMBER(D12)),D12=0),"",K12/D12)</x:f>
-        <x:v>65.40833333333333</x:v>
+        <x:v>56.06428571428571</x:v>
       </x:c>
       <x:c r="N12" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K12)),NOT(ISNUMBER(F12)),F12=0),"",K12/F12)</x:f>
@@ -4285,12 +4310,15 @@
       </x:c>
       <x:c r="R12" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C12,1)="딜",ISNUMBER(M12)),M12,"")</x:f>
-        <x:v>65.40833333333333</x:v>
+        <x:v>56.06428571428571</x:v>
       </x:c>
       <x:c r="S12" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C12,1)="딜",ISNUMBER(N12)),N12,"")</x:f>
         <x:v>142.70909090909092</x:v>
       </x:c>
+      <x:c r="T12" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0">
       <x:c r="A13" s="17" t="str">
@@ -4313,34 +4341,34 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H13" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="I13" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"",G13*MAX(1,H13))</x:f>
-        <x:v>80</x:v>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"",G13*MAX(1,H13)+T13)</x:f>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J13" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"",IF(G13&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G13*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G13*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H13)))</x:f>
-        <x:v>86</x:v>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"",IF(G13&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G13*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G13*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H13)-1)+((1-'직업'!$D$5)*MAX(1,INT((G13+T13)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G13+T13)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="K13" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J13)),"",J13*IF(ISNUMBER(SEARCH("광역",$C13)),'범례'!$C$30,1))</x:f>
-        <x:v>172</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="L13" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J13)),NOT(ISNUMBER(D13)),D13=0),"",J13/D13)</x:f>
-        <x:v>17.2</x:v>
+        <x:v>25.8</x:v>
       </x:c>
       <x:c r="M13" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K13)),NOT(ISNUMBER(D13)),D13=0),"",K13/D13)</x:f>
-        <x:v>34.4</x:v>
+        <x:v>51.6</x:v>
       </x:c>
       <x:c r="N13" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K13)),NOT(ISNUMBER(F13)),F13=0),"",K13/F13)</x:f>
-        <x:v>172</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="O13" s="17" t="n">
         <x:v>0</x:v>
@@ -4353,11 +4381,14 @@
       </x:c>
       <x:c r="R13" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C13,1)="딜",ISNUMBER(M13)),M13,"")</x:f>
-        <x:v>34.4</x:v>
+        <x:v>51.6</x:v>
       </x:c>
       <x:c r="S13" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C13,1)="딜",ISNUMBER(N13)),N13,"")</x:f>
-        <x:v>172</x:v>
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="T13" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0">
@@ -4381,34 +4412,34 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="G14" s="17" t="n">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H14" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G14)),NOT(ISNUMBER(H14))),"",G14*MAX(1,H14))</x:f>
-        <x:v>40</x:v>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G14)),NOT(ISNUMBER(H14))),"",G14*MAX(1,H14)+T14)</x:f>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J14" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G14)),NOT(ISNUMBER(H14))),"",IF(G14&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G14*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G14*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H14)))</x:f>
-        <x:v>43</x:v>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G14)),NOT(ISNUMBER(H14))),"",IF(G14&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G14*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G14*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H14)-1)+((1-'직업'!$D$5)*MAX(1,INT((G14+T14)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G14+T14)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
+        <x:v>53.75</x:v>
       </x:c>
       <x:c r="K14" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J14)),"",J14*IF(ISNUMBER(SEARCH("광역",$C14)),'범례'!$C$30,1))</x:f>
-        <x:v>86</x:v>
+        <x:v>107.5</x:v>
       </x:c>
       <x:c r="L14" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J14)),NOT(ISNUMBER(D14)),D14=0),"",J14/D14)</x:f>
-        <x:v>21.5</x:v>
+        <x:v>26.875</x:v>
       </x:c>
       <x:c r="M14" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K14)),NOT(ISNUMBER(D14)),D14=0),"",K14/D14)</x:f>
-        <x:v>43</x:v>
+        <x:v>53.75</x:v>
       </x:c>
       <x:c r="N14" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K14)),NOT(ISNUMBER(F14)),F14=0),"",K14/F14)</x:f>
-        <x:v>172</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="O14" s="17" t="n">
         <x:v>0</x:v>
@@ -4421,11 +4452,14 @@
       </x:c>
       <x:c r="R14" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C14,1)="딜",ISNUMBER(M14)),M14,"")</x:f>
-        <x:v>43</x:v>
+        <x:v>53.75</x:v>
       </x:c>
       <x:c r="S14" s="22" t="n">
         <x:f aca="0">IF(AND(LEFT($C14,1)="딜",ISNUMBER(N14)),N14,"")</x:f>
-        <x:v>172</x:v>
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="T14" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0">
@@ -4455,11 +4489,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G15)),NOT(ISNUMBER(H15))),"",G15*MAX(1,H15))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G15)),NOT(ISNUMBER(H15))),"",G15*MAX(1,H15)+T15)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J15" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G15)),NOT(ISNUMBER(H15))),"",IF(G15&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G15*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G15*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H15)))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G15)),NOT(ISNUMBER(H15))),"",IF(G15&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G15*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G15*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H15)-1)+((1-'직업'!$D$5)*MAX(1,INT((G15+T15)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G15+T15)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K15" s="41" t="n">
@@ -4492,6 +4526,9 @@
       </x:c>
       <x:c r="S15" s="22" t="str">
         <x:f aca="0">IF(AND(LEFT($C15,1)="딜",ISNUMBER(N15)),N15,"")</x:f>
+      </x:c>
+      <x:c r="T15" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0">
@@ -4515,34 +4552,34 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="G16" s="17" t="n">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H16" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G16)),NOT(ISNUMBER(H16))),"",G16*MAX(1,H16))</x:f>
-        <x:v>30</x:v>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G16)),NOT(ISNUMBER(H16))),"",G16*MAX(1,H16)+T16)</x:f>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J16" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G16)),NOT(ISNUMBER(H16))),"",IF(G16&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G16*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G16*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H16)))</x:f>
-        <x:v>32.25</x:v>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G16)),NOT(ISNUMBER(H16))),"",IF(G16&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G16*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G16*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H16)-1)+((1-'직업'!$D$5)*MAX(1,INT((G16+T16)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G16+T16)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K16" s="41" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(J16)),"",J16*IF(ISNUMBER(SEARCH("광역",$C16)),'범례'!$C$30,1))</x:f>
-        <x:v>32.25</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="L16" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(J16)),NOT(ISNUMBER(D16)),D16=0),"",J16/D16)</x:f>
-        <x:v>16.125</x:v>
+        <x:v>21.5</x:v>
       </x:c>
       <x:c r="M16" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K16)),NOT(ISNUMBER(D16)),D16=0),"",K16/D16)</x:f>
-        <x:v>16.125</x:v>
+        <x:v>21.5</x:v>
       </x:c>
       <x:c r="N16" s="22" t="n">
         <x:f aca="0">IF(OR(NOT(ISNUMBER(K16)),NOT(ISNUMBER(F16)),F16=0),"",K16/F16)</x:f>
-        <x:v>80.625</x:v>
+        <x:v>107.5</x:v>
       </x:c>
       <x:c r="O16" s="17" t="n">
         <x:v>0</x:v>
@@ -4558,6 +4595,9 @@
       </x:c>
       <x:c r="S16" s="22" t="str">
         <x:f aca="0">IF(AND(LEFT($C16,1)="딜",ISNUMBER(N16)),N16,"")</x:f>
+      </x:c>
+      <x:c r="T16" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0">
@@ -4587,11 +4627,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I17" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G17)),NOT(ISNUMBER(H17))),"",G17*MAX(1,H17))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G17)),NOT(ISNUMBER(H17))),"",G17*MAX(1,H17)+T17)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J17" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G17)),NOT(ISNUMBER(H17))),"",IF(G17&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G17*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G17*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H17)))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G17)),NOT(ISNUMBER(H17))),"",IF(G17&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G17*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G17*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H17)-1)+((1-'직업'!$D$5)*MAX(1,INT((G17+T17)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G17+T17)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K17" s="41" t="n">
@@ -4624,6 +4664,9 @@
       </x:c>
       <x:c r="S17" s="22" t="str">
         <x:f aca="0">IF(AND(LEFT($C17,1)="딜",ISNUMBER(N17)),N17,"")</x:f>
+      </x:c>
+      <x:c r="T17" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0">
@@ -4653,11 +4696,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I18" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G18)),NOT(ISNUMBER(H18))),"",G18*MAX(1,H18))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G18)),NOT(ISNUMBER(H18))),"",G18*MAX(1,H18)+T18)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J18" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G18)),NOT(ISNUMBER(H18))),"",IF(G18&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G18*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G18*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*MAX(1,H18)))</x:f>
+        <x:f aca="0">IF(OR(NOT(ISNUMBER(G18)),NOT(ISNUMBER(H18))),"",IF(G18&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G18*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G18*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H18)-1)+((1-'직업'!$D$5)*MAX(1,INT((G18+T18)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G18+T18)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K18" s="41" t="n">
@@ -4690,6 +4733,9 @@
       </x:c>
       <x:c r="S18" s="22" t="str">
         <x:f aca="0">IF(AND(LEFT($C18,1)="딜",ISNUMBER(N18)),N18,"")</x:f>
+      </x:c>
+      <x:c r="T18" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0">
@@ -4703,7 +4749,7 @@
       </x:c>
       <x:c r="B23" s="22" t="n">
         <x:f aca="0">IFERROR(MAX(R5:R18),"")</x:f>
-        <x:v>65.40833333333333</x:v>
+        <x:v>57.333333333333336</x:v>
       </x:c>
       <x:c r="C23" s="25" t="s">
         <x:v>69</x:v>
@@ -4715,7 +4761,7 @@
       </x:c>
       <x:c r="B24" s="22" t="n">
         <x:f aca="0">IFERROR(MIN(R5:R18),"")</x:f>
-        <x:v>26.875</x:v>
+        <x:v>32.25</x:v>
       </x:c>
       <x:c r="C24" s="25"/>
     </x:row>
@@ -4725,7 +4771,7 @@
       </x:c>
       <x:c r="B25" s="19" t="n">
         <x:f aca="0">IFERROR(B23/B24,"")</x:f>
-        <x:v>2.433798449612403</x:v>
+        <x:v>1.777777777777778</x:v>
       </x:c>
       <x:c r="C25" s="25" t="s">
         <x:v>72</x:v>
@@ -4737,7 +4783,7 @@
       </x:c>
       <x:c r="B26" s="22" t="n">
         <x:f aca="0">IFERROR(MAX(S5:S18),"")</x:f>
-        <x:v>322.5</x:v>
+        <x:v>349.375</x:v>
       </x:c>
       <x:c r="C26" s="25" t="s">
         <x:v>74</x:v>
@@ -4749,7 +4795,7 @@
       </x:c>
       <x:c r="B27" s="22" t="n">
         <x:f aca="0">IFERROR(MIN(S5:S18),"")</x:f>
-        <x:v>39.63636363636363</x:v>
+        <x:v>67.32142857142857</x:v>
       </x:c>
       <x:c r="C27" s="25"/>
     </x:row>
@@ -4759,7 +4805,7 @@
       </x:c>
       <x:c r="B28" s="19" t="n">
         <x:f aca="0">IFERROR(B26/B27,"")</x:f>
-        <x:v>8.136467889908257</x:v>
+        <x:v>5.189655172413794</x:v>
       </x:c>
       <x:c r="C28" s="25" t="s">
         <x:v>72</x:v>
@@ -5062,7 +5108,7 @@
       </x:c>
       <x:c r="F6" s="41" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$J:$J,MATCH($B6,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>53.75</x:v>
+        <x:v>96.75</x:v>
       </x:c>
       <x:c r="G6" s="27" t="str">
         <x:f aca="0">IF($A6&lt;=4,"손패","대기열")</x:f>
@@ -5204,7 +5250,7 @@
       </x:c>
       <x:c r="F9" s="41" t="n">
         <x:f aca="0">IFERROR(INDEX('스킬'!$J:$J,MATCH($B9,'스킬'!$B:$B,0)),"")</x:f>
-        <x:v>43.6</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G9" s="27" t="str">
         <x:f aca="0">IF($A9&lt;=4,"손패","대기열")</x:f>
@@ -5436,7 +5482,7 @@
       </x:c>
       <x:c r="B19" s="41" t="n">
         <x:f aca="0">SUM(F5:F12)</x:f>
-        <x:v>527.8</x:v>
+        <x:v>613.2</x:v>
       </x:c>
       <x:c r="D19" s="38"/>
       <x:c r="E19" s="39"/>
@@ -5454,7 +5500,7 @@
       </x:c>
       <x:c r="B20" s="41" t="n">
         <x:f aca="0">IFERROR(B19/B17,"")</x:f>
-        <x:v>17.59333333333333</x:v>
+        <x:v>20.44</x:v>
       </x:c>
       <x:c r="D20" s="38" t="str">
         <x:v>기절·초과피해·입력 순서 미포함; 실측 아님</x:v>
@@ -5756,7 +5802,7 @@
       </x:c>
       <x:c r="I5" s="22" t="n">
         <x:f aca="0">IFERROR(C5/'덱시뮬'!$B$20,"")</x:f>
-        <x:v>19.893899204244036</x:v>
+        <x:v>17.123287671232877</x:v>
       </x:c>
       <x:c r="J5" s="20" t="str">
         <x:v>일반 공격. 필요하면 차단 가능</x:v>
@@ -5790,7 +5836,7 @@
       </x:c>
       <x:c r="I6" s="22" t="n">
         <x:f aca="0">IFERROR(C6/'덱시뮬'!$B$20,"")</x:f>
-        <x:v>17.051913603637743</x:v>
+        <x:v>14.677103718199607</x:v>
       </x:c>
       <x:c r="J6" s="20" t="s">
         <x:v>110</x:v>
@@ -5824,7 +5870,7 @@
       </x:c>
       <x:c r="I7" s="22" t="n">
         <x:f aca="0">IFERROR(C7/'덱시뮬'!$B$20,"")</x:f>
-        <x:v>28.419856006062908</x:v>
+        <x:v>24.46183953033268</x:v>
       </x:c>
       <x:c r="J7" s="20" t="str">
         <x:v>빨강: 방어력 20 기준 200. 방어도 보유 시 100 후 흡수</x:v>
@@ -5858,7 +5904,7 @@
       </x:c>
       <x:c r="I8" s="22" t="n">
         <x:f aca="0">IF(NOT(ISNUMBER(C8)),"",C8/'덱시뮬'!$B$20)</x:f>
-        <x:v>45.47176960970065</x:v>
+        <x:v>39.138943248532286</x:v>
       </x:c>
       <x:c r="J8" s="20" t="str">
         <x:v>D 데이터 생성. 전투 편성 미연결</x:v>

--- a/Docs/밸런스시트.xlsx
+++ b/Docs/밸런스시트.xlsx
@@ -5793,7 +5793,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G5" s="17" t="n">
-        <x:v>2.5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H5" s="11" t="inlineStr">
         <x:is>
@@ -5829,7 +5829,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G6" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>3.6</x:v>
       </x:c>
       <x:c r="H6" s="17" t="s">
         <x:v>109</x:v>
@@ -5863,7 +5863,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G7" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="H7" s="17" t="s">
         <x:v>112</x:v>
@@ -5897,7 +5897,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G8" s="17" t="n">
-        <x:v>3.5</x:v>
+        <x:v>4.2</x:v>
       </x:c>
       <x:c r="H8" s="17" t="str">
         <x:v>초록·주황 가능</x:v>

--- a/Docs/밸런스시트.xlsx
+++ b/Docs/밸런스시트.xlsx
@@ -4516,7 +4516,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P15" s="17" t="n">
-        <x:v>2.5</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="Q15" s="20" t="str">
         <x:v>시작 덱. 일반 시전, 캐스팅 중 대상만</x:v>
@@ -4585,7 +4585,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P16" s="17" t="n">
-        <x:v>2.5</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="Q16" s="20" t="str">
         <x:v>보상. 일반 시전, 피해+차단</x:v>
@@ -5793,7 +5793,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G5" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="H5" s="11" t="inlineStr">
         <x:is>
@@ -5829,7 +5829,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G6" s="17" t="n">
-        <x:v>3.6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H6" s="17" t="s">
         <x:v>109</x:v>
@@ -5863,7 +5863,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G7" s="17" t="n">
-        <x:v>4.8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H7" s="17" t="s">
         <x:v>112</x:v>
@@ -5897,7 +5897,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G8" s="17" t="n">
-        <x:v>4.2</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="H8" s="17" t="str">
         <x:v>초록·주황 가능</x:v>

--- a/Docs/밸런스시트.xlsx
+++ b/Docs/밸런스시트.xlsx
@@ -3261,304 +3261,306 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="46" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="52" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="20.100000381469727" hidden="0">
-      <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="15" hidden="0">
-      <x:c r="A2" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="15" hidden="0">
-      <x:c r="A4" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B4" s="4"/>
-    </x:row>
-    <x:row r="5" ht="15" hidden="0">
-      <x:c r="A5" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="15" hidden="0">
-      <x:c r="A6" s="7" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="6" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="15" hidden="0">
-      <x:c r="A7" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B7" s="6" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="15" hidden="0">
-      <x:c r="A8" s="7"/>
-      <x:c r="B8" s="4"/>
-    </x:row>
-    <x:row r="9" ht="15" hidden="0">
-      <x:c r="A9" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B9" s="4"/>
-    </x:row>
-    <x:row r="10" ht="15" hidden="0">
-      <x:c r="A10" s="7" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B10" s="6" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="15" hidden="0">
-      <x:c r="A11" s="7" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B11" s="6" t="str">
-        <x:v>구현 스킬 14종 계산. 10 A20·A23·A29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="29.850000381469727" hidden="0">
-      <x:c r="A12" s="7" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B12" s="6" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="15" hidden="0">
-      <x:c r="A13" s="7" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B13" s="6" t="str">
-        <x:v>A·B·C·D 데이터. 전체 패턴·편성은 04 참조</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="15" hidden="0">
-      <x:c r="A14" s="7" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B14" s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="15" hidden="0">
-      <x:c r="A17" s="3" t="str">
-        <x:v>공용 가정 — 현재 프로토타입 계산</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="31.5" hidden="0" customHeight="1">
-      <x:c r="A18" s="8" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B18" s="8" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C18" s="8" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D18" s="8" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="15" hidden="0">
-      <x:c r="A19" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B19" s="10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C19" s="11" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="D19" s="12" t="str">
-        <x:v>10 A25·T21. 패시브 없는 기본값</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="15" hidden="0">
-      <x:c r="A20" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B20" s="10" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C20" s="11" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D20" s="12" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="15" hidden="0">
-      <x:c r="A21" s="9" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B21" s="10" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C21" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D21" s="12" t="str">
-        <x:v>현재 A·B·C 방어력 (10 N항)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="15" hidden="0">
-      <x:c r="A22" s="9" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B22" s="10" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C22" s="13" t="n">
-        <x:f aca="0">C21/(C21+C20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D22" s="10" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="15" hidden="0">
-      <x:c r="A23" s="9" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B23" s="10" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C23" s="11" t="n">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="D23" s="12" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="15" hidden="0">
-      <x:c r="A24" s="9" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B24" s="10" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C24" s="11" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D24" s="12" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="15" hidden="0">
-      <x:c r="A25" s="9" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B25" s="12"/>
-      <x:c r="C25" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D25" s="12" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="29.850000381469727" hidden="0">
-      <x:c r="A26" s="9" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B26" s="10" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C26" s="11" t="n">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="D26" s="10" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="15" hidden="0">
-      <x:c r="A27" s="9" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B27" s="10" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C27" s="11" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D27" s="12" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="15" hidden="0">
-      <x:c r="A28" s="9" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B28" s="10" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C28" s="11" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D28" s="12" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="15" hidden="0">
-      <x:c r="A29" s="9" t="str">
-        <x:v>기본 포션 횟수</x:v>
-      </x:c>
-      <x:c r="B29" s="10" t="str">
-        <x:v>최대 HP의 30%씩 회복</x:v>
-      </x:c>
-      <x:c r="C29" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D29" s="10" t="str">
-        <x:v>10 A46. 시작 3/3, PS01 최대치·현재 +1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="15" hidden="0">
-      <x:c r="A30" s="9" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B30" s="10" t="str">
-        <x:v>튜토리얼 제외 A+B / C / A+B+C</x:v>
-      </x:c>
-      <x:c r="C30" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D30" s="10" t="str">
-        <x:v>(2+1+3)/3=2. 10 A32·A34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="15" hidden="0">
-      <x:c r="A31" s="14" t="str">
-        <x:v>수치 원본: Docs/10 결정 로그. 이 파일은 계산 도구이며 실측 결과와 구분합니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="15" hidden="0">
-      <x:c r="A32" s="14" t="str">
-        <x:v>2026-10-07: 포션 3/3·전투 구성·적 피해 갱신. 10 A32·A33·A38·A43·A46.</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="26" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="46" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="52" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20.100000381469727" hidden="0">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="15" hidden="0">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="15" hidden="0">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" ht="15" hidden="0">
+      <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="15" hidden="0">
+      <c r="A6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" ht="15" hidden="0">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" ht="15" hidden="0">
+      <c r="A8" s="7"/>
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" ht="15" hidden="0">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="4"/>
+    </row>
+    <row r="10" ht="15" hidden="0">
+      <c r="A10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" ht="15" hidden="0">
+      <c r="A11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>구현 스킬 15종 계산. SK15 비전 배리어 추가(2026-10-20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="29.850000381469727" hidden="0">
+      <c r="A12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" ht="15" hidden="0">
+      <c r="A13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="6" t="str">
+        <v>A·B·C·D 데이터. 전체 패턴·편성은 04 참조</v>
+      </c>
+    </row>
+    <row r="14" ht="15" hidden="0">
+      <c r="A14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" ht="15" hidden="0">
+      <c r="A17" s="3" t="str">
+        <v>공용 가정 — 현재 프로토타입 계산</v>
+      </c>
+    </row>
+    <row r="18" ht="31.5" hidden="0" customHeight="1">
+      <c r="A18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" ht="15" hidden="0">
+      <c r="A19" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D19" s="12" t="str">
+        <v>10 A25·T21. 패시브 없는 기본값</v>
+      </c>
+    </row>
+    <row r="20" ht="15" hidden="0">
+      <c r="A20" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" ht="15" hidden="0">
+      <c r="A21" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="12" t="str">
+        <v>현재 A·B·C 방어력 (10 N항)</v>
+      </c>
+    </row>
+    <row r="22" ht="15" hidden="0">
+      <c r="A22" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <f aca="0">C21/(C21+C20)</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" ht="15" hidden="0">
+      <c r="A23" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" ht="15" hidden="0">
+      <c r="A24" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" ht="15" hidden="0">
+      <c r="A25" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="12"/>
+      <c r="C25" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" ht="29.850000381469727" hidden="0">
+      <c r="A26" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" ht="15" hidden="0">
+      <c r="A27" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" ht="15" hidden="0">
+      <c r="A28" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>180</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" ht="15" hidden="0">
+      <c r="A29" s="9" t="str">
+        <v>기본 포션 횟수</v>
+      </c>
+      <c r="B29" s="10" t="str">
+        <v>최대 HP의 30%씩 회복</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="10" t="str">
+        <v>10 A46. 시작 3/3, PS01 최대치·현재 +1</v>
+      </c>
+    </row>
+    <row r="30" ht="15" hidden="0">
+      <c r="A30" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="10" t="str">
+        <v>튜토리얼 제외 A+B / C / A+B+C</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="10" t="str">
+        <v>(2+1+3)/3=2. 10 A32·A34</v>
+      </c>
+    </row>
+    <row r="31" ht="15" hidden="0">
+      <c r="A31" s="14" t="str">
+        <v>수치 원본: Docs/10 결정 로그. 이 파일은 계산 도구이며 실측 결과와 구분합니다.</v>
+      </c>
+    </row>
+    <row r="32" ht="15" hidden="0">
+      <c r="A32" s="14" t="str">
+        <v>2026-10-07: 포션 3/3·전투 구성·적 피해 갱신. 10 A32·A33·A38·A43·A46.</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3659,1322 +3661,1403 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="8" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="7" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
-    <x:col min="10" max="13" width="14" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="13" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="12" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="10" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="42" hidden="0" customWidth="1"/>
-    <x:col min="18" max="19" width="13" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="20" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="20.100000381469727" hidden="0">
-      <x:c r="A1" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="15" hidden="0">
-      <x:c r="A2" s="2" t="str">
-        <x:v>현재 구현 14종. 10 A20·A23·A25·A29 기준, 패시브·과잉 피해·시전 취소 제외.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="31.5" hidden="0" customHeight="1">
-      <x:c r="A4" s="16" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B4" s="8" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D4" s="8" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E4" s="8" t="str">
-        <x:v>시전/채널(초)</x:v>
-      </x:c>
-      <x:c r="F4" s="8" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G4" s="8" t="str">
-        <x:v>1타 피해</x:v>
-      </x:c>
-      <x:c r="H4" s="8" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="I4" s="8" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="J4" s="8" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="K4" s="8" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L4" s="8" t="str">
-        <x:v>코스트당 (1체)</x:v>
-      </x:c>
-      <x:c r="M4" s="8" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="N4" s="8" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="O4" s="8" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="P4" s="8" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="Q4" s="8" t="str">
-        <x:v>구현·발동 방식</x:v>
-      </x:c>
-      <x:c r="R4" s="8" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="S4" s="8" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="T4" s="8" t="str">
-        <x:v>마지막 추가 피해</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="15" hidden="0">
-      <x:c r="A5" s="11" t="str">
-        <x:v>SK01</x:v>
-      </x:c>
-      <x:c r="B5" s="17" t="str">
-        <x:v>파이어볼</x:v>
-      </x:c>
-      <x:c r="C5" s="17" t="str">
-        <x:v>딜/단일</x:v>
-      </x:c>
-      <x:c r="D5" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F5" s="22" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(E5)),"",MAX(E5,'범례'!$C$26))</x:f>
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="G5" s="17" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H5" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I5" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(H5))),"",G5*MAX(1,H5)+T5)</x:f>
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J5" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(H5))),"",IF(G5&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G5*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G5*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H5)-1)+((1-'직업'!$D$5)*MAX(1,INT((G5+T5)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G5+T5)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
-        <x:v>32.25</x:v>
-      </x:c>
-      <x:c r="K5" s="41" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(J5)),"",J5*IF(ISNUMBER(SEARCH("광역",$C5)),'범례'!$C$30,1))</x:f>
-        <x:v>32.25</x:v>
-      </x:c>
-      <x:c r="L5" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(J5)),NOT(ISNUMBER(D5)),D5=0),"",J5/D5)</x:f>
-        <x:v>32.25</x:v>
-      </x:c>
-      <x:c r="M5" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K5)),NOT(ISNUMBER(D5)),D5=0),"",K5/D5)</x:f>
-        <x:v>32.25</x:v>
-      </x:c>
-      <x:c r="N5" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K5)),NOT(ISNUMBER(F5)),F5=0),"",K5/F5)</x:f>
-        <x:v>80.625</x:v>
-      </x:c>
-      <x:c r="O5" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P5" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q5" s="20" t="str">
-        <x:v>시작 덱. 일반 시전</x:v>
-      </x:c>
-      <x:c r="R5" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C5,1)="딜",ISNUMBER(M5)),M5,"")</x:f>
-        <x:v>32.25</x:v>
-      </x:c>
-      <x:c r="S5" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C5,1)="딜",ISNUMBER(N5)),N5,"")</x:f>
-        <x:v>80.625</x:v>
-      </x:c>
-      <x:c r="T5" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="15" hidden="0">
-      <x:c r="A6" s="11" t="str">
-        <x:v>SK02</x:v>
-      </x:c>
-      <x:c r="B6" s="17" t="str">
-        <x:v>아이스애로우</x:v>
-      </x:c>
-      <x:c r="C6" s="17" t="str">
-        <x:v>딜/단일</x:v>
-      </x:c>
-      <x:c r="D6" s="17" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E6" s="17" t="n">
-        <x:v>2.8</x:v>
-      </x:c>
-      <x:c r="F6" s="22" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(E6)),"",MAX(E6,'범례'!$C$26))</x:f>
-        <x:v>2.8</x:v>
-      </x:c>
-      <x:c r="G6" s="17" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H6" s="17" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I6" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G6)),NOT(ISNUMBER(H6))),"",G6*MAX(1,H6)+T6)</x:f>
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="J6" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G6)),NOT(ISNUMBER(H6))),"",IF(G6&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G6*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G6*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H6)-1)+((1-'직업'!$D$5)*MAX(1,INT((G6+T6)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G6+T6)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
-        <x:v>188.5</x:v>
-      </x:c>
-      <x:c r="K6" s="41" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(J6)),"",J6*IF(ISNUMBER(SEARCH("광역",$C6)),'범례'!$C$30,1))</x:f>
-        <x:v>188.5</x:v>
-      </x:c>
-      <x:c r="L6" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(J6)),NOT(ISNUMBER(D6)),D6=0),"",J6/D6)</x:f>
-        <x:v>37.7</x:v>
-      </x:c>
-      <x:c r="M6" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K6)),NOT(ISNUMBER(D6)),D6=0),"",K6/D6)</x:f>
-        <x:v>37.7</x:v>
-      </x:c>
-      <x:c r="N6" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K6)),NOT(ISNUMBER(F6)),F6=0),"",K6/F6)</x:f>
-        <x:v>67.32142857142857</x:v>
-      </x:c>
-      <x:c r="O6" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P6" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q6" s="24" t="str">
-        <x:v>시작 덱. 채널링 0.5초마다, 사망 후딜 0.3초</x:v>
-      </x:c>
-      <x:c r="R6" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C6,1)="딜",ISNUMBER(M6)),M6,"")</x:f>
-        <x:v>37.7</x:v>
-      </x:c>
-      <x:c r="S6" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C6,1)="딜",ISNUMBER(N6)),N6,"")</x:f>
-        <x:v>67.32142857142857</x:v>
-      </x:c>
-      <x:c r="T6" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="15" hidden="0">
-      <x:c r="A7" s="11" t="str">
-        <x:v>SK03</x:v>
-      </x:c>
-      <x:c r="B7" s="17" t="str">
-        <x:v>매직 커터</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="str">
-        <x:v>딜/단일</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E7" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F7" s="22" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(E7)),"",MAX(E7,'범례'!$C$26))</x:f>
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H7" s="17" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I7" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G7)),NOT(ISNUMBER(H7))),"",G7*MAX(1,H7)+T7)</x:f>
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="J7" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G7)),NOT(ISNUMBER(H7))),"",IF(G7&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G7*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G7*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H7)-1)+((1-'직업'!$D$5)*MAX(1,INT((G7+T7)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G7+T7)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
-        <x:v>64.5</x:v>
-      </x:c>
-      <x:c r="K7" s="41" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(J7)),"",J7*IF(ISNUMBER(SEARCH("광역",$C7)),'범례'!$C$30,1))</x:f>
-        <x:v>64.5</x:v>
-      </x:c>
-      <x:c r="L7" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(J7)),NOT(ISNUMBER(D7)),D7=0),"",J7/D7)</x:f>
-        <x:v>32.25</x:v>
-      </x:c>
-      <x:c r="M7" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K7)),NOT(ISNUMBER(D7)),D7=0),"",K7/D7)</x:f>
-        <x:v>32.25</x:v>
-      </x:c>
-      <x:c r="N7" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K7)),NOT(ISNUMBER(F7)),F7=0),"",K7/F7)</x:f>
-        <x:v>161.25</x:v>
-      </x:c>
-      <x:c r="O7" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P7" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q7" s="24" t="str">
-        <x:v>시작 덱. 일반 시전</x:v>
-      </x:c>
-      <x:c r="R7" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C7,1)="딜",ISNUMBER(M7)),M7,"")</x:f>
-        <x:v>32.25</x:v>
-      </x:c>
-      <x:c r="S7" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C7,1)="딜",ISNUMBER(N7)),N7,"")</x:f>
-        <x:v>161.25</x:v>
-      </x:c>
-      <x:c r="T7" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="15" hidden="0">
-      <x:c r="A8" s="11" t="str">
-        <x:v>SK04</x:v>
-      </x:c>
-      <x:c r="B8" s="17" t="str">
-        <x:v>파이어 필라</x:v>
-      </x:c>
-      <x:c r="C8" s="17" t="str">
-        <x:v>딜/광역</x:v>
-      </x:c>
-      <x:c r="D8" s="17" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E8" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F8" s="22" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(E8)),"",MAX(E8,'범례'!$C$26))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G8" s="17" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H8" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I8" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G8)),NOT(ISNUMBER(H8))),"",G8*MAX(1,H8)+T8)</x:f>
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="J8" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G8)),NOT(ISNUMBER(H8))),"",IF(G8&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G8*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G8*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H8)-1)+((1-'직업'!$D$5)*MAX(1,INT((G8+T8)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G8+T8)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
-        <x:v>96.75</x:v>
-      </x:c>
-      <x:c r="K8" s="41" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(J8)),"",J8*IF(ISNUMBER(SEARCH("광역",$C8)),'범례'!$C$30,1))</x:f>
-        <x:v>193.5</x:v>
-      </x:c>
-      <x:c r="L8" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(J8)),NOT(ISNUMBER(D8)),D8=0),"",J8/D8)</x:f>
-        <x:v>24.1875</x:v>
-      </x:c>
-      <x:c r="M8" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K8)),NOT(ISNUMBER(D8)),D8=0),"",K8/D8)</x:f>
-        <x:v>48.375</x:v>
-      </x:c>
-      <x:c r="N8" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K8)),NOT(ISNUMBER(F8)),F8=0),"",K8/F8)</x:f>
-        <x:v>193.5</x:v>
-      </x:c>
-      <x:c r="O8" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P8" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q8" s="24" t="str">
-        <x:v>시작 덱. 일반 시전</x:v>
-      </x:c>
-      <x:c r="R8" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C8,1)="딜",ISNUMBER(M8)),M8,"")</x:f>
-        <x:v>48.375</x:v>
-      </x:c>
-      <x:c r="S8" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C8,1)="딜",ISNUMBER(N8)),N8,"")</x:f>
-        <x:v>193.5</x:v>
-      </x:c>
-      <x:c r="T8" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="15" hidden="0">
-      <x:c r="A9" s="11" t="str">
-        <x:v>SK05</x:v>
-      </x:c>
-      <x:c r="B9" s="17" t="str">
-        <x:v>라이트닝 스피어</x:v>
-      </x:c>
-      <x:c r="C9" s="17" t="str">
-        <x:v>딜/단일</x:v>
-      </x:c>
-      <x:c r="D9" s="17" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E9" s="17" t="n">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="F9" s="22" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(E9)),"",MAX(E9,'범례'!$C$26))</x:f>
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="G9" s="17" t="n">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H9" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I9" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G9)),NOT(ISNUMBER(H9))),"",G9*MAX(1,H9)+T9)</x:f>
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="J9" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G9)),NOT(ISNUMBER(H9))),"",IF(G9&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G9*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G9*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H9)-1)+((1-'직업'!$D$5)*MAX(1,INT((G9+T9)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G9+T9)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
-        <x:v>145.2</x:v>
-      </x:c>
-      <x:c r="K9" s="41" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(J9)),"",J9*IF(ISNUMBER(SEARCH("광역",$C9)),'범례'!$C$30,1))</x:f>
-        <x:v>145.2</x:v>
-      </x:c>
-      <x:c r="L9" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(J9)),NOT(ISNUMBER(D9)),D9=0),"",J9/D9)</x:f>
-        <x:v>36.3</x:v>
-      </x:c>
-      <x:c r="M9" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K9)),NOT(ISNUMBER(D9)),D9=0),"",K9/D9)</x:f>
-        <x:v>36.3</x:v>
-      </x:c>
-      <x:c r="N9" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K9)),NOT(ISNUMBER(F9)),F9=0),"",K9/F9)</x:f>
-        <x:v>181.49999999999997</x:v>
-      </x:c>
-      <x:c r="O9" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P9" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q9" s="24" t="str">
-        <x:v>시작 덱. 일반 시전</x:v>
-      </x:c>
-      <x:c r="R9" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C9,1)="딜",ISNUMBER(M9)),M9,"")</x:f>
-        <x:v>36.3</x:v>
-      </x:c>
-      <x:c r="S9" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C9,1)="딜",ISNUMBER(N9)),N9,"")</x:f>
-        <x:v>181.49999999999997</x:v>
-      </x:c>
-      <x:c r="T9" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="15" hidden="0">
-      <x:c r="A10" s="11" t="str">
-        <x:v>SK06</x:v>
-      </x:c>
-      <x:c r="B10" s="17" t="str">
-        <x:v>매직 스파크</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="str">
-        <x:v>딜/광역</x:v>
-      </x:c>
-      <x:c r="D10" s="17" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E10" s="17" t="n">
-        <x:v>2.2</x:v>
-      </x:c>
-      <x:c r="F10" s="22" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(E10)),"",MAX(E10,'범례'!$C$26))</x:f>
-        <x:v>2.2</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H10" s="17" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I10" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G10)),NOT(ISNUMBER(H10))),"",G10*MAX(1,H10)+T10)</x:f>
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="J10" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G10)),NOT(ISNUMBER(H10))),"",IF(G10&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G10*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G10*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H10)-1)+((1-'직업'!$D$5)*MAX(1,INT((G10+T10)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G10+T10)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="K10" s="41" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(J10)),"",J10*IF(ISNUMBER(SEARCH("광역",$C10)),'범례'!$C$30,1))</x:f>
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="L10" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(J10)),NOT(ISNUMBER(D10)),D10=0),"",J10/D10)</x:f>
-        <x:v>28.666666666666668</x:v>
-      </x:c>
-      <x:c r="M10" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K10)),NOT(ISNUMBER(D10)),D10=0),"",K10/D10)</x:f>
-        <x:v>57.333333333333336</x:v>
-      </x:c>
-      <x:c r="N10" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K10)),NOT(ISNUMBER(F10)),F10=0),"",K10/F10)</x:f>
-        <x:v>78.18181818181817</x:v>
-      </x:c>
-      <x:c r="O10" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P10" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q10" s="24" t="str">
-        <x:v>시작 덱. 채널링 0.25초마다</x:v>
-      </x:c>
-      <x:c r="R10" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C10,1)="딜",ISNUMBER(M10)),M10,"")</x:f>
-        <x:v>57.333333333333336</x:v>
-      </x:c>
-      <x:c r="S10" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C10,1)="딜",ISNUMBER(N10)),N10,"")</x:f>
-        <x:v>78.18181818181817</x:v>
-      </x:c>
-      <x:c r="T10" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="15" hidden="0">
-      <x:c r="A11" s="11" t="str">
-        <x:v>SK07</x:v>
-      </x:c>
-      <x:c r="B11" s="17" t="str">
-        <x:v>매직 임팩트</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="str">
-        <x:v>딜/단일</x:v>
-      </x:c>
-      <x:c r="D11" s="17" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E11" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F11" s="22" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(E11)),"",MAX(E11,'범례'!$C$26))</x:f>
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H11" s="17" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I11" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G11)),NOT(ISNUMBER(H11))),"",G11*MAX(1,H11)+T11)</x:f>
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="J11" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G11)),NOT(ISNUMBER(H11))),"",IF(G11&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G11*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G11*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H11)-1)+((1-'직업'!$D$5)*MAX(1,INT((G11+T11)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G11+T11)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
-        <x:v>139.75</x:v>
-      </x:c>
-      <x:c r="K11" s="41" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(J11)),"",J11*IF(ISNUMBER(SEARCH("광역",$C11)),'범례'!$C$30,1))</x:f>
-        <x:v>139.75</x:v>
-      </x:c>
-      <x:c r="L11" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(J11)),NOT(ISNUMBER(D11)),D11=0),"",J11/D11)</x:f>
-        <x:v>46.583333333333336</x:v>
-      </x:c>
-      <x:c r="M11" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K11)),NOT(ISNUMBER(D11)),D11=0),"",K11/D11)</x:f>
-        <x:v>46.583333333333336</x:v>
-      </x:c>
-      <x:c r="N11" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K11)),NOT(ISNUMBER(F11)),F11=0),"",K11/F11)</x:f>
-        <x:v>349.375</x:v>
-      </x:c>
-      <x:c r="O11" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P11" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q11" s="24" t="str">
-        <x:v>보상. 일반 시전</x:v>
-      </x:c>
-      <x:c r="R11" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C11,1)="딜",ISNUMBER(M11)),M11,"")</x:f>
-        <x:v>46.583333333333336</x:v>
-      </x:c>
-      <x:c r="S11" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C11,1)="딜",ISNUMBER(N11)),N11,"")</x:f>
-        <x:v>349.375</x:v>
-      </x:c>
-      <x:c r="T11" s="17" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="15" hidden="0">
-      <x:c r="A12" s="11" t="str">
-        <x:v>SK08</x:v>
-      </x:c>
-      <x:c r="B12" s="17" t="str">
-        <x:v>저지먼트</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="str">
-        <x:v>딜/단일</x:v>
-      </x:c>
-      <x:c r="D12" s="17" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E12" s="17" t="n">
-        <x:v>2.75</x:v>
-      </x:c>
-      <x:c r="F12" s="41" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(E12)),"",MAX(E12,'범례'!$C$26))</x:f>
-        <x:v>2.75</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="n">
-        <x:v>365</x:v>
-      </x:c>
-      <x:c r="H12" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I12" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"",G12*MAX(1,H12)+T12)</x:f>
-        <x:v>365</x:v>
-      </x:c>
-      <x:c r="J12" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"",IF(G12&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G12*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G12*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H12)-1)+((1-'직업'!$D$5)*MAX(1,INT((G12+T12)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G12+T12)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
-        <x:v>392.45</x:v>
-      </x:c>
-      <x:c r="K12" s="41" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(J12)),"",J12*IF(ISNUMBER(SEARCH("광역",$C12)),'범례'!$C$30,1))</x:f>
-        <x:v>392.45</x:v>
-      </x:c>
-      <x:c r="L12" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(J12)),NOT(ISNUMBER(D12)),D12=0),"",J12/D12)</x:f>
-        <x:v>56.06428571428571</x:v>
-      </x:c>
-      <x:c r="M12" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K12)),NOT(ISNUMBER(D12)),D12=0),"",K12/D12)</x:f>
-        <x:v>56.06428571428571</x:v>
-      </x:c>
-      <x:c r="N12" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K12)),NOT(ISNUMBER(F12)),F12=0),"",K12/F12)</x:f>
-        <x:v>142.70909090909092</x:v>
-      </x:c>
-      <x:c r="O12" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P12" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q12" s="24" t="str">
-        <x:v>보상. 일반 시전</x:v>
-      </x:c>
-      <x:c r="R12" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C12,1)="딜",ISNUMBER(M12)),M12,"")</x:f>
-        <x:v>56.06428571428571</x:v>
-      </x:c>
-      <x:c r="S12" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C12,1)="딜",ISNUMBER(N12)),N12,"")</x:f>
-        <x:v>142.70909090909092</x:v>
-      </x:c>
-      <x:c r="T12" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="15" hidden="0">
-      <x:c r="A13" s="17" t="str">
-        <x:v>SK09</x:v>
-      </x:c>
-      <x:c r="B13" s="17" t="str">
-        <x:v>블리자드</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="str">
-        <x:v>딜/광역</x:v>
-      </x:c>
-      <x:c r="D13" s="17" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E13" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F13" s="22" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(E13)),"",MAX(E13,'범례'!$C$26))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H13" s="17" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I13" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"",G13*MAX(1,H13)+T13)</x:f>
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="J13" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"",IF(G13&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G13*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G13*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H13)-1)+((1-'직업'!$D$5)*MAX(1,INT((G13+T13)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G13+T13)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="K13" s="41" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(J13)),"",J13*IF(ISNUMBER(SEARCH("광역",$C13)),'범례'!$C$30,1))</x:f>
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="L13" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(J13)),NOT(ISNUMBER(D13)),D13=0),"",J13/D13)</x:f>
-        <x:v>25.8</x:v>
-      </x:c>
-      <x:c r="M13" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K13)),NOT(ISNUMBER(D13)),D13=0),"",K13/D13)</x:f>
-        <x:v>51.6</x:v>
-      </x:c>
-      <x:c r="N13" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K13)),NOT(ISNUMBER(F13)),F13=0),"",K13/F13)</x:f>
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="O13" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P13" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q13" s="20" t="str">
-        <x:v>보상. 일반 시전, 광역</x:v>
-      </x:c>
-      <x:c r="R13" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C13,1)="딜",ISNUMBER(M13)),M13,"")</x:f>
-        <x:v>51.6</x:v>
-      </x:c>
-      <x:c r="S13" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C13,1)="딜",ISNUMBER(N13)),N13,"")</x:f>
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="T13" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="15" hidden="0">
-      <x:c r="A14" s="17" t="str">
-        <x:v>SK10</x:v>
-      </x:c>
-      <x:c r="B14" s="17" t="str">
-        <x:v>다크 이럽션</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="str">
-        <x:v>딜/광역</x:v>
-      </x:c>
-      <x:c r="D14" s="17" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="F14" s="22" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(E14)),"",MAX(E14,'범례'!$C$26))</x:f>
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H14" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I14" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G14)),NOT(ISNUMBER(H14))),"",G14*MAX(1,H14)+T14)</x:f>
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="J14" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G14)),NOT(ISNUMBER(H14))),"",IF(G14&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G14*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G14*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H14)-1)+((1-'직업'!$D$5)*MAX(1,INT((G14+T14)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G14+T14)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
-        <x:v>53.75</x:v>
-      </x:c>
-      <x:c r="K14" s="41" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(J14)),"",J14*IF(ISNUMBER(SEARCH("광역",$C14)),'범례'!$C$30,1))</x:f>
-        <x:v>107.5</x:v>
-      </x:c>
-      <x:c r="L14" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(J14)),NOT(ISNUMBER(D14)),D14=0),"",J14/D14)</x:f>
-        <x:v>26.875</x:v>
-      </x:c>
-      <x:c r="M14" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K14)),NOT(ISNUMBER(D14)),D14=0),"",K14/D14)</x:f>
-        <x:v>53.75</x:v>
-      </x:c>
-      <x:c r="N14" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K14)),NOT(ISNUMBER(F14)),F14=0),"",K14/F14)</x:f>
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="O14" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P14" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q14" s="20" t="str">
-        <x:v>보상. 일반 시전</x:v>
-      </x:c>
-      <x:c r="R14" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C14,1)="딜",ISNUMBER(M14)),M14,"")</x:f>
-        <x:v>53.75</x:v>
-      </x:c>
-      <x:c r="S14" s="22" t="n">
-        <x:f aca="0">IF(AND(LEFT($C14,1)="딜",ISNUMBER(N14)),N14,"")</x:f>
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="T14" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="15" hidden="0">
-      <x:c r="A15" s="17" t="str">
-        <x:v>SK11</x:v>
-      </x:c>
-      <x:c r="B15" s="17" t="str">
-        <x:v>침묵</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="str">
-        <x:v>차단</x:v>
-      </x:c>
-      <x:c r="D15" s="17" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E15" s="17" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="F15" s="22" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(E15)),"",MAX(E15,'범례'!$C$26))</x:f>
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I15" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G15)),NOT(ISNUMBER(H15))),"",G15*MAX(1,H15)+T15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J15" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G15)),NOT(ISNUMBER(H15))),"",IF(G15&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G15*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G15*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H15)-1)+((1-'직업'!$D$5)*MAX(1,INT((G15+T15)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G15+T15)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K15" s="41" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(J15)),"",J15*IF(ISNUMBER(SEARCH("광역",$C15)),'범례'!$C$30,1))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L15" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(J15)),NOT(ISNUMBER(D15)),D15=0),"",J15/D15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M15" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K15)),NOT(ISNUMBER(D15)),D15=0),"",K15/D15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K15)),NOT(ISNUMBER(F15)),F15=0),"",K15/F15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O15" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P15" s="17" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="Q15" s="20" t="str">
-        <x:v>시작 덱. 일반 시전, 캐스팅 중 대상만</x:v>
-      </x:c>
-      <x:c r="R15" s="22" t="str">
-        <x:f aca="0">IF(AND(LEFT($C15,1)="딜",ISNUMBER(M15)),M15,"")</x:f>
-      </x:c>
-      <x:c r="S15" s="22" t="str">
-        <x:f aca="0">IF(AND(LEFT($C15,1)="딜",ISNUMBER(N15)),N15,"")</x:f>
-      </x:c>
-      <x:c r="T15" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="15" hidden="0">
-      <x:c r="A16" s="17" t="str">
-        <x:v>SK12</x:v>
-      </x:c>
-      <x:c r="B16" s="17" t="str">
-        <x:v>제압</x:v>
-      </x:c>
-      <x:c r="C16" s="17" t="str">
-        <x:v>차단</x:v>
-      </x:c>
-      <x:c r="D16" s="17" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E16" s="17" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="F16" s="22" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(E16)),"",MAX(E16,'범례'!$C$26))</x:f>
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="G16" s="17" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H16" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I16" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G16)),NOT(ISNUMBER(H16))),"",G16*MAX(1,H16)+T16)</x:f>
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="J16" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G16)),NOT(ISNUMBER(H16))),"",IF(G16&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G16*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G16*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H16)-1)+((1-'직업'!$D$5)*MAX(1,INT((G16+T16)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G16+T16)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="K16" s="41" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(J16)),"",J16*IF(ISNUMBER(SEARCH("광역",$C16)),'범례'!$C$30,1))</x:f>
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L16" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(J16)),NOT(ISNUMBER(D16)),D16=0),"",J16/D16)</x:f>
-        <x:v>21.5</x:v>
-      </x:c>
-      <x:c r="M16" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K16)),NOT(ISNUMBER(D16)),D16=0),"",K16/D16)</x:f>
-        <x:v>21.5</x:v>
-      </x:c>
-      <x:c r="N16" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K16)),NOT(ISNUMBER(F16)),F16=0),"",K16/F16)</x:f>
-        <x:v>107.5</x:v>
-      </x:c>
-      <x:c r="O16" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P16" s="17" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="Q16" s="20" t="str">
-        <x:v>보상. 일반 시전, 피해+차단</x:v>
-      </x:c>
-      <x:c r="R16" s="22" t="str">
-        <x:f aca="0">IF(AND(LEFT($C16,1)="딜",ISNUMBER(M16)),M16,"")</x:f>
-      </x:c>
-      <x:c r="S16" s="22" t="str">
-        <x:f aca="0">IF(AND(LEFT($C16,1)="딜",ISNUMBER(N16)),N16,"")</x:f>
-      </x:c>
-      <x:c r="T16" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="15" hidden="0">
-      <x:c r="A17" s="17" t="str">
-        <x:v>SK13</x:v>
-      </x:c>
-      <x:c r="B17" s="17" t="str">
-        <x:v>매직아머</x:v>
-      </x:c>
-      <x:c r="C17" s="17" t="str">
-        <x:v>방어</x:v>
-      </x:c>
-      <x:c r="D17" s="17" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E17" s="17" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="F17" s="22" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(E17)),"",MAX(E17,'범례'!$C$26))</x:f>
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="G17" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H17" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I17" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G17)),NOT(ISNUMBER(H17))),"",G17*MAX(1,H17)+T17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J17" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G17)),NOT(ISNUMBER(H17))),"",IF(G17&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G17*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G17*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H17)-1)+((1-'직업'!$D$5)*MAX(1,INT((G17+T17)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G17+T17)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K17" s="41" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(J17)),"",J17*IF(ISNUMBER(SEARCH("광역",$C17)),'범례'!$C$30,1))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L17" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(J17)),NOT(ISNUMBER(D17)),D17=0),"",J17/D17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M17" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K17)),NOT(ISNUMBER(D17)),D17=0),"",K17/D17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K17)),NOT(ISNUMBER(F17)),F17=0),"",K17/F17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O17" s="17" t="n">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="P17" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q17" s="20" t="str">
-        <x:v>시작 덱. 일반 시전</x:v>
-      </x:c>
-      <x:c r="R17" s="22" t="str">
-        <x:f aca="0">IF(AND(LEFT($C17,1)="딜",ISNUMBER(M17)),M17,"")</x:f>
-      </x:c>
-      <x:c r="S17" s="22" t="str">
-        <x:f aca="0">IF(AND(LEFT($C17,1)="딜",ISNUMBER(N17)),N17,"")</x:f>
-      </x:c>
-      <x:c r="T17" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="15" hidden="0">
-      <x:c r="A18" s="17" t="str">
-        <x:v>SK14</x:v>
-      </x:c>
-      <x:c r="B18" s="17" t="str">
-        <x:v>생츄어리</x:v>
-      </x:c>
-      <x:c r="C18" s="17" t="str">
-        <x:v>방어</x:v>
-      </x:c>
-      <x:c r="D18" s="17" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E18" s="17" t="n">
-        <x:v>2.5</x:v>
-      </x:c>
-      <x:c r="F18" s="22" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(E18)),"",MAX(E18,'범례'!$C$26))</x:f>
-        <x:v>2.5</x:v>
-      </x:c>
-      <x:c r="G18" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H18" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I18" s="19" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G18)),NOT(ISNUMBER(H18))),"",G18*MAX(1,H18)+T18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J18" s="41" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(G18)),NOT(ISNUMBER(H18))),"",IF(G18&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G18*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G18*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H18)-1)+((1-'직업'!$D$5)*MAX(1,INT((G18+T18)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G18+T18)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K18" s="41" t="n">
-        <x:f aca="0">IF(NOT(ISNUMBER(J18)),"",J18*IF(ISNUMBER(SEARCH("광역",$C18)),'범례'!$C$30,1))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L18" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(J18)),NOT(ISNUMBER(D18)),D18=0),"",J18/D18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M18" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K18)),NOT(ISNUMBER(D18)),D18=0),"",K18/D18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="22" t="n">
-        <x:f aca="0">IF(OR(NOT(ISNUMBER(K18)),NOT(ISNUMBER(F18)),F18=0),"",K18/F18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O18" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P18" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q18" s="20" t="str">
-        <x:v>보상. 채널링 중 무적·기절 면역</x:v>
-      </x:c>
-      <x:c r="R18" s="22" t="str">
-        <x:f aca="0">IF(AND(LEFT($C18,1)="딜",ISNUMBER(M18)),M18,"")</x:f>
-      </x:c>
-      <x:c r="S18" s="22" t="str">
-        <x:f aca="0">IF(AND(LEFT($C18,1)="딜",ISNUMBER(N18)),N18,"")</x:f>
-      </x:c>
-      <x:c r="T18" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="15" hidden="0">
-      <x:c r="A22" s="3" t="str">
-        <x:v>구현 딜 카드 비교 (잡몹전 평균 적 수 기준)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="29.850000381469727" hidden="0">
-      <x:c r="A23" s="10" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="B23" s="22" t="n">
-        <x:f aca="0">IFERROR(MAX(R5:R18),"")</x:f>
-        <x:v>57.333333333333336</x:v>
-      </x:c>
-      <x:c r="C23" s="25" t="s">
-        <x:v>69</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="29.850000381469727" hidden="0">
-      <x:c r="A24" s="10" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B24" s="22" t="n">
-        <x:f aca="0">IFERROR(MIN(R5:R18),"")</x:f>
-        <x:v>32.25</x:v>
-      </x:c>
-      <x:c r="C24" s="25"/>
-    </x:row>
-    <x:row r="25" ht="29.850000381469727" hidden="0">
-      <x:c r="A25" s="10" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B25" s="19" t="n">
-        <x:f aca="0">IFERROR(B23/B24,"")</x:f>
-        <x:v>1.777777777777778</x:v>
-      </x:c>
-      <x:c r="C25" s="25" t="s">
-        <x:v>72</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="29.850000381469727" hidden="0">
-      <x:c r="A26" s="10" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B26" s="22" t="n">
-        <x:f aca="0">IFERROR(MAX(S5:S18),"")</x:f>
-        <x:v>349.375</x:v>
-      </x:c>
-      <x:c r="C26" s="25" t="s">
-        <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="29.850000381469727" hidden="0">
-      <x:c r="A27" s="10" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B27" s="22" t="n">
-        <x:f aca="0">IFERROR(MIN(S5:S18),"")</x:f>
-        <x:v>67.32142857142857</x:v>
-      </x:c>
-      <x:c r="C27" s="25"/>
-    </x:row>
-    <x:row r="28" ht="29.850000381469727" hidden="0">
-      <x:c r="A28" s="10" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B28" s="19" t="n">
-        <x:f aca="0">IFERROR(B26/B27,"")</x:f>
-        <x:v>5.189655172413794</x:v>
-      </x:c>
-      <x:c r="C28" s="25" t="s">
-        <x:v>72</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="29.850000381469727" hidden="0">
-      <x:c r="A29" s="10" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B29" s="23" t="n">
-        <x:f aca="0">COUNTIF(C5:C18,"딜/단일")</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C29" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">목표 6</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="29.850000381469727" hidden="0">
-      <x:c r="A30" s="10" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B30" s="23" t="n">
-        <x:f aca="0">COUNTIF(C5:C18,"딜/광역")</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C30" s="25" t="s">
-        <x:v>79</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="29.850000381469727" hidden="0">
-      <x:c r="A31" s="10" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B31" s="23" t="n">
-        <x:f aca="0">COUNTIF(C5:C18,"차단")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C31" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">목표 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="29.850000381469727" hidden="0">
-      <x:c r="A32" s="10" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B32" s="23" t="n">
-        <x:f aca="0">COUNTIF(C5:C18,"방어")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C32" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">목표 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="15" hidden="0">
-      <x:c r="A34" s="14" t="str">
-        <x:v>비율은 참고 지표. 시전 취소·대상 수·실제 사용 장면과 함께 판단.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="15" hidden="0">
-      <x:c r="A35" s="14" t="str">
-        <x:v>제압은 피해+차단의 승인 예외. 10 A23 참조.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="15" hidden="0">
-      <x:c r="A37" s="3" t="s">
-        <x:v>82</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="22" hidden="0" customHeight="1">
-      <x:c r="A38" s="38" t="str">
-        <x:v>단일/광역 기본 방향은 10 T11. 카드별 예외는 A20·A23·A29.</x:v>
-      </x:c>
-      <x:c r="B38" s="39"/>
-      <x:c r="C38" s="39"/>
-      <x:c r="D38" s="39"/>
-      <x:c r="E38" s="39"/>
-      <x:c r="F38" s="39"/>
-      <x:c r="G38" s="39"/>
-      <x:c r="H38" s="39"/>
-      <x:c r="I38" s="39"/>
-      <x:c r="J38" s="39"/>
-      <x:c r="K38" s="39"/>
-      <x:c r="L38" s="39"/>
-      <x:c r="M38" s="39"/>
-      <x:c r="N38" s="39"/>
-      <x:c r="O38" s="39"/>
-      <x:c r="P38" s="39"/>
-      <x:c r="Q38" s="39"/>
-      <x:c r="R38" s="39"/>
-      <x:c r="S38" s="39"/>
-    </x:row>
-    <x:row r="39" ht="22" hidden="0" customHeight="1">
-      <x:c r="A39" s="40" t="str">
-        <x:v>L열은 1체, M열은 일반 전투 평균 적 수 기준. 실제 대상 수·시전 시간을 함께 비교.</x:v>
-      </x:c>
-      <x:c r="B39" s="39"/>
-      <x:c r="C39" s="39"/>
-      <x:c r="D39" s="39"/>
-      <x:c r="E39" s="39"/>
-      <x:c r="F39" s="39"/>
-      <x:c r="G39" s="39"/>
-      <x:c r="H39" s="39"/>
-      <x:c r="I39" s="39"/>
-      <x:c r="J39" s="39"/>
-      <x:c r="K39" s="39"/>
-      <x:c r="L39" s="39"/>
-      <x:c r="M39" s="39"/>
-      <x:c r="N39" s="39"/>
-      <x:c r="O39" s="39"/>
-      <x:c r="P39" s="39"/>
-      <x:c r="Q39" s="39"/>
-      <x:c r="R39" s="39"/>
-      <x:c r="S39" s="39"/>
-    </x:row>
-    <x:row r="40" ht="22" hidden="0" customHeight="1">
-      <x:c r="A40" s="38" t="str">
-        <x:v>보스전은 본체 1체+오브 최대 2체. 광역 가치는 활성 오브 수에 따라 달라짐(10 A43).</x:v>
-      </x:c>
-      <x:c r="B40" s="39"/>
-      <x:c r="C40" s="39"/>
-      <x:c r="D40" s="39"/>
-      <x:c r="E40" s="39"/>
-      <x:c r="F40" s="39"/>
-      <x:c r="G40" s="39"/>
-      <x:c r="H40" s="39"/>
-      <x:c r="I40" s="39"/>
-      <x:c r="J40" s="39"/>
-      <x:c r="K40" s="39"/>
-      <x:c r="L40" s="39"/>
-      <x:c r="M40" s="39"/>
-      <x:c r="N40" s="39"/>
-      <x:c r="O40" s="39"/>
-      <x:c r="P40" s="39"/>
-      <x:c r="Q40" s="39"/>
-      <x:c r="R40" s="39"/>
-      <x:c r="S40" s="39"/>
-    </x:row>
-    <x:row r="41" ht="22" hidden="0" customHeight="1">
-      <x:c r="A41" s="38" t="str">
-        <x:v>광역 시전 시간은 현재 카드별 값을 따름. 채널링은 중단 시 남은 피해 미발생.</x:v>
-      </x:c>
-      <x:c r="B41" s="39"/>
-      <x:c r="C41" s="39"/>
-      <x:c r="D41" s="39"/>
-      <x:c r="E41" s="39"/>
-      <x:c r="F41" s="39"/>
-      <x:c r="G41" s="39"/>
-      <x:c r="H41" s="39"/>
-      <x:c r="I41" s="39"/>
-      <x:c r="J41" s="39"/>
-      <x:c r="K41" s="39"/>
-      <x:c r="L41" s="39"/>
-      <x:c r="M41" s="39"/>
-      <x:c r="N41" s="39"/>
-      <x:c r="O41" s="39"/>
-      <x:c r="P41" s="39"/>
-      <x:c r="Q41" s="39"/>
-      <x:c r="R41" s="39"/>
-      <x:c r="S41" s="39"/>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="9" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="8" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="7" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="10" hidden="0" customWidth="1"/>
+    <col min="10" max="13" width="14" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="13" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="12" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="10" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="42" hidden="0" customWidth="1"/>
+    <col min="18" max="19" width="13" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="20" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20.100000381469727" hidden="0">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>스킬 풀 밸런스 (15종)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" hidden="0">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>현재 구현 15종. SK15 비전 배리어 추가(2026-10-20). 패시브·과잉 피해·시전 취소 제외.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="31.5" hidden="0" customHeight="1">
+      <c r="A4" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="8" t="str">
+        <v>시전/채널(초)</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="8" t="str">
+        <v>1타 피해</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L4" s="8" t="str">
+        <v>코스트당 (1체)</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" s="8" t="str">
+        <v>구현·발동 방식</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="S4" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="T4" s="8" t="str">
+        <v>마지막 추가 피해</v>
+      </c>
+    </row>
+    <row r="5" ht="15" hidden="0">
+      <c r="A5" s="11" t="str">
+        <v>SK01</v>
+      </c>
+      <c r="B5" s="17" t="str">
+        <v>파이어볼</v>
+      </c>
+      <c r="C5" s="17" t="str">
+        <v>딜/단일</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="22" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(E5)),"",MAX(E5,'범례'!$C$26))</f>
+        <v>0.4</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="19" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(H5))),"",G5*MAX(1,H5)+T5)</f>
+        <v>30</v>
+      </c>
+      <c r="J5" s="41" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(H5))),"",IF(G5&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G5*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G5*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H5)-1)+((1-'직업'!$D$5)*MAX(1,INT((G5+T5)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G5+T5)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</f>
+        <v>32.25</v>
+      </c>
+      <c r="K5" s="41" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(J5)),"",J5*IF(ISNUMBER(SEARCH("광역",$C5)),'범례'!$C$30,1))</f>
+        <v>32.25</v>
+      </c>
+      <c r="L5" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(J5)),NOT(ISNUMBER(D5)),D5=0),"",J5/D5)</f>
+        <v>32.25</v>
+      </c>
+      <c r="M5" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K5)),NOT(ISNUMBER(D5)),D5=0),"",K5/D5)</f>
+        <v>32.25</v>
+      </c>
+      <c r="N5" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K5)),NOT(ISNUMBER(F5)),F5=0),"",K5/F5)</f>
+        <v>80.625</v>
+      </c>
+      <c r="O5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="20" t="str">
+        <v>시작 덱. 일반 시전</v>
+      </c>
+      <c r="R5" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C5,1)="딜",ISNUMBER(M5)),M5,"")</f>
+        <v>32.25</v>
+      </c>
+      <c r="S5" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C5,1)="딜",ISNUMBER(N5)),N5,"")</f>
+        <v>80.625</v>
+      </c>
+      <c r="T5" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="15" hidden="0">
+      <c r="A6" s="11" t="str">
+        <v>SK02</v>
+      </c>
+      <c r="B6" s="17" t="str">
+        <v>아이스애로우</v>
+      </c>
+      <c r="C6" s="17" t="str">
+        <v>딜/단일</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F6" s="22" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(E6)),"",MAX(E6,'범례'!$C$26))</f>
+        <v>2.8</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" s="19" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G6)),NOT(ISNUMBER(H6))),"",G6*MAX(1,H6)+T6)</f>
+        <v>175</v>
+      </c>
+      <c r="J6" s="41" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G6)),NOT(ISNUMBER(H6))),"",IF(G6&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G6*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G6*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H6)-1)+((1-'직업'!$D$5)*MAX(1,INT((G6+T6)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G6+T6)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</f>
+        <v>188.5</v>
+      </c>
+      <c r="K6" s="41" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(J6)),"",J6*IF(ISNUMBER(SEARCH("광역",$C6)),'범례'!$C$30,1))</f>
+        <v>188.5</v>
+      </c>
+      <c r="L6" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(J6)),NOT(ISNUMBER(D6)),D6=0),"",J6/D6)</f>
+        <v>37.7</v>
+      </c>
+      <c r="M6" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K6)),NOT(ISNUMBER(D6)),D6=0),"",K6/D6)</f>
+        <v>37.7</v>
+      </c>
+      <c r="N6" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K6)),NOT(ISNUMBER(F6)),F6=0),"",K6/F6)</f>
+        <v>67.32142857142857</v>
+      </c>
+      <c r="O6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="24" t="str">
+        <v>시작 덱. 채널링 0.5초마다, 사망 후딜 0.3초</v>
+      </c>
+      <c r="R6" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C6,1)="딜",ISNUMBER(M6)),M6,"")</f>
+        <v>37.7</v>
+      </c>
+      <c r="S6" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C6,1)="딜",ISNUMBER(N6)),N6,"")</f>
+        <v>67.32142857142857</v>
+      </c>
+      <c r="T6" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="15" hidden="0">
+      <c r="A7" s="11" t="str">
+        <v>SK03</v>
+      </c>
+      <c r="B7" s="17" t="str">
+        <v>매직 커터</v>
+      </c>
+      <c r="C7" s="17" t="str">
+        <v>딜/단일</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="22" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(E7)),"",MAX(E7,'범례'!$C$26))</f>
+        <v>0.4</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G7)),NOT(ISNUMBER(H7))),"",G7*MAX(1,H7)+T7)</f>
+        <v>60</v>
+      </c>
+      <c r="J7" s="41" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G7)),NOT(ISNUMBER(H7))),"",IF(G7&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G7*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G7*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H7)-1)+((1-'직업'!$D$5)*MAX(1,INT((G7+T7)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G7+T7)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</f>
+        <v>64.5</v>
+      </c>
+      <c r="K7" s="41" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(J7)),"",J7*IF(ISNUMBER(SEARCH("광역",$C7)),'범례'!$C$30,1))</f>
+        <v>64.5</v>
+      </c>
+      <c r="L7" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(J7)),NOT(ISNUMBER(D7)),D7=0),"",J7/D7)</f>
+        <v>32.25</v>
+      </c>
+      <c r="M7" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K7)),NOT(ISNUMBER(D7)),D7=0),"",K7/D7)</f>
+        <v>32.25</v>
+      </c>
+      <c r="N7" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K7)),NOT(ISNUMBER(F7)),F7=0),"",K7/F7)</f>
+        <v>161.25</v>
+      </c>
+      <c r="O7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="24" t="str">
+        <v>시작 덱. 일반 시전</v>
+      </c>
+      <c r="R7" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C7,1)="딜",ISNUMBER(M7)),M7,"")</f>
+        <v>32.25</v>
+      </c>
+      <c r="S7" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C7,1)="딜",ISNUMBER(N7)),N7,"")</f>
+        <v>161.25</v>
+      </c>
+      <c r="T7" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="15" hidden="0">
+      <c r="A8" s="11" t="str">
+        <v>SK04</v>
+      </c>
+      <c r="B8" s="17" t="str">
+        <v>파이어 필라</v>
+      </c>
+      <c r="C8" s="17" t="str">
+        <v>딜/광역</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(E8)),"",MAX(E8,'범례'!$C$26))</f>
+        <v>1</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G8)),NOT(ISNUMBER(H8))),"",G8*MAX(1,H8)+T8)</f>
+        <v>90</v>
+      </c>
+      <c r="J8" s="41" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G8)),NOT(ISNUMBER(H8))),"",IF(G8&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G8*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G8*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H8)-1)+((1-'직업'!$D$5)*MAX(1,INT((G8+T8)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G8+T8)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</f>
+        <v>96.75</v>
+      </c>
+      <c r="K8" s="41" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(J8)),"",J8*IF(ISNUMBER(SEARCH("광역",$C8)),'범례'!$C$30,1))</f>
+        <v>193.5</v>
+      </c>
+      <c r="L8" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(J8)),NOT(ISNUMBER(D8)),D8=0),"",J8/D8)</f>
+        <v>24.1875</v>
+      </c>
+      <c r="M8" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K8)),NOT(ISNUMBER(D8)),D8=0),"",K8/D8)</f>
+        <v>48.375</v>
+      </c>
+      <c r="N8" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K8)),NOT(ISNUMBER(F8)),F8=0),"",K8/F8)</f>
+        <v>193.5</v>
+      </c>
+      <c r="O8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="24" t="str">
+        <v>시작 덱. 일반 시전</v>
+      </c>
+      <c r="R8" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C8,1)="딜",ISNUMBER(M8)),M8,"")</f>
+        <v>48.375</v>
+      </c>
+      <c r="S8" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C8,1)="딜",ISNUMBER(N8)),N8,"")</f>
+        <v>193.5</v>
+      </c>
+      <c r="T8" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="15" hidden="0">
+      <c r="A9" s="11" t="str">
+        <v>SK05</v>
+      </c>
+      <c r="B9" s="17" t="str">
+        <v>라이트닝 스피어</v>
+      </c>
+      <c r="C9" s="17" t="str">
+        <v>딜/단일</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(E9)),"",MAX(E9,'범례'!$C$26))</f>
+        <v>0.8</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>135</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G9)),NOT(ISNUMBER(H9))),"",G9*MAX(1,H9)+T9)</f>
+        <v>135</v>
+      </c>
+      <c r="J9" s="41" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G9)),NOT(ISNUMBER(H9))),"",IF(G9&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G9*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G9*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H9)-1)+((1-'직업'!$D$5)*MAX(1,INT((G9+T9)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G9+T9)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</f>
+        <v>145.2</v>
+      </c>
+      <c r="K9" s="41" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(J9)),"",J9*IF(ISNUMBER(SEARCH("광역",$C9)),'범례'!$C$30,1))</f>
+        <v>145.2</v>
+      </c>
+      <c r="L9" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(J9)),NOT(ISNUMBER(D9)),D9=0),"",J9/D9)</f>
+        <v>36.3</v>
+      </c>
+      <c r="M9" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K9)),NOT(ISNUMBER(D9)),D9=0),"",K9/D9)</f>
+        <v>36.3</v>
+      </c>
+      <c r="N9" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K9)),NOT(ISNUMBER(F9)),F9=0),"",K9/F9)</f>
+        <v>181.49999999999997</v>
+      </c>
+      <c r="O9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="24" t="str">
+        <v>시작 덱. 일반 시전</v>
+      </c>
+      <c r="R9" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C9,1)="딜",ISNUMBER(M9)),M9,"")</f>
+        <v>36.3</v>
+      </c>
+      <c r="S9" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C9,1)="딜",ISNUMBER(N9)),N9,"")</f>
+        <v>181.49999999999997</v>
+      </c>
+      <c r="T9" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="15" hidden="0">
+      <c r="A10" s="11" t="str">
+        <v>SK06</v>
+      </c>
+      <c r="B10" s="17" t="str">
+        <v>매직 스파크</v>
+      </c>
+      <c r="C10" s="17" t="str">
+        <v>딜/광역</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(E10)),"",MAX(E10,'범례'!$C$26))</f>
+        <v>2.2</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G10)),NOT(ISNUMBER(H10))),"",G10*MAX(1,H10)+T10)</f>
+        <v>80</v>
+      </c>
+      <c r="J10" s="41" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G10)),NOT(ISNUMBER(H10))),"",IF(G10&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G10*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G10*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H10)-1)+((1-'직업'!$D$5)*MAX(1,INT((G10+T10)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G10+T10)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</f>
+        <v>86</v>
+      </c>
+      <c r="K10" s="41" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(J10)),"",J10*IF(ISNUMBER(SEARCH("광역",$C10)),'범례'!$C$30,1))</f>
+        <v>172</v>
+      </c>
+      <c r="L10" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(J10)),NOT(ISNUMBER(D10)),D10=0),"",J10/D10)</f>
+        <v>28.666666666666668</v>
+      </c>
+      <c r="M10" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K10)),NOT(ISNUMBER(D10)),D10=0),"",K10/D10)</f>
+        <v>57.333333333333336</v>
+      </c>
+      <c r="N10" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K10)),NOT(ISNUMBER(F10)),F10=0),"",K10/F10)</f>
+        <v>78.18181818181817</v>
+      </c>
+      <c r="O10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="24" t="str">
+        <v>시작 덱. 채널링 0.25초마다</v>
+      </c>
+      <c r="R10" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C10,1)="딜",ISNUMBER(M10)),M10,"")</f>
+        <v>57.333333333333336</v>
+      </c>
+      <c r="S10" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C10,1)="딜",ISNUMBER(N10)),N10,"")</f>
+        <v>78.18181818181817</v>
+      </c>
+      <c r="T10" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="15" hidden="0">
+      <c r="A11" s="11" t="str">
+        <v>SK07</v>
+      </c>
+      <c r="B11" s="17" t="str">
+        <v>매직 임팩트</v>
+      </c>
+      <c r="C11" s="17" t="str">
+        <v>딜/단일</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(E11)),"",MAX(E11,'범례'!$C$26))</f>
+        <v>0.4</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G11)),NOT(ISNUMBER(H11))),"",G11*MAX(1,H11)+T11)</f>
+        <v>130</v>
+      </c>
+      <c r="J11" s="41" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G11)),NOT(ISNUMBER(H11))),"",IF(G11&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G11*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G11*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H11)-1)+((1-'직업'!$D$5)*MAX(1,INT((G11+T11)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G11+T11)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</f>
+        <v>139.75</v>
+      </c>
+      <c r="K11" s="41" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(J11)),"",J11*IF(ISNUMBER(SEARCH("광역",$C11)),'범례'!$C$30,1))</f>
+        <v>139.75</v>
+      </c>
+      <c r="L11" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(J11)),NOT(ISNUMBER(D11)),D11=0),"",J11/D11)</f>
+        <v>46.583333333333336</v>
+      </c>
+      <c r="M11" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K11)),NOT(ISNUMBER(D11)),D11=0),"",K11/D11)</f>
+        <v>46.583333333333336</v>
+      </c>
+      <c r="N11" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K11)),NOT(ISNUMBER(F11)),F11=0),"",K11/F11)</f>
+        <v>349.375</v>
+      </c>
+      <c r="O11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="24" t="str">
+        <v>보상. 일반 시전</v>
+      </c>
+      <c r="R11" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C11,1)="딜",ISNUMBER(M11)),M11,"")</f>
+        <v>46.583333333333336</v>
+      </c>
+      <c r="S11" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C11,1)="딜",ISNUMBER(N11)),N11,"")</f>
+        <v>349.375</v>
+      </c>
+      <c r="T11" s="17" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" ht="15" hidden="0">
+      <c r="A12" s="11" t="str">
+        <v>SK08</v>
+      </c>
+      <c r="B12" s="17" t="str">
+        <v>저지먼트</v>
+      </c>
+      <c r="C12" s="17" t="str">
+        <v>딜/단일</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F12" s="41" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(E12)),"",MAX(E12,'범례'!$C$26))</f>
+        <v>2.75</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>365</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"",G12*MAX(1,H12)+T12)</f>
+        <v>365</v>
+      </c>
+      <c r="J12" s="41" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G12)),NOT(ISNUMBER(H12))),"",IF(G12&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G12*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G12*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H12)-1)+((1-'직업'!$D$5)*MAX(1,INT((G12+T12)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G12+T12)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</f>
+        <v>392.45</v>
+      </c>
+      <c r="K12" s="41" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(J12)),"",J12*IF(ISNUMBER(SEARCH("광역",$C12)),'범례'!$C$30,1))</f>
+        <v>392.45</v>
+      </c>
+      <c r="L12" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(J12)),NOT(ISNUMBER(D12)),D12=0),"",J12/D12)</f>
+        <v>56.06428571428571</v>
+      </c>
+      <c r="M12" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K12)),NOT(ISNUMBER(D12)),D12=0),"",K12/D12)</f>
+        <v>56.06428571428571</v>
+      </c>
+      <c r="N12" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K12)),NOT(ISNUMBER(F12)),F12=0),"",K12/F12)</f>
+        <v>142.70909090909092</v>
+      </c>
+      <c r="O12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="24" t="str">
+        <v>보상. 일반 시전</v>
+      </c>
+      <c r="R12" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C12,1)="딜",ISNUMBER(M12)),M12,"")</f>
+        <v>56.06428571428571</v>
+      </c>
+      <c r="S12" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C12,1)="딜",ISNUMBER(N12)),N12,"")</f>
+        <v>142.70909090909092</v>
+      </c>
+      <c r="T12" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="15" hidden="0">
+      <c r="A13" s="17" t="str">
+        <v>SK09</v>
+      </c>
+      <c r="B13" s="17" t="str">
+        <v>블리자드</v>
+      </c>
+      <c r="C13" s="17" t="str">
+        <v>딜/광역</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(E13)),"",MAX(E13,'범례'!$C$26))</f>
+        <v>1</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"",G13*MAX(1,H13)+T13)</f>
+        <v>120</v>
+      </c>
+      <c r="J13" s="41" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(H13))),"",IF(G13&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G13*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G13*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H13)-1)+((1-'직업'!$D$5)*MAX(1,INT((G13+T13)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G13+T13)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</f>
+        <v>129</v>
+      </c>
+      <c r="K13" s="41" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(J13)),"",J13*IF(ISNUMBER(SEARCH("광역",$C13)),'범례'!$C$30,1))</f>
+        <v>258</v>
+      </c>
+      <c r="L13" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(J13)),NOT(ISNUMBER(D13)),D13=0),"",J13/D13)</f>
+        <v>25.8</v>
+      </c>
+      <c r="M13" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K13)),NOT(ISNUMBER(D13)),D13=0),"",K13/D13)</f>
+        <v>51.6</v>
+      </c>
+      <c r="N13" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K13)),NOT(ISNUMBER(F13)),F13=0),"",K13/F13)</f>
+        <v>258</v>
+      </c>
+      <c r="O13" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="20" t="str">
+        <v>보상. 일반 시전, 광역</v>
+      </c>
+      <c r="R13" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C13,1)="딜",ISNUMBER(M13)),M13,"")</f>
+        <v>51.6</v>
+      </c>
+      <c r="S13" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C13,1)="딜",ISNUMBER(N13)),N13,"")</f>
+        <v>258</v>
+      </c>
+      <c r="T13" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="15" hidden="0">
+      <c r="A14" s="17" t="str">
+        <v>SK10</v>
+      </c>
+      <c r="B14" s="17" t="str">
+        <v>다크 이럽션</v>
+      </c>
+      <c r="C14" s="17" t="str">
+        <v>딜/광역</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F14" s="22" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(E14)),"",MAX(E14,'범례'!$C$26))</f>
+        <v>0.5</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G14)),NOT(ISNUMBER(H14))),"",G14*MAX(1,H14)+T14)</f>
+        <v>50</v>
+      </c>
+      <c r="J14" s="41" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G14)),NOT(ISNUMBER(H14))),"",IF(G14&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G14*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G14*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H14)-1)+((1-'직업'!$D$5)*MAX(1,INT((G14+T14)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G14+T14)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</f>
+        <v>53.75</v>
+      </c>
+      <c r="K14" s="41" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(J14)),"",J14*IF(ISNUMBER(SEARCH("광역",$C14)),'범례'!$C$30,1))</f>
+        <v>107.5</v>
+      </c>
+      <c r="L14" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(J14)),NOT(ISNUMBER(D14)),D14=0),"",J14/D14)</f>
+        <v>26.875</v>
+      </c>
+      <c r="M14" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K14)),NOT(ISNUMBER(D14)),D14=0),"",K14/D14)</f>
+        <v>53.75</v>
+      </c>
+      <c r="N14" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K14)),NOT(ISNUMBER(F14)),F14=0),"",K14/F14)</f>
+        <v>215</v>
+      </c>
+      <c r="O14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="20" t="str">
+        <v>보상. 일반 시전</v>
+      </c>
+      <c r="R14" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C14,1)="딜",ISNUMBER(M14)),M14,"")</f>
+        <v>53.75</v>
+      </c>
+      <c r="S14" s="22" t="n">
+        <f aca="0">IF(AND(LEFT($C14,1)="딜",ISNUMBER(N14)),N14,"")</f>
+        <v>215</v>
+      </c>
+      <c r="T14" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="15" hidden="0">
+      <c r="A15" s="17" t="str">
+        <v>SK11</v>
+      </c>
+      <c r="B15" s="17" t="str">
+        <v>침묵</v>
+      </c>
+      <c r="C15" s="17" t="str">
+        <v>차단</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F15" s="22" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(E15)),"",MAX(E15,'범례'!$C$26))</f>
+        <v>0.4</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G15)),NOT(ISNUMBER(H15))),"",G15*MAX(1,H15)+T15)</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="41" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G15)),NOT(ISNUMBER(H15))),"",IF(G15&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G15*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G15*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H15)-1)+((1-'직업'!$D$5)*MAX(1,INT((G15+T15)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G15+T15)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(J15)),"",J15*IF(ISNUMBER(SEARCH("광역",$C15)),'범례'!$C$30,1))</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(J15)),NOT(ISNUMBER(D15)),D15=0),"",J15/D15)</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K15)),NOT(ISNUMBER(D15)),D15=0),"",K15/D15)</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K15)),NOT(ISNUMBER(F15)),F15=0),"",K15/F15)</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q15" s="20" t="str">
+        <v>시작 덱. 일반 시전, 캐스팅 중 대상만</v>
+      </c>
+      <c r="R15" s="22" t="str">
+        <f aca="0">IF(AND(LEFT($C15,1)="딜",ISNUMBER(M15)),M15,"")</f>
+      </c>
+      <c r="S15" s="22" t="str">
+        <f aca="0">IF(AND(LEFT($C15,1)="딜",ISNUMBER(N15)),N15,"")</f>
+      </c>
+      <c r="T15" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="15" hidden="0">
+      <c r="A16" s="17" t="str">
+        <v>SK12</v>
+      </c>
+      <c r="B16" s="17" t="str">
+        <v>제압</v>
+      </c>
+      <c r="C16" s="17" t="str">
+        <v>차단</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F16" s="22" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(E16)),"",MAX(E16,'범례'!$C$26))</f>
+        <v>0.4</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G16)),NOT(ISNUMBER(H16))),"",G16*MAX(1,H16)+T16)</f>
+        <v>40</v>
+      </c>
+      <c r="J16" s="41" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G16)),NOT(ISNUMBER(H16))),"",IF(G16&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G16*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G16*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H16)-1)+((1-'직업'!$D$5)*MAX(1,INT((G16+T16)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G16+T16)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</f>
+        <v>43</v>
+      </c>
+      <c r="K16" s="41" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(J16)),"",J16*IF(ISNUMBER(SEARCH("광역",$C16)),'범례'!$C$30,1))</f>
+        <v>43</v>
+      </c>
+      <c r="L16" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(J16)),NOT(ISNUMBER(D16)),D16=0),"",J16/D16)</f>
+        <v>21.5</v>
+      </c>
+      <c r="M16" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K16)),NOT(ISNUMBER(D16)),D16=0),"",K16/D16)</f>
+        <v>21.5</v>
+      </c>
+      <c r="N16" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K16)),NOT(ISNUMBER(F16)),F16=0),"",K16/F16)</f>
+        <v>107.5</v>
+      </c>
+      <c r="O16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q16" s="20" t="str">
+        <v>보상. 일반 시전, 피해+차단</v>
+      </c>
+      <c r="R16" s="22" t="str">
+        <f aca="0">IF(AND(LEFT($C16,1)="딜",ISNUMBER(M16)),M16,"")</f>
+      </c>
+      <c r="S16" s="22" t="str">
+        <f aca="0">IF(AND(LEFT($C16,1)="딜",ISNUMBER(N16)),N16,"")</f>
+      </c>
+      <c r="T16" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="15" hidden="0">
+      <c r="A17" s="17" t="str">
+        <v>SK13</v>
+      </c>
+      <c r="B17" s="17" t="str">
+        <v>매직아머</v>
+      </c>
+      <c r="C17" s="17" t="str">
+        <v>방어</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F17" s="22" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(E17)),"",MAX(E17,'범례'!$C$26))</f>
+        <v>0.4</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G17)),NOT(ISNUMBER(H17))),"",G17*MAX(1,H17)+T17)</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="41" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G17)),NOT(ISNUMBER(H17))),"",IF(G17&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G17*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G17*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H17)-1)+((1-'직업'!$D$5)*MAX(1,INT((G17+T17)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G17+T17)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(J17)),"",J17*IF(ISNUMBER(SEARCH("광역",$C17)),'범례'!$C$30,1))</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(J17)),NOT(ISNUMBER(D17)),D17=0),"",J17/D17)</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K17)),NOT(ISNUMBER(D17)),D17=0),"",K17/D17)</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K17)),NOT(ISNUMBER(F17)),F17=0),"",K17/F17)</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="P17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="20" t="str">
+        <v>시작 덱. 일반 시전</v>
+      </c>
+      <c r="R17" s="22" t="str">
+        <f aca="0">IF(AND(LEFT($C17,1)="딜",ISNUMBER(M17)),M17,"")</f>
+      </c>
+      <c r="S17" s="22" t="str">
+        <f aca="0">IF(AND(LEFT($C17,1)="딜",ISNUMBER(N17)),N17,"")</f>
+      </c>
+      <c r="T17" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="15" hidden="0">
+      <c r="A18" s="17" t="str">
+        <v>SK14</v>
+      </c>
+      <c r="B18" s="17" t="str">
+        <v>생츄어리</v>
+      </c>
+      <c r="C18" s="17" t="str">
+        <v>방어</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F18" s="22" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(E18)),"",MAX(E18,'범례'!$C$26))</f>
+        <v>2.5</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G18)),NOT(ISNUMBER(H18))),"",G18*MAX(1,H18)+T18)</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="41" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G18)),NOT(ISNUMBER(H18))),"",IF(G18&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G18*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G18*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H18)-1)+((1-'직업'!$D$5)*MAX(1,INT((G18+T18)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G18+T18)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41" t="n">
+        <f aca="0">IF(NOT(ISNUMBER(J18)),"",J18*IF(ISNUMBER(SEARCH("광역",$C18)),'범례'!$C$30,1))</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(J18)),NOT(ISNUMBER(D18)),D18=0),"",J18/D18)</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K18)),NOT(ISNUMBER(D18)),D18=0),"",K18/D18)</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="22" t="n">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K18)),NOT(ISNUMBER(F18)),F18=0),"",K18/F18)</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="20" t="str">
+        <v>보상. 채널링 중 무적·기절 면역</v>
+      </c>
+      <c r="R18" s="22" t="str">
+        <f aca="0">IF(AND(LEFT($C18,1)="딜",ISNUMBER(M18)),M18,"")</f>
+      </c>
+      <c r="S18" s="22" t="str">
+        <f aca="0">IF(AND(LEFT($C18,1)="딜",ISNUMBER(N18)),N18,"")</f>
+      </c>
+      <c r="T18" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="15" hidden="0">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>SK15</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>비전 배리어</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="str">
+        <v>방어</v>
+      </c>
+      <c r="D19" s="17">
+        <v>5</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F19" s="22">
+        <f aca="0">IF(NOT(ISNUMBER(E19)),"",MAX(E19,'범례'!$C$26))</f>
+        <v>0.4</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="19">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G19)),NOT(ISNUMBER(H19))),"",G19*MAX(1,H19)+T19)</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="41">
+        <f aca="0">IF(OR(NOT(ISNUMBER(G19)),NOT(ISNUMBER(H19))),"",IF(G19&lt;=0,0,((1-'직업'!$D$5)*MAX(1,INT(G19*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT(G19*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))*(MAX(1,H19)-1)+((1-'직업'!$D$5)*MAX(1,INT((G19+T19)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)+0.5))+'직업'!$D$5*MAX(1,INT((G19+T19)*'범례'!$C$20/('범례'!$C$21+'범례'!$C$20)*'범례'!$C$19+0.5)))))</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41">
+        <f aca="0">IF(NOT(ISNUMBER(J19)),"",J19*IF(ISNUMBER(SEARCH("광역",$C19)),'범례'!$C$30,1))</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="22">
+        <f aca="0">IF(OR(NOT(ISNUMBER(J19)),NOT(ISNUMBER(D19)),D19=0),"",J19/D19)</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="22">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K19)),NOT(ISNUMBER(D19)),D19=0),"",K19/D19)</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="22">
+        <f aca="0">IF(OR(NOT(ISNUMBER(K19)),NOT(ISNUMBER(F19)),F19=0),"",K19/F19)</f>
+        <v>0</v>
+      </c>
+      <c r="O19" s="17">
+        <v>250</v>
+      </c>
+      <c r="P19" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="20" t="inlineStr">
+        <is>
+          <t>보상. 일반 시전, 방어도 누적</t>
+        </is>
+      </c>
+      <c r="R19" s="22" t="str">
+        <f aca="0">IF(AND(LEFT($C19,1)="딜",ISNUMBER(M19)),M19,"")</f>
+        <v/>
+      </c>
+      <c r="S19" s="22" t="str">
+        <f aca="0">IF(AND(LEFT($C19,1)="딜",ISNUMBER(N19)),N19,"")</f>
+        <v/>
+      </c>
+      <c r="T19" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="15" hidden="0">
+      <c r="A22" s="3" t="str">
+        <v>구현 딜 카드 비교 (잡몹전 평균 적 수 기준)</v>
+      </c>
+    </row>
+    <row r="23" ht="29.850000381469727" hidden="0">
+      <c r="A23" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="22">
+        <f>IFERROR(MAX(R5:R19),"")</f>
+        <v>57.333333333333336</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" ht="29.850000381469727" hidden="0">
+      <c r="A24" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="22">
+        <f>IFERROR(MIN(R5:R19),"")</f>
+        <v>32.25</v>
+      </c>
+      <c r="C24" s="25"/>
+    </row>
+    <row r="25" ht="29.850000381469727" hidden="0">
+      <c r="A25" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="19" t="n">
+        <f aca="0">IFERROR(B23/B24,"")</f>
+        <v>1.777777777777778</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" ht="29.850000381469727" hidden="0">
+      <c r="A26" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="22">
+        <f>IFERROR(MAX(S5:S19),"")</f>
+        <v>349.375</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" ht="29.850000381469727" hidden="0">
+      <c r="A27" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="22">
+        <f>IFERROR(MIN(S5:S19),"")</f>
+        <v>67.32142857142857</v>
+      </c>
+      <c r="C27" s="25"/>
+    </row>
+    <row r="28" ht="29.850000381469727" hidden="0">
+      <c r="A28" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="19" t="n">
+        <f aca="0">IFERROR(B26/B27,"")</f>
+        <v>5.189655172413794</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" ht="29.850000381469727" hidden="0">
+      <c r="A29" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="23">
+        <f>COUNTIF(C5:C19,"딜/단일")</f>
+        <v>6</v>
+      </c>
+      <c r="C29" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목표 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="29.850000381469727" hidden="0">
+      <c r="A30" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="23">
+        <f>COUNTIF(C5:C19,"딜/광역")</f>
+        <v>4</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" ht="29.850000381469727" hidden="0">
+      <c r="A31" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" s="23">
+        <f>COUNTIF(C5:C19,"차단")</f>
+        <v>2</v>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목표 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="29.850000381469727" hidden="0">
+      <c r="A32" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" s="23">
+        <f>COUNTIF(C5:C19,"방어")</f>
+        <v>3</v>
+      </c>
+      <c r="C32" s="25" t="inlineStr">
+        <is>
+          <t>목표 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" hidden="0">
+      <c r="A34" s="14" t="str">
+        <v>비율은 참고 지표. 시전 취소·대상 수·실제 사용 장면과 함께 판단.</v>
+      </c>
+    </row>
+    <row r="35" ht="15" hidden="0">
+      <c r="A35" s="14" t="str">
+        <v>제압은 피해+차단의 승인 예외. 10 A23 참조.</v>
+      </c>
+    </row>
+    <row r="37" ht="15" hidden="0">
+      <c r="A37" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" ht="22" hidden="0" customHeight="1">
+      <c r="A38" s="38" t="str">
+        <v>단일/광역 기본 방향은 10 T11. 카드별 예외는 A20·A23·A29.</v>
+      </c>
+      <c r="B38" s="39"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="39"/>
+      <c r="K38" s="39"/>
+      <c r="L38" s="39"/>
+      <c r="M38" s="39"/>
+      <c r="N38" s="39"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="39"/>
+      <c r="Q38" s="39"/>
+      <c r="R38" s="39"/>
+      <c r="S38" s="39"/>
+    </row>
+    <row r="39" ht="22" hidden="0" customHeight="1">
+      <c r="A39" s="40" t="str">
+        <v>L열은 1체, M열은 일반 전투 평균 적 수 기준. 실제 대상 수·시전 시간을 함께 비교.</v>
+      </c>
+      <c r="B39" s="39"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39"/>
+      <c r="K39" s="39"/>
+      <c r="L39" s="39"/>
+      <c r="M39" s="39"/>
+      <c r="N39" s="39"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="39"/>
+      <c r="Q39" s="39"/>
+      <c r="R39" s="39"/>
+      <c r="S39" s="39"/>
+    </row>
+    <row r="40" ht="22" hidden="0" customHeight="1">
+      <c r="A40" s="38" t="str">
+        <v>보스전은 본체 1체+오브 최대 2체. 광역 가치는 활성 오브 수에 따라 달라짐(10 A43).</v>
+      </c>
+      <c r="B40" s="39"/>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="39"/>
+      <c r="H40" s="39"/>
+      <c r="I40" s="39"/>
+      <c r="J40" s="39"/>
+      <c r="K40" s="39"/>
+      <c r="L40" s="39"/>
+      <c r="M40" s="39"/>
+      <c r="N40" s="39"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="39"/>
+      <c r="Q40" s="39"/>
+      <c r="R40" s="39"/>
+      <c r="S40" s="39"/>
+    </row>
+    <row r="41" ht="22" hidden="0" customHeight="1">
+      <c r="A41" s="38" t="str">
+        <v>광역 시전 시간은 현재 카드별 값을 따름. 채널링은 중단 시 남은 피해 미발생.</v>
+      </c>
+      <c r="B41" s="39"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="39"/>
+      <c r="H41" s="39"/>
+      <c r="I41" s="39"/>
+      <c r="J41" s="39"/>
+      <c r="K41" s="39"/>
+      <c r="L41" s="39"/>
+      <c r="M41" s="39"/>
+      <c r="N41" s="39"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="39"/>
+      <c r="Q41" s="39"/>
+      <c r="R41" s="39"/>
+      <c r="S41" s="39"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Docs/밸런스시트.xlsx
+++ b/Docs/밸런스시트.xlsx
@@ -4799,7 +4799,7 @@
         <v>0</v>
       </c>
       <c r="O19" s="17">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="P19" s="17" t="n">
         <v>0</v>
